--- a/result/result_2.xlsx
+++ b/result/result_2.xlsx
@@ -127,6 +127,61 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2286000" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2286000" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -416,15 +471,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="40" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
     <col width="80" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -458,8 +514,13 @@
           <t>回答</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>图表</t>
+        </is>
+      </c>
     </row>
-    <row r="2">
+    <row r="2" ht="120" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>B1001</t>
@@ -493,13 +554,13 @@
   "子问题": [
     {
       "Q": "金花股份利润总额是多少",
-      "A": "共 12 行：('金花股份', 2022, 'FY', None); ('金花股份', 2023, 'Q1', None); ('金花股份', 2023, 'HY', None)",
+      "A": "金花股份的利润总额从2024三季报的 3,245.72 万元 变化到2025三季报的 3,533.59 万元（+8.87%）",
       "SQL": "SELECT stock_abbr, report_year, report_period, total_profit FROM income_sheet WHERE (stock_abbr='金花股份') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
       "image": "B1001_1.jpg"
     },
     {
       "Q": "2025年第三季度的",
-      "A": "共 1 行：('金花股份', 2025, 'Q3', 3533.59)",
+      "A": "金花股份 2025三季报的利润总额为 3,533.59 万元",
       "SQL": "SELECT stock_abbr, report_year, report_period, total_profit FROM income_sheet WHERE (stock_abbr='金花股份') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
       "image": "B1001_2.jpg"
     }
@@ -507,8 +568,13 @@
 }</t>
         </is>
       </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>B1001_2.jpg</t>
+        </is>
+      </c>
     </row>
-    <row r="3">
+    <row r="3" ht="120" customHeight="1">
       <c r="A3" s="1" t="inlineStr">
         <is>
           <t>B1002</t>
@@ -542,7 +608,7 @@
   "子问题": [
     {
       "Q": "金花股份近几年的利润总额变化趋势是什么样的",
-      "A": "共 12 行：('金花股份', 2022, 'FY', None); ('金花股份', 2023, 'Q1', None); ('金花股份', 2023, 'HY', None)",
+      "A": "金花股份的利润总额从2024三季报的 3,245.72 万元 变化到2025三季报的 3,533.59 万元（+8.87%）",
       "SQL": "SELECT stock_abbr, report_year, report_period, total_profit FROM income_sheet WHERE (stock_abbr='金花股份') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
       "image": "B1002_1.jpg"
     }
@@ -550,8 +616,14 @@
 }</t>
         </is>
       </c>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>B1002_1.jpg</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/result/result_2.xlsx
+++ b/result/result_2.xlsx
@@ -169,6 +169,806 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2286000" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2286000" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2286000" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2286000" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2286000" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2286000" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2286000" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>20</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2286000" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2286000" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="11" name="Image 11" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>25</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2286000" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="12" name="Image 12" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>26</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2286000" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="13" name="Image 13" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>28</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2286000" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId14"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>29</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2286000" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId15"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>30</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2286000" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="16" name="Image 16" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId16"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>34</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2286000" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="17" name="Image 17" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId17"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>40</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2286000" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="18" name="Image 18" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId18"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>42</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2286000" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="19" name="Image 19" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId19"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>44</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2286000" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="20" name="Image 20" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId20"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2286000" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="21" name="Image 21" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId21"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>47</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2286000" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="22" name="Image 22" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId22"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>48</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2286000" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="23" name="Image 23" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId23"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>49</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2286000" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="24" name="Image 24" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId24"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>50</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2286000" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="25" name="Image 25" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId25"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>51</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2286000" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="26" name="Image 26" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId26"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>56</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2286000" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="27" name="Image 27" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId27"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>58</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2286000" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="28" name="Image 28" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId28"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>59</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2286000" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="29" name="Image 29" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId29"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>60</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2286000" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="30" name="Image 30" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId30"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>62</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2286000" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="31" name="Image 31" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId31"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>64</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2286000" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="32" name="Image 32" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId32"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>66</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2286000" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="33" name="Image 33" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId33"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>69</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2286000" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="34" name="Image 34" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId34"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -471,7 +1271,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -622,6 +1422,3110 @@
         </is>
       </c>
     </row>
+    <row r="4" ht="120" customHeight="1">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>B1003</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>数据基本查询</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>[{"Q": "999与白云山相比，去年收益率最高的是"}]</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>SELECT stock_abbr, report_year, report_period, roe FROM core_performance_indicators_sheet WHERE (stock_abbr='白云山' OR stock_code='000999') AND report_period='FY' ORDER BY roe DESC LIMIT 10</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>{
+  "问题编号": "B1003",
+  "问题类型": "数据基本查询",
+  "子问题": [
+    {
+      "Q": "999与白云山相比，去年收益率最高的是",
+      "A": "ROE 排名 Top5：1) 华润三九 15.86%; 2) 白云山 13.46%; 3) 白云山 12.97%; 4) 白云山 11.55%; 5) 华润三九 —",
+      "SQL": "SELECT stock_abbr, report_year, report_period, roe FROM core_performance_indicators_sheet WHERE (stock_abbr='白云山' OR stock_code='000999') AND report_period='FY' ORDER BY roe DESC LIMIT 10",
+      "image": "B1003_1.jpg"
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="inlineStr">
+        <is>
+          <t>B1003_1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="120" customHeight="1">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>B1004</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>数据基本查询</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>[{"Q": "2025年前三季度，公司实现收入超过200亿元的企业有哪些"}]</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr"/>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>{
+  "问题编号": "B1004",
+  "问题类型": "数据基本查询",
+  "子问题": [
+    {
+      "Q": "2025年前三季度，公司实现收入超过200亿元的企业有哪些",
+      "A": "信息不足，无法生成 SQL",
+      "SQL": "",
+      "image": ""
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G5" s="1" t="inlineStr"/>
+    </row>
+    <row r="6" ht="120" customHeight="1">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>B1005</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>数据基本查询</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>[{"Q": "企业名称：三金，第三季度公司主营业务收入是多少"}, {"Q": "2025年第三季度的"}]</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr"/>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t>{
+  "问题编号": "B1005",
+  "问题类型": "数据基本查询",
+  "子问题": [
+    {
+      "Q": "企业名称：三金，第三季度公司主营业务收入是多少",
+      "A": "澄清：请问要查询哪家公司？",
+      "SQL": "",
+      "image": ""
+    },
+    {
+      "Q": "2025年第三季度的",
+      "A": "澄清：请问要查询哪家公司？",
+      "SQL": "",
+      "image": ""
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G6" s="1" t="inlineStr"/>
+    </row>
+    <row r="7" ht="120" customHeight="1">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>B1006</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>数据统计分析查询</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>[{"Q": "分析一下千金药业2025收入情况，看看有什么变化。"}, {"Q": "绘制近3年的收入趋势图"}, {"Q": "绘制水平柱状图"}]</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="inlineStr"/>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="F7" s="1" t="inlineStr">
+        <is>
+          <t>{
+  "问题编号": "B1006",
+  "问题类型": "数据统计分析查询",
+  "子问题": [
+    {
+      "Q": "分析一下千金药业2025收入情况，看看有什么变化。",
+      "A": "信息不足，无法生成 SQL",
+      "SQL": "",
+      "image": ""
+    },
+    {
+      "Q": "绘制近3年的收入趋势图",
+      "A": "澄清：请问要分析哪家公司的趋势？",
+      "SQL": "",
+      "image": ""
+    },
+    {
+      "Q": "绘制水平柱状图",
+      "A": "澄清：请问要查询哪家公司？",
+      "SQL": "",
+      "image": ""
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G7" s="1" t="inlineStr"/>
+    </row>
+    <row r="8" ht="120" customHeight="1">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>B1007</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>数据统计分析查询</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>[{"Q": "哪些企业是亏钱的？"}, {"Q": "“亏钱”在业务场景中，指的是经审计财务报表的核心利润指标为负的数据。"}]</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="inlineStr"/>
+      <c r="E8" s="1" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="F8" s="1" t="inlineStr">
+        <is>
+          <t>{
+  "问题编号": "B1007",
+  "问题类型": "数据统计分析查询",
+  "子问题": [
+    {
+      "Q": "哪些企业是亏钱的？",
+      "A": "澄清：请问要查询哪家公司？",
+      "SQL": "",
+      "image": ""
+    },
+    {
+      "Q": "“亏钱”在业务场景中，指的是经审计财务报表的核心利润指标为负的数据。",
+      "A": "澄清：请问要查询哪家公司？",
+      "SQL": "",
+      "image": ""
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G8" s="1" t="inlineStr"/>
+    </row>
+    <row r="9" ht="120" customHeight="1">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>B1008</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>数据基本查询</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>[{"Q": "香雪制药2024年研发费用是多少"}, {"Q": "销售费用是多少"}]</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="inlineStr"/>
+      <c r="E9" s="1" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="F9" s="1" t="inlineStr">
+        <is>
+          <t>{
+  "问题编号": "B1008",
+  "问题类型": "数据基本查询",
+  "子问题": [
+    {
+      "Q": "香雪制药2024年研发费用是多少",
+      "A": "澄清：请问要查询哪家公司？",
+      "SQL": "",
+      "image": ""
+    },
+    {
+      "Q": "销售费用是多少",
+      "A": "澄清：请问要查询哪家公司？",
+      "SQL": "",
+      "image": ""
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G9" s="1" t="inlineStr"/>
+    </row>
+    <row r="10" ht="120" customHeight="1">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>B1009</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>数据统计分析查询</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>[{"Q": "2025年第三季度，66家中药公司中“营业总收入”和“净利润”均排名前五的公司有哪些？请列出其股票代码、简称、营业总收入（万元）、净利润（万元）"}]</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t>SELECT stock_abbr, report_year, report_period, net_profit FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY net_profit DESC LIMIT 10</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="F10" s="1" t="inlineStr">
+        <is>
+          <t>{
+  "问题编号": "B1009",
+  "问题类型": "数据统计分析查询",
+  "子问题": [
+    {
+      "Q": "2025年第三季度，66家中药公司中“营业总收入”和“净利润”均排名前五的公司有哪些？请列出其股票代码、简称、营业总收入（万元）、净利润（万元）",
+      "A": "净利润 排名 Top5：1) 白云山 33.98 亿元; 2) 达仁堂 21.46 亿元; 3) 片仔癀 21.33 亿元; 4) 同仁堂 15.93 亿元; 5) 济川药业 10.24 亿元",
+      "SQL": "SELECT stock_abbr, report_year, report_period, net_profit FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY net_profit DESC LIMIT 10",
+      "image": "B1009_1.jpg"
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G10" s="1" t="inlineStr">
+        <is>
+          <t>B1009_1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="120" customHeight="1">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>B1010</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>数据统计分析查询</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>[{"Q": "对比白云山（600332）2022年至2025年第三季度的“营业总收入同比增长率”，展示各报告期的增长率数据，并生成趋势折线图。"}]</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="inlineStr">
+        <is>
+          <t>SELECT stock_abbr, report_year, report_period, total_operating_revenue FROM income_sheet WHERE (stock_abbr='白云山' OR stock_code='600332') AND report_year IN (2022,2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END</t>
+        </is>
+      </c>
+      <c r="E11" s="1" t="inlineStr">
+        <is>
+          <t>line</t>
+        </is>
+      </c>
+      <c r="F11" s="1" t="inlineStr">
+        <is>
+          <t>{
+  "问题编号": "B1010",
+  "问题类型": "数据统计分析查询",
+  "子问题": [
+    {
+      "Q": "对比白云山（600332）2022年至2025年第三季度的“营业总收入同比增长率”，展示各报告期的增长率数据，并生成趋势折线图。",
+      "A": "白云山 2025三季报 的营业总收入为 616.06 亿元（仅有效值）",
+      "SQL": "SELECT stock_abbr, report_year, report_period, total_operating_revenue FROM income_sheet WHERE (stock_abbr='白云山' OR stock_code='600332') AND report_year IN (2022,2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
+      "image": "B1010_1.jpg"
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G11" s="1" t="inlineStr">
+        <is>
+          <t>B1010_1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="120" customHeight="1">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>B1011</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>数据统计分析查询</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t>[{"Q": "2025年第三季度，资产负债率（负债总额/资产总额）超过60%的中药公司有哪些？请列出股票代码、简称、资产负债率（%）。"}]</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="inlineStr"/>
+      <c r="E12" s="1" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="F12" s="1" t="inlineStr">
+        <is>
+          <t>{
+  "问题编号": "B1011",
+  "问题类型": "数据统计分析查询",
+  "子问题": [
+    {
+      "Q": "2025年第三季度，资产负债率（负债总额/资产总额）超过60%的中药公司有哪些？请列出股票代码、简称、资产负债率（%）。",
+      "A": "澄清：请问要查询哪家公司？",
+      "SQL": "",
+      "image": ""
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G12" s="1" t="inlineStr"/>
+    </row>
+    <row r="13" ht="120" customHeight="1">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>B1012</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>数据统计分析查询</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>[{"Q": "2025年第三季度，“经营性现金流量净额”为负数且“净利润”为正数的公司有哪些？请列出其股票代码、简称、经营性现金流净额（万元）、净利润（万元）。"}]</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="inlineStr"/>
+      <c r="E13" s="1" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="F13" s="1" t="inlineStr">
+        <is>
+          <t>{
+  "问题编号": "B1012",
+  "问题类型": "数据统计分析查询",
+  "子问题": [
+    {
+      "Q": "2025年第三季度，“经营性现金流量净额”为负数且“净利润”为正数的公司有哪些？请列出其股票代码、简称、经营性现金流净额（万元）、净利润（万元）。",
+      "A": "澄清：请问要查询哪家公司？",
+      "SQL": "",
+      "image": ""
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G13" s="1" t="inlineStr"/>
+    </row>
+    <row r="14" ht="120" customHeight="1">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>B1013</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>数据统计分析查询</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t>[{"Q": "2025年第三季度，“销售毛利率”和“销售净利率”均高于行业均值的中药公司有哪些？请同步输出行业均值和公司具体数值。"}]</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="inlineStr"/>
+      <c r="E14" s="1" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="F14" s="1" t="inlineStr">
+        <is>
+          <t>{
+  "问题编号": "B1013",
+  "问题类型": "数据统计分析查询",
+  "子问题": [
+    {
+      "Q": "2025年第三季度，“销售毛利率”和“销售净利率”均高于行业均值的中药公司有哪些？请同步输出行业均值和公司具体数值。",
+      "A": "澄清：请问要查询哪家公司？",
+      "SQL": "",
+      "image": ""
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G14" s="1" t="inlineStr"/>
+    </row>
+    <row r="15" ht="120" customHeight="1">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>B1014</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>数据统计分析查询</t>
+        </is>
+      </c>
+      <c r="C15" s="1" t="inlineStr">
+        <is>
+          <t>[{"Q": "云南白药（000538）2025年第三季度的“营业总收入环比增长率”与2024年第三季度的环比增长率相比，变化了多少？请展示两年同期的环比数据。"}]</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="inlineStr">
+        <is>
+          <t>SELECT stock_abbr, report_year, report_period, total_operating_revenue FROM income_sheet WHERE (stock_abbr='云南白药' OR stock_code='000538') AND report_year IN (2025,2024) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END</t>
+        </is>
+      </c>
+      <c r="E15" s="1" t="inlineStr">
+        <is>
+          <t>line</t>
+        </is>
+      </c>
+      <c r="F15" s="1" t="inlineStr">
+        <is>
+          <t>{
+  "问题编号": "B1014",
+  "问题类型": "数据统计分析查询",
+  "子问题": [
+    {
+      "Q": "云南白药（000538）2025年第三季度的“营业总收入环比增长率”与2024年第三季度的环比增长率相比，变化了多少？请展示两年同期的环比数据。",
+      "A": "未查询到有效数据",
+      "SQL": "SELECT stock_abbr, report_year, report_period, total_operating_revenue FROM income_sheet WHERE (stock_abbr='云南白药' OR stock_code='000538') AND report_year IN (2025,2024) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
+      "image": "B1014_1.jpg"
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G15" s="1" t="inlineStr">
+        <is>
+          <t>B1014_1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="120" customHeight="1">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>B1015</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>数据统计分析查询</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="inlineStr">
+        <is>
+          <t>[{"Q": "2022-2025年第三季度，“加权平均净资产收益率（扣非）”连续四个报告期均超过10%的公司有哪些？请列出股票代码、简称及各期收益率。"}]</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="inlineStr"/>
+      <c r="E16" s="1" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="F16" s="1" t="inlineStr">
+        <is>
+          <t>{
+  "问题编号": "B1015",
+  "问题类型": "数据统计分析查询",
+  "子问题": [
+    {
+      "Q": "2022-2025年第三季度，“加权平均净资产收益率（扣非）”连续四个报告期均超过10%的公司有哪些？请列出股票代码、简称及各期收益率。",
+      "A": "澄清：请问要查询哪家公司？",
+      "SQL": "",
+      "image": ""
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G16" s="1" t="inlineStr"/>
+    </row>
+    <row r="17" ht="120" customHeight="1">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>B1016</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>数据统计分析查询</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t>[{"Q": "2025年第三季度，“资产-存货”金额排名前三的公司，其“营业总收入”与存货金额的比值分别是多少？请列出公司简称、存货（万元）、营业总收入（万元）及比值。"}]</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="inlineStr">
+        <is>
+          <t>SELECT stock_abbr, report_year, report_period, total_operating_revenue FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY total_operating_revenue DESC LIMIT 10</t>
+        </is>
+      </c>
+      <c r="E17" s="1" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="F17" s="1" t="inlineStr">
+        <is>
+          <t>{
+  "问题编号": "B1016",
+  "问题类型": "数据统计分析查询",
+  "子问题": [
+    {
+      "Q": "2025年第三季度，“资产-存货”金额排名前三的公司，其“营业总收入”与存货金额的比值分别是多少？请列出公司简称、存货（万元）、营业总收入（万元）及比值。",
+      "A": "营业总收入 排名 Top5：1) 白云山 616.06 亿元; 2) 同仁堂 133.08 亿元; 3) 步长制药 84.69 亿元; 4) 太极集团 80.88 亿元; 5) 片仔癀 74.42 亿元",
+      "SQL": "SELECT stock_abbr, report_year, report_period, total_operating_revenue FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY total_operating_revenue DESC LIMIT 10",
+      "image": "B1016_1.jpg"
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G17" s="1" t="inlineStr">
+        <is>
+          <t>B1016_1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="120" customHeight="1">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>B1017</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t>数据统计分析查询</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="inlineStr">
+        <is>
+          <t>[{"Q": "2025年第三季度，“资产-应收账款”占“营业总收入”比例超过30%的公司有哪些？请列出股票代码、简称、应收账款占比（%）。"}]</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="inlineStr"/>
+      <c r="E18" s="1" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="F18" s="1" t="inlineStr">
+        <is>
+          <t>{
+  "问题编号": "B1017",
+  "问题类型": "数据统计分析查询",
+  "子问题": [
+    {
+      "Q": "2025年第三季度，“资产-应收账款”占“营业总收入”比例超过30%的公司有哪些？请列出股票代码、简称、应收账款占比（%）。",
+      "A": "澄清：请问要查询哪家公司？",
+      "SQL": "",
+      "image": ""
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G18" s="1" t="inlineStr"/>
+    </row>
+    <row r="19" ht="120" customHeight="1">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>B1018</t>
+        </is>
+      </c>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t>数据统计分析查询</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t>[{"Q": "2025年第三季度，“净利润同比增长率”波动最大（即与2024年同期相比，增幅或降幅绝对值最大）的3家公司是哪些？请展示具体增长率。"}]</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="inlineStr">
+        <is>
+          <t>SELECT stock_abbr, report_year, report_period, net_profit FROM income_sheet WHERE report_year IN (2025,2024) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END</t>
+        </is>
+      </c>
+      <c r="E19" s="1" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="F19" s="1" t="inlineStr">
+        <is>
+          <t>{
+  "问题编号": "B1018",
+  "问题类型": "数据统计分析查询",
+  "子问题": [
+    {
+      "Q": "2025年第三季度，“净利润同比增长率”波动最大（即与2024年同期相比，增幅或降幅绝对值最大）的3家公司是哪些？请展示具体增长率。",
+      "A": "净利润 对比：赛隆药业 2024三季报 —; 贵州百灵 2025三季报 —; 东阿阿胶 2024三季报 —; 东阿阿胶 2025三季报 —; 云南白药 2024三季报 —; 云南白药 2025三季报 —; 启迪药业 2024三季报 —; 启迪药业 2025三季报 —; 仁和药业 2024三季报 —; 仁和药业 2025三季报 —; 通化金马 2024三季报 —; 通化金马 2025三季报 —; 华神科技 2024三季报 —; 华神科技 2025三季报 —; 九芝堂 2025三季报 —; 华润三九 2024三季报 —; 华润三九 2025三季报 —; 万邦德 2024三季报 —; 万邦德 2025三季报 —; 沃华医药 2024三季报 —; 沃华医药 2025三季报 —; 莱茵生物 2024三季报 —; 莱茵生物 2025三季报 —; 嘉应制药 2024三季报 —; 嘉应制药 2025三季报 —; 新里程 2024三季报 —; 新里程 2025三季报 —; 桂林三金 2024三季报 —; 桂林三金 2025三季报 —; 奇正藏药 2024三季报 —; 奇正藏药 2025三季报 —; 众生药业 2024三季报 —; 众生药业 2025三季报 —; 精华制药 2024三季报 —; 精华制药 2025三季报 —; 信邦制药 2024三季报 —; 信邦制药 2025三季报 —; 益盛药业 2024三季报 —; 益盛药业 2025三季报 —; 瑞康医药 2024三季报 —; 瑞康医药 2025三季报 —; 以岭药业 2024三季报 —; 以岭药业 2025三季报 —; 特一药业 2024三季报 —; 特一药业 2025三季报 —; 葵花药业 2024三季报 —; 葵花药业 2025三季报 —; 康弘药业 2024三季报 —; 康弘药业 2025三季报 —; 盘龙药业 2024三季报 —; 盘龙药业 2025三季报 —; 新天药业 2024三季报 —; 新天药业 2025三季报 —; 华森制药 2024三季报 —; 华森制药 2025三季报 —; 红日药业 2024三季报 —; 红日药业 2025三季报 —; 振东制药 2024三季报 —; 振东制药 2025三季报 —; 佐力药业 2024三季报 —; 佐力药业 2025三季报 —; 新光药业 2024三季报 —; 新光药业 2025三季报 —; 陇神戎发 2024三季报 —; 陇神戎发 2025三季报 —; 康泰医学 2024三季报 —; 康泰医学 2025三季报 —; 维康药业 2024三季报 —; 维康药业 2025三季报 —; 粤万年青 2024三季报 —; 粤万年青 2025三季报 —; 恩威医药 2024三季报 —; 恩威医药 2025三季报 —; 金花股份 2024三季报 3,077.02 万元; 金花股份 2025三季报 3,423.74 万元; 同仁堂 2024三季报 19.84 亿元; 同仁堂 2025三季报 15.93 亿元; 太极集团 2024三季报 5.52 亿元; 太极集团 2025三季报 1.64 亿元; 太龙药业 2024三季报 2,994.75 万元; 太龙药业 2025三季报 3,047.46 万元; 中恒集团 2024三季报 -918.55 万元; 中恒集团 2025三季报 -931.86 万元; 羚锐制药 2024三季报 5.74 亿元; 羚锐制药 2025三季报 6.54 亿元; 达仁堂 2024三季报 7.93 亿元; 达仁堂 2025三季报 21.46 亿元; 白云山 2024三季报 32.89 亿元; 白云山 2025三季报 33.98 亿元; 亚宝药业 2024三季报 2.28 亿元; 亚宝药业 2025三季报 1.98 亿元; 昆药集团 2024三季报 3.91 亿元; 昆药集团 2025三季报 3.23 亿元; 片仔癀 2024三季报 27.18 亿元; 片仔癀 2025三季报 21.33 亿元; 千金药业 2024三季报 2.13 亿元; 千金药业 2025三季报 2.58 亿元; 康美药业 2024三季报 811.09 万元; 康美药业 2025三季报 1,509.11 万元; 天士力 2024三季报 8.28 亿元; 天士力 2025三季报 9.93 亿元; 康缘药业 2024三季报 3.64 亿元; 康缘药业 2025三季报 2.08 亿元; 济川药业 2024三季报 19.07 亿元; 济川药业 2025三季报 10.24 亿元; 康恩贝 2024三季报 5.46 亿元; 康恩贝 2025三季报 5.96 亿元; 益佰制药 2024三季报 —; 益佰制药 2025三季报 -9,062.98 万元; 神奇制药 2024三季报 5,881.42 万元; 神奇制药 2025三季报 5,109.10 万元; 天目药业 2024三季报 -376.11 万元; 天目药业 2025三季报 750.81 万元; 江中药业 2024三季报 6.84 亿元; 江中药业 2025三季报 7.43 亿元; 广誉远 2024三季报 8,032.73 万元; 广誉远 2025三季报 8,215.46 万元; 健民集团 2024三季报 3.25 亿元; 健民集团 2025三季报 2.89 亿元; 马应龙 2024三季报 4.72 亿元; 马应龙 2025三季报 5.19 亿元; 康惠制药 2024三季报 -4,778.22 万元; 康惠制药 2025三季报 -1.57 亿元; 贵州三力 2024三季报 1.99 亿元; 贵州三力 2025三季报 8,367.73 万元; 珍宝岛 2024三季报 3.96 亿元; 珍宝岛 2025三季报 -3.76 亿元; 步长制药 2024三季报 —; 步长制药 2025三季报 7.91 亿元; 寿仙谷 2024三季报 1.19 亿元; 寿仙谷 2025三季报 7,634.62 万元; 方盛制药 2024三季报 2.27 亿元; 方盛制药 2025三季报 2.65 亿元",
+      "SQL": "SELECT stock_abbr, report_year, report_period, net_profit FROM income_sheet WHERE report_year IN (2025,2024) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
+      "image": "B1018_1.jpg"
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G19" s="1" t="inlineStr">
+        <is>
+          <t>B1018_1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="120" customHeight="1">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>B1019</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>数据统计分析查询</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t>[{"Q": "2025年第三季度，“营业总支出-研发费用”占“营业总收入”比例排名前五的公司有哪些？请列出简称、研发费用占比（%）。"}]</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="inlineStr">
+        <is>
+          <t>SELECT stock_abbr, report_year, report_period, total_operating_revenue FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY total_operating_revenue DESC LIMIT 10</t>
+        </is>
+      </c>
+      <c r="E20" s="1" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="F20" s="1" t="inlineStr">
+        <is>
+          <t>{
+  "问题编号": "B1019",
+  "问题类型": "数据统计分析查询",
+  "子问题": [
+    {
+      "Q": "2025年第三季度，“营业总支出-研发费用”占“营业总收入”比例排名前五的公司有哪些？请列出简称、研发费用占比（%）。",
+      "A": "营业总收入 排名 Top5：1) 白云山 616.06 亿元; 2) 同仁堂 133.08 亿元; 3) 步长制药 84.69 亿元; 4) 太极集团 80.88 亿元; 5) 片仔癀 74.42 亿元",
+      "SQL": "SELECT stock_abbr, report_year, report_period, total_operating_revenue FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY total_operating_revenue DESC LIMIT 10",
+      "image": "B1019_1.jpg"
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G20" s="1" t="inlineStr">
+        <is>
+          <t>B1019_1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="120" customHeight="1">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>B1020</t>
+        </is>
+      </c>
+      <c r="B21" s="1" t="inlineStr">
+        <is>
+          <t>数据统计分析查询</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="inlineStr">
+        <is>
+          <t>[{"Q": "2025年第三季度，“股东权益-未分配利润”金额排名前五的公司，其2025年的“净利润”占未分配利润的比例是多少？请展示具体数值。"}]</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="inlineStr">
+        <is>
+          <t>SELECT stock_abbr, report_year, report_period, net_profit FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY net_profit DESC LIMIT 10</t>
+        </is>
+      </c>
+      <c r="E21" s="1" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="F21" s="1" t="inlineStr">
+        <is>
+          <t>{
+  "问题编号": "B1020",
+  "问题类型": "数据统计分析查询",
+  "子问题": [
+    {
+      "Q": "2025年第三季度，“股东权益-未分配利润”金额排名前五的公司，其2025年的“净利润”占未分配利润的比例是多少？请展示具体数值。",
+      "A": "净利润 排名 Top5：1) 白云山 33.98 亿元; 2) 达仁堂 21.46 亿元; 3) 片仔癀 21.33 亿元; 4) 同仁堂 15.93 亿元; 5) 济川药业 10.24 亿元",
+      "SQL": "SELECT stock_abbr, report_year, report_period, net_profit FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY net_profit DESC LIMIT 10",
+      "image": "B1020_1.jpg"
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G21" s="1" t="inlineStr">
+        <is>
+          <t>B1020_1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="120" customHeight="1">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>B1021</t>
+        </is>
+      </c>
+      <c r="B22" s="1" t="inlineStr">
+        <is>
+          <t>数据统计分析查询</t>
+        </is>
+      </c>
+      <c r="C22" s="1" t="inlineStr">
+        <is>
+          <t>[{"Q": "2025年第三季度，“负债-短期借款”金额超过“资产-货币资金”金额的公司有哪些？请列出简称、短期借款（万元）、货币资金（万元）。"}]</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="inlineStr"/>
+      <c r="E22" s="1" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="F22" s="1" t="inlineStr">
+        <is>
+          <t>{
+  "问题编号": "B1021",
+  "问题类型": "数据统计分析查询",
+  "子问题": [
+    {
+      "Q": "2025年第三季度，“负债-短期借款”金额超过“资产-货币资金”金额的公司有哪些？请列出简称、短期借款（万元）、货币资金（万元）。",
+      "A": "澄清：请问要查询哪家公司？",
+      "SQL": "",
+      "image": ""
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G22" s="1" t="inlineStr"/>
+    </row>
+    <row r="23" ht="120" customHeight="1">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>B1022</t>
+        </is>
+      </c>
+      <c r="B23" s="1" t="inlineStr">
+        <is>
+          <t>数据统计分析查询</t>
+        </is>
+      </c>
+      <c r="C23" s="1" t="inlineStr">
+        <is>
+          <t>[{"Q": "2025年第三季度，“核心业绩指标表”中的“营业总收入”与“利润表”中的“营业总收入”不一致的公司有哪些？请列出股票代码及两个表中的数值。"}]</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="inlineStr"/>
+      <c r="E23" s="1" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="F23" s="1" t="inlineStr">
+        <is>
+          <t>{
+  "问题编号": "B1022",
+  "问题类型": "数据统计分析查询",
+  "子问题": [
+    {
+      "Q": "2025年第三季度，“核心业绩指标表”中的“营业总收入”与“利润表”中的“营业总收入”不一致的公司有哪些？请列出股票代码及两个表中的数值。",
+      "A": "澄清：请问要查询哪家公司？",
+      "SQL": "",
+      "image": ""
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G23" s="1" t="inlineStr"/>
+    </row>
+    <row r="24" ht="120" customHeight="1">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>B1023</t>
+        </is>
+      </c>
+      <c r="B24" s="1" t="inlineStr">
+        <is>
+          <t>数据统计分析查询</t>
+        </is>
+      </c>
+      <c r="C24" s="1" t="inlineStr">
+        <is>
+          <t>[{"Q": "计算2022年财报至2025年第三季度，66家公司的营业总收入复合增长率，排名前三的公司是哪些？请展示复合增长率（%）。"}]</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="inlineStr">
+        <is>
+          <t>SELECT stock_abbr, report_year, report_period, total_operating_revenue FROM income_sheet WHERE report_year IN (2022,2025) AND report_period IN ('Q3') ORDER BY total_operating_revenue DESC LIMIT 10</t>
+        </is>
+      </c>
+      <c r="E24" s="1" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="F24" s="1" t="inlineStr">
+        <is>
+          <t>{
+  "问题编号": "B1023",
+  "问题类型": "数据统计分析查询",
+  "子问题": [
+    {
+      "Q": "计算2022年财报至2025年第三季度，66家公司的营业总收入复合增长率，排名前三的公司是哪些？请展示复合增长率（%）。",
+      "A": "营业总收入 排名 Top5：1) 白云山 616.06 亿元; 2) 同仁堂 133.08 亿元; 3) 步长制药 84.69 亿元; 4) 太极集团 80.88 亿元; 5) 片仔癀 74.42 亿元",
+      "SQL": "SELECT stock_abbr, report_year, report_period, total_operating_revenue FROM income_sheet WHERE report_year IN (2022,2025) AND report_period IN ('Q3') ORDER BY total_operating_revenue DESC LIMIT 10",
+      "image": "B1023_1.jpg"
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G24" s="1" t="inlineStr">
+        <is>
+          <t>B1023_1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="120" customHeight="1">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>B1024</t>
+        </is>
+      </c>
+      <c r="B25" s="1" t="inlineStr">
+        <is>
+          <t>数据统计分析查询</t>
+        </is>
+      </c>
+      <c r="C25" s="1" t="inlineStr">
+        <is>
+          <t>[{"Q": "2025年第三季度，“扣非净利润”与“净利润”的差值绝对值最大的5家公司是哪些？请列出简称、净利润（万元）、扣非净利润（万元）及差值。"}]</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="inlineStr"/>
+      <c r="E25" s="1" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="F25" s="1" t="inlineStr">
+        <is>
+          <t>{
+  "问题编号": "B1024",
+  "问题类型": "数据统计分析查询",
+  "子问题": [
+    {
+      "Q": "2025年第三季度，“扣非净利润”与“净利润”的差值绝对值最大的5家公司是哪些？请列出简称、净利润（万元）、扣非净利润（万元）及差值。",
+      "A": "澄清：请问要查询哪家公司？",
+      "SQL": "",
+      "image": ""
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G25" s="1" t="inlineStr"/>
+    </row>
+    <row r="26" ht="120" customHeight="1">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>B1025</t>
+        </is>
+      </c>
+      <c r="B26" s="1" t="inlineStr">
+        <is>
+          <t>数据统计分析查询</t>
+        </is>
+      </c>
+      <c r="C26" s="1" t="inlineStr">
+        <is>
+          <t>[{"Q": "2025年第三季度，“投资性现金流量净额”为正数（即投资现金流入大于流出）的公司有多少家？请列出其中营收排名前三的公司简称及投资现金流净额（万元）。"}]</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="inlineStr">
+        <is>
+          <t>SELECT stock_abbr, report_year, report_period, net_cash_flow FROM cash_flow_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY net_cash_flow DESC LIMIT 10</t>
+        </is>
+      </c>
+      <c r="E26" s="1" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="F26" s="1" t="inlineStr">
+        <is>
+          <t>{
+  "问题编号": "B1025",
+  "问题类型": "数据统计分析查询",
+  "子问题": [
+    {
+      "Q": "2025年第三季度，“投资性现金流量净额”为正数（即投资现金流入大于流出）的公司有多少家？请列出其中营收排名前三的公司简称及投资现金流净额（万元）。",
+      "A": "现金流净额 排名 Top5：1) 广誉远 1.80 亿元; 2) 太龙药业 1.75 亿元; 3) 江中药业 1.15 亿元; 4) 益佰制药 7,268.83 万元; 5) 亚宝药业 6,714.99 万元",
+      "SQL": "SELECT stock_abbr, report_year, report_period, net_cash_flow FROM cash_flow_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY net_cash_flow DESC LIMIT 10",
+      "image": "B1025_1.jpg"
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G26" s="1" t="inlineStr">
+        <is>
+          <t>B1025_1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="120" customHeight="1">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>B1026</t>
+        </is>
+      </c>
+      <c r="B27" s="1" t="inlineStr">
+        <is>
+          <t>数据统计分析查询</t>
+        </is>
+      </c>
+      <c r="C27" s="1" t="inlineStr">
+        <is>
+          <t>[{"Q": "2025年第三季度，“营业总支出-销售费用”占“营业总收入”比例低于行业均值的公司中，“净利润”最高的3家是哪些？请同步展示行业均值。"}]</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="inlineStr">
+        <is>
+          <t>SELECT stock_abbr, report_year, report_period, net_profit FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY net_profit DESC LIMIT 10</t>
+        </is>
+      </c>
+      <c r="E27" s="1" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="F27" s="1" t="inlineStr">
+        <is>
+          <t>{
+  "问题编号": "B1026",
+  "问题类型": "数据统计分析查询",
+  "子问题": [
+    {
+      "Q": "2025年第三季度，“营业总支出-销售费用”占“营业总收入”比例低于行业均值的公司中，“净利润”最高的3家是哪些？请同步展示行业均值。",
+      "A": "净利润 排名 Top5：1) 白云山 33.98 亿元; 2) 达仁堂 21.46 亿元; 3) 片仔癀 21.33 亿元; 4) 同仁堂 15.93 亿元; 5) 济川药业 10.24 亿元",
+      "SQL": "SELECT stock_abbr, report_year, report_period, net_profit FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY net_profit DESC LIMIT 10",
+      "image": "B1026_1.jpg"
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G27" s="1" t="inlineStr">
+        <is>
+          <t>B1026_1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="120" customHeight="1">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>B1027</t>
+        </is>
+      </c>
+      <c r="B28" s="1" t="inlineStr">
+        <is>
+          <t>数据统计分析查询</t>
+        </is>
+      </c>
+      <c r="C28" s="1" t="inlineStr">
+        <is>
+          <t>[{"Q": "2025年第三季度，“资产-总资产同比增长率”超过“营业总收入同比增长率”10个百分点以上的公司有哪些？请列出简称、资产增长率（%）、营收增长率（%）。"}]</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="inlineStr"/>
+      <c r="E28" s="1" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="F28" s="1" t="inlineStr">
+        <is>
+          <t>{
+  "问题编号": "B1027",
+  "问题类型": "数据统计分析查询",
+  "子问题": [
+    {
+      "Q": "2025年第三季度，“资产-总资产同比增长率”超过“营业总收入同比增长率”10个百分点以上的公司有哪些？请列出简称、资产增长率（%）、营收增长率（%）。",
+      "A": "澄清：请问要查询哪家公司？",
+      "SQL": "",
+      "image": ""
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G28" s="1" t="inlineStr"/>
+    </row>
+    <row r="29" ht="120" customHeight="1">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>B1028</t>
+        </is>
+      </c>
+      <c r="B29" s="1" t="inlineStr">
+        <is>
+          <t>数据统计分析查询</t>
+        </is>
+      </c>
+      <c r="C29" s="1" t="inlineStr">
+        <is>
+          <t>[{"Q": "对比白云山（600332）、云南白药（000538）、片仔癀（600436）2022-2025年第三季度的“净利润（万元）”，生成多系列折线图展示趋势。"}]</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="inlineStr">
+        <is>
+          <t>SELECT stock_abbr, report_year, report_period, net_profit FROM income_sheet WHERE (stock_abbr='白云山' OR stock_abbr='云南白药' OR stock_abbr='片仔癀' OR stock_code='600332' OR stock_code='000538' OR stock_code='600436') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END</t>
+        </is>
+      </c>
+      <c r="E29" s="1" t="inlineStr">
+        <is>
+          <t>line</t>
+        </is>
+      </c>
+      <c r="F29" s="1" t="inlineStr">
+        <is>
+          <t>{
+  "问题编号": "B1028",
+  "问题类型": "数据统计分析查询",
+  "子问题": [
+    {
+      "Q": "对比白云山（600332）、云南白药（000538）、片仔癀（600436）2022-2025年第三季度的“净利润（万元）”，生成多系列折线图展示趋势。",
+      "A": "白云山的净利润从2025三季报的 33.98 亿元 变化到2025三季报的 21.33 亿元（-37.22%）",
+      "SQL": "SELECT stock_abbr, report_year, report_period, net_profit FROM income_sheet WHERE (stock_abbr='白云山' OR stock_abbr='云南白药' OR stock_abbr='片仔癀' OR stock_code='600332' OR stock_code='000538' OR stock_code='600436') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
+      "image": "B1028_1.jpg"
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G29" s="1" t="inlineStr">
+        <is>
+          <t>B1028_1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="120" customHeight="1">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>B1029</t>
+        </is>
+      </c>
+      <c r="B30" s="1" t="inlineStr">
+        <is>
+          <t>数据基本查询</t>
+        </is>
+      </c>
+      <c r="C30" s="1" t="inlineStr">
+        <is>
+          <t>[{"Q": "2025年第三季度所有上市公司的股票代码、公司简称和营业总收入（单位：万元），按营业总收入从高到低排序。"}]</t>
+        </is>
+      </c>
+      <c r="D30" s="1" t="inlineStr">
+        <is>
+          <t>SELECT stock_abbr, report_year, report_period, total_operating_revenue FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY total_operating_revenue DESC LIMIT 10</t>
+        </is>
+      </c>
+      <c r="E30" s="1" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="F30" s="1" t="inlineStr">
+        <is>
+          <t>{
+  "问题编号": "B1029",
+  "问题类型": "数据基本查询",
+  "子问题": [
+    {
+      "Q": "2025年第三季度所有上市公司的股票代码、公司简称和营业总收入（单位：万元），按营业总收入从高到低排序。",
+      "A": "营业总收入 排名 Top5：1) 白云山 616.06 亿元; 2) 同仁堂 133.08 亿元; 3) 步长制药 84.69 亿元; 4) 太极集团 80.88 亿元; 5) 片仔癀 74.42 亿元",
+      "SQL": "SELECT stock_abbr, report_year, report_period, total_operating_revenue FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY total_operating_revenue DESC LIMIT 10",
+      "image": "B1029_1.jpg"
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G30" s="1" t="inlineStr">
+        <is>
+          <t>B1029_1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="120" customHeight="1">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>B1030</t>
+        </is>
+      </c>
+      <c r="B31" s="1" t="inlineStr">
+        <is>
+          <t>数据基本查询</t>
+        </is>
+      </c>
+      <c r="C31" s="1" t="inlineStr">
+        <is>
+          <t>[{"Q": "从资产负债表中提取片仔癀（600436）2022年全年的资产总额、负债总额、股东权益总额（单位：万元）"}]</t>
+        </is>
+      </c>
+      <c r="D31" s="1" t="inlineStr">
+        <is>
+          <t>SELECT stock_abbr, report_year, report_period, equity_total_equity FROM balance_sheet WHERE (stock_abbr='片仔癀' OR stock_code='600436') AND report_year IN (2022) AND report_period IN ('FY') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END</t>
+        </is>
+      </c>
+      <c r="E31" s="1" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="F31" s="1" t="inlineStr">
+        <is>
+          <t>{
+  "问题编号": "B1030",
+  "问题类型": "数据基本查询",
+  "子问题": [
+    {
+      "Q": "从资产负债表中提取片仔癀（600436）2022年全年的资产总额、负债总额、股东权益总额（单位：万元）",
+      "A": "片仔癀 2022年报的股东权益为 —",
+      "SQL": "SELECT stock_abbr, report_year, report_period, equity_total_equity FROM balance_sheet WHERE (stock_abbr='片仔癀' OR stock_code='600436') AND report_year IN (2022) AND report_period IN ('FY') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
+      "image": "B1030_1.jpg"
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G31" s="1" t="inlineStr">
+        <is>
+          <t>B1030_1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="120" customHeight="1">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>B1031</t>
+        </is>
+      </c>
+      <c r="B32" s="1" t="inlineStr">
+        <is>
+          <t>数据基本查询</t>
+        </is>
+      </c>
+      <c r="C32" s="1" t="inlineStr">
+        <is>
+          <t>[{"Q": "统计2025年第三季度净利润为负数的中药公司数量，并列出这些公司的股票代码和简称。"}]</t>
+        </is>
+      </c>
+      <c r="D32" s="1" t="inlineStr"/>
+      <c r="E32" s="1" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="F32" s="1" t="inlineStr">
+        <is>
+          <t>{
+  "问题编号": "B1031",
+  "问题类型": "数据基本查询",
+  "子问题": [
+    {
+      "Q": "统计2025年第三季度净利润为负数的中药公司数量，并列出这些公司的股票代码和简称。",
+      "A": "澄清：请问要查询哪家公司？",
+      "SQL": "",
+      "image": ""
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G32" s="1" t="inlineStr"/>
+    </row>
+    <row r="33" ht="120" customHeight="1">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>B1032</t>
+        </is>
+      </c>
+      <c r="B33" s="1" t="inlineStr">
+        <is>
+          <t>数据基本查询</t>
+        </is>
+      </c>
+      <c r="C33" s="1" t="inlineStr">
+        <is>
+          <t>[{"Q": "关联核心业绩指标表和利润表，查询2025年第三季度每家公司的股票代码、简称、营业总收入（取自核心业绩指标表）、销售毛利率（利润表中（营业收入-营业成本）/营业收入*100），保留两位小数。"}]</t>
+        </is>
+      </c>
+      <c r="D33" s="1" t="inlineStr">
+        <is>
+          <t>SELECT stock_abbr, report_year, report_period, total_operating_revenue FROM income_sheet WHERE (stock_code='000100') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END</t>
+        </is>
+      </c>
+      <c r="E33" s="1" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="F33" s="1" t="inlineStr">
+        <is>
+          <t>{
+  "问题编号": "B1032",
+  "问题类型": "数据基本查询",
+  "子问题": [
+    {
+      "Q": "关联核心业绩指标表和利润表，查询2025年第三季度每家公司的股票代码、简称、营业总收入（取自核心业绩指标表）、销售毛利率（利润表中（营业收入-营业成本）/营业收入*100），保留两位小数。",
+      "A": "未查询到数据",
+      "SQL": "SELECT stock_abbr, report_year, report_period, total_operating_revenue FROM income_sheet WHERE (stock_code='000100') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
+      "image": ""
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G33" s="1" t="inlineStr"/>
+    </row>
+    <row r="34" ht="120" customHeight="1">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>B1033</t>
+        </is>
+      </c>
+      <c r="B34" s="1" t="inlineStr">
+        <is>
+          <t>数据基本查询</t>
+        </is>
+      </c>
+      <c r="C34" s="1" t="inlineStr">
+        <is>
+          <t>[{"Q": "结合现金流量表和利润表，查询2024年全年所有公司的股票代码、简称、净利润（利润表）、经营性现金流量净额（现金流量表），筛选出经营性现金流量净额大于净利润的公司。"}]</t>
+        </is>
+      </c>
+      <c r="D34" s="1" t="inlineStr"/>
+      <c r="E34" s="1" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="F34" s="1" t="inlineStr">
+        <is>
+          <t>{
+  "问题编号": "B1033",
+  "问题类型": "数据基本查询",
+  "子问题": [
+    {
+      "Q": "结合现金流量表和利润表，查询2024年全年所有公司的股票代码、简称、净利润（利润表）、经营性现金流量净额（现金流量表），筛选出经营性现金流量净额大于净利润的公司。",
+      "A": "澄清：请问要查询哪家公司？",
+      "SQL": "",
+      "image": ""
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G34" s="1" t="inlineStr"/>
+    </row>
+    <row r="35" ht="120" customHeight="1">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>B1034</t>
+        </is>
+      </c>
+      <c r="B35" s="1" t="inlineStr">
+        <is>
+          <t>数据基本查询</t>
+        </is>
+      </c>
+      <c r="C35" s="1" t="inlineStr">
+        <is>
+          <t>[{"Q": "计算云南白药（000538）2025年第三季度营业总收入的环比增长率（环比增长率=(本季度值-上季度值)/上季度值*100），并展示2025年第二季度和第三季度的营业总收入（万元）及环比增长率（保留两位小数）。"}]</t>
+        </is>
+      </c>
+      <c r="D35" s="1" t="inlineStr">
+        <is>
+          <t>SELECT stock_abbr, report_year, report_period, total_operating_revenue FROM income_sheet WHERE (stock_abbr='云南白药' OR stock_code='000538' OR stock_code='000100') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END</t>
+        </is>
+      </c>
+      <c r="E35" s="1" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="F35" s="1" t="inlineStr">
+        <is>
+          <t>{
+  "问题编号": "B1034",
+  "问题类型": "数据基本查询",
+  "子问题": [
+    {
+      "Q": "计算云南白药（000538）2025年第三季度营业总收入的环比增长率（环比增长率=(本季度值-上季度值)/上季度值*100），并展示2025年第二季度和第三季度的营业总收入（万元）及环比增长率（保留两位小数）。",
+      "A": "云南白药 2025三季报的营业总收入为 —",
+      "SQL": "SELECT stock_abbr, report_year, report_period, total_operating_revenue FROM income_sheet WHERE (stock_abbr='云南白药' OR stock_code='000538' OR stock_code='000100') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
+      "image": "B1034_1.jpg"
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G35" s="1" t="inlineStr">
+        <is>
+          <t>B1034_1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="120" customHeight="1">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>B1035</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="inlineStr">
+        <is>
+          <t>数据基本查询</t>
+        </is>
+      </c>
+      <c r="C36" s="1" t="inlineStr">
+        <is>
+          <t>[{"Q": "统计2025年第三季度各公司净利润同比增长率（同比增长率=(2025Q3值-2024Q3值)/2024Q3值*100），找出同比增长率超过50%的公司，列出股票代码、简称和同比增长率"}]</t>
+        </is>
+      </c>
+      <c r="D36" s="1" t="inlineStr">
+        <is>
+          <t>SELECT stock_abbr, report_year, report_period, net_profit FROM income_sheet WHERE (stock_code='000100') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END</t>
+        </is>
+      </c>
+      <c r="E36" s="1" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="F36" s="1" t="inlineStr">
+        <is>
+          <t>{
+  "问题编号": "B1035",
+  "问题类型": "数据基本查询",
+  "子问题": [
+    {
+      "Q": "统计2025年第三季度各公司净利润同比增长率（同比增长率=(2025Q3值-2024Q3值)/2024Q3值*100），找出同比增长率超过50%的公司，列出股票代码、简称和同比增长率",
+      "A": "未查询到数据",
+      "SQL": "SELECT stock_abbr, report_year, report_period, net_profit FROM income_sheet WHERE (stock_code='000100') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
+      "image": ""
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G36" s="1" t="inlineStr"/>
+    </row>
+    <row r="37" ht="120" customHeight="1">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>B1036</t>
+        </is>
+      </c>
+      <c r="B37" s="1" t="inlineStr">
+        <is>
+          <t>数据基本查询</t>
+        </is>
+      </c>
+      <c r="C37" s="1" t="inlineStr">
+        <is>
+          <t>[{"Q": "计算2025年第三季度66家中药公司的资产负债率（负债总额/资产总额*100）行业均值，同时列出资产负债率最高的前10家公司的股票代码、简称和资产负债率（保留两位小数）。"}]</t>
+        </is>
+      </c>
+      <c r="D37" s="1" t="inlineStr">
+        <is>
+          <t>SELECT stock_abbr, report_year, report_period, asset_liability_ratio FROM balance_sheet WHERE (stock_code='000100') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY asset_liability_ratio DESC LIMIT 10</t>
+        </is>
+      </c>
+      <c r="E37" s="1" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="F37" s="1" t="inlineStr">
+        <is>
+          <t>{
+  "问题编号": "B1036",
+  "问题类型": "数据基本查询",
+  "子问题": [
+    {
+      "Q": "计算2025年第三季度66家中药公司的资产负债率（负债总额/资产总额*100）行业均值，同时列出资产负债率最高的前10家公司的股票代码、简称和资产负债率（保留两位小数）。",
+      "A": "未查询到数据",
+      "SQL": "SELECT stock_abbr, report_year, report_period, asset_liability_ratio FROM balance_sheet WHERE (stock_code='000100') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY asset_liability_ratio DESC LIMIT 10",
+      "image": ""
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G37" s="1" t="inlineStr"/>
+    </row>
+    <row r="38" ht="120" customHeight="1">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>B1037</t>
+        </is>
+      </c>
+      <c r="B38" s="1" t="inlineStr">
+        <is>
+          <t>数据基本查询</t>
+        </is>
+      </c>
+      <c r="C38" s="1" t="inlineStr">
+        <is>
+          <t>[{"Q": "按2025年第三季度的销售净利率（净利润/营业总收入*100）分组，统计销售净利率在0-5%、5%-10%、10%以上三个区间的公司数量。"}]</t>
+        </is>
+      </c>
+      <c r="D38" s="1" t="inlineStr">
+        <is>
+          <t>SELECT stock_abbr, report_year, report_period, net_profit FROM income_sheet WHERE (stock_code='000100') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END</t>
+        </is>
+      </c>
+      <c r="E38" s="1" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="F38" s="1" t="inlineStr">
+        <is>
+          <t>{
+  "问题编号": "B1037",
+  "问题类型": "数据基本查询",
+  "子问题": [
+    {
+      "Q": "按2025年第三季度的销售净利率（净利润/营业总收入*100）分组，统计销售净利率在0-5%、5%-10%、10%以上三个区间的公司数量。",
+      "A": "未查询到数据",
+      "SQL": "SELECT stock_abbr, report_year, report_period, net_profit FROM income_sheet WHERE (stock_code='000100') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
+      "image": ""
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G38" s="1" t="inlineStr"/>
+    </row>
+    <row r="39" ht="120" customHeight="1">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>B1038</t>
+        </is>
+      </c>
+      <c r="B39" s="1" t="inlineStr">
+        <is>
+          <t>数据基本查询</t>
+        </is>
+      </c>
+      <c r="C39" s="1" t="inlineStr">
+        <is>
+          <t>[{"Q": "查询2025年第三季度满足以下条件的公司：营业总收入超过10亿元（即100000万元）、资产负债率低于40%、经营性现金流量净额为正，列出股票代码、简称、营业总收入、资产负债率、经营性现金流量净额。"}]</t>
+        </is>
+      </c>
+      <c r="D39" s="1" t="inlineStr">
+        <is>
+          <t>SELECT stock_abbr, report_year, report_period, total_operating_revenue FROM income_sheet WHERE (stock_code='100000') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END</t>
+        </is>
+      </c>
+      <c r="E39" s="1" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="F39" s="1" t="inlineStr">
+        <is>
+          <t>{
+  "问题编号": "B1038",
+  "问题类型": "数据基本查询",
+  "子问题": [
+    {
+      "Q": "查询2025年第三季度满足以下条件的公司：营业总收入超过10亿元（即100000万元）、资产负债率低于40%、经营性现金流量净额为正，列出股票代码、简称、营业总收入、资产负债率、经营性现金流量净额。",
+      "A": "未查询到数据",
+      "SQL": "SELECT stock_abbr, report_year, report_period, total_operating_revenue FROM income_sheet WHERE (stock_code='100000') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
+      "image": ""
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G39" s="1" t="inlineStr"/>
+    </row>
+    <row r="40" ht="120" customHeight="1">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>B1039</t>
+        </is>
+      </c>
+      <c r="B40" s="1" t="inlineStr">
+        <is>
+          <t>数据基本查询</t>
+        </is>
+      </c>
+      <c r="C40" s="1" t="inlineStr">
+        <is>
+          <t>[{"Q": "找出2022-2025年第三季度期间，连续四个报告期扣非净利润均超过1亿元的公司，列出股票代码、简称及各报告期的扣非净利润（万元）"}]</t>
+        </is>
+      </c>
+      <c r="D40" s="1" t="inlineStr"/>
+      <c r="E40" s="1" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="F40" s="1" t="inlineStr">
+        <is>
+          <t>{
+  "问题编号": "B1039",
+  "问题类型": "数据基本查询",
+  "子问题": [
+    {
+      "Q": "找出2022-2025年第三季度期间，连续四个报告期扣非净利润均超过1亿元的公司，列出股票代码、简称及各报告期的扣非净利润（万元）",
+      "A": "澄清：请问要查询哪家公司？",
+      "SQL": "",
+      "image": ""
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G40" s="1" t="inlineStr"/>
+    </row>
+    <row r="41" ht="120" customHeight="1">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>B1040</t>
+        </is>
+      </c>
+      <c r="B41" s="1" t="inlineStr">
+        <is>
+          <t>数据基本查询</t>
+        </is>
+      </c>
+      <c r="C41" s="1" t="inlineStr">
+        <is>
+          <t>[{"Q": "关联资产负债表和现金流量表，查询2025年第三季度货币资金占总资产比例超过20%，且投资性现金流量净额为负数的公司，按货币资金占比从高到低排序。"}]</t>
+        </is>
+      </c>
+      <c r="D41" s="1" t="inlineStr">
+        <is>
+          <t>SELECT stock_abbr, report_year, report_period, asset_total_assets FROM balance_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY asset_total_assets DESC LIMIT 10</t>
+        </is>
+      </c>
+      <c r="E41" s="1" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="F41" s="1" t="inlineStr">
+        <is>
+          <t>{
+  "问题编号": "B1040",
+  "问题类型": "数据基本查询",
+  "子问题": [
+    {
+      "Q": "关联资产负债表和现金流量表，查询2025年第三季度货币资金占总资产比例超过20%，且投资性现金流量净额为负数的公司，按货币资金占比从高到低排序。",
+      "A": "总资产 排名 Top5：1) 白云山 831.69 亿元; 2) 华润三九 565.64 亿元; 3) 云南白药 533.43 亿元; 4) 同仁堂 318.19 亿元; 5) 步长制药 195.70 亿元",
+      "SQL": "SELECT stock_abbr, report_year, report_period, asset_total_assets FROM balance_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY asset_total_assets DESC LIMIT 10",
+      "image": "B1040_1.jpg"
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G41" s="1" t="inlineStr">
+        <is>
+          <t>B1040_1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="120" customHeight="1">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>B1041</t>
+        </is>
+      </c>
+      <c r="B42" s="1" t="inlineStr">
+        <is>
+          <t>数据基本查询</t>
+        </is>
+      </c>
+      <c r="C42" s="1" t="inlineStr">
+        <is>
+          <t>[{"Q": "检查2025年第三季度核心业绩指标表中的“营业总收入”与利润表中的“营业收入”数值不一致的公司，列出股票代码、两个表中的数值及差值（绝对值）。"}]</t>
+        </is>
+      </c>
+      <c r="D42" s="1" t="inlineStr"/>
+      <c r="E42" s="1" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="F42" s="1" t="inlineStr">
+        <is>
+          <t>{
+  "问题编号": "B1041",
+  "问题类型": "数据基本查询",
+  "子问题": [
+    {
+      "Q": "检查2025年第三季度核心业绩指标表中的“营业总收入”与利润表中的“营业收入”数值不一致的公司，列出股票代码、两个表中的数值及差值（绝对值）。",
+      "A": "澄清：请问要查询哪家公司？",
+      "SQL": "",
+      "image": ""
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G42" s="1" t="inlineStr"/>
+    </row>
+    <row r="43" ht="120" customHeight="1">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>B1042</t>
+        </is>
+      </c>
+      <c r="B43" s="1" t="inlineStr">
+        <is>
+          <t>数据基本查询</t>
+        </is>
+      </c>
+      <c r="C43" s="1" t="inlineStr">
+        <is>
+          <t>[{"Q": "统计2025年第三季度研发费用占营业总收入比例最高的5家公司，要求同时展示研发费用（万元）、营业总收入（万元）、研发费用占比（保留两位小数）"}]</t>
+        </is>
+      </c>
+      <c r="D43" s="1" t="inlineStr">
+        <is>
+          <t>SELECT stock_abbr, report_year, report_period, total_operating_revenue FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY total_operating_revenue DESC LIMIT 10</t>
+        </is>
+      </c>
+      <c r="E43" s="1" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="F43" s="1" t="inlineStr">
+        <is>
+          <t>{
+  "问题编号": "B1042",
+  "问题类型": "数据基本查询",
+  "子问题": [
+    {
+      "Q": "统计2025年第三季度研发费用占营业总收入比例最高的5家公司，要求同时展示研发费用（万元）、营业总收入（万元）、研发费用占比（保留两位小数）",
+      "A": "营业总收入 排名 Top5：1) 白云山 616.06 亿元; 2) 同仁堂 133.08 亿元; 3) 步长制药 84.69 亿元; 4) 太极集团 80.88 亿元; 5) 片仔癀 74.42 亿元",
+      "SQL": "SELECT stock_abbr, report_year, report_period, total_operating_revenue FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY total_operating_revenue DESC LIMIT 10",
+      "image": "B1042_1.jpg"
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G43" s="1" t="inlineStr">
+        <is>
+          <t>B1042_1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="120" customHeight="1">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>B1043</t>
+        </is>
+      </c>
+      <c r="B44" s="1" t="inlineStr">
+        <is>
+          <t>数据基本查询</t>
+        </is>
+      </c>
+      <c r="C44" s="1" t="inlineStr">
+        <is>
+          <t>[{"Q": "计算2025年第三季度66家公司的净利润中位数，找出净利润高于中位数且销售毛利率低于行业均值的公司，列出股票代码、简称、净利润、销售毛利率。"}]</t>
+        </is>
+      </c>
+      <c r="D44" s="1" t="inlineStr"/>
+      <c r="E44" s="1" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="F44" s="1" t="inlineStr">
+        <is>
+          <t>{
+  "问题编号": "B1043",
+  "问题类型": "数据基本查询",
+  "子问题": [
+    {
+      "Q": "计算2025年第三季度66家公司的净利润中位数，找出净利润高于中位数且销售毛利率低于行业均值的公司，列出股票代码、简称、净利润、销售毛利率。",
+      "A": "澄清：请问要查询哪家公司？",
+      "SQL": "",
+      "image": ""
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G44" s="1" t="inlineStr"/>
+    </row>
+    <row r="45" ht="120" customHeight="1">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>B1044</t>
+        </is>
+      </c>
+      <c r="B45" s="1" t="inlineStr">
+        <is>
+          <t>数据基本查询</t>
+        </is>
+      </c>
+      <c r="C45" s="1" t="inlineStr">
+        <is>
+          <t>[{"Q": "2025年第三季度营业总收入排名前五的中药公司有哪些？"}, {"Q": "这五家公司的净利润分别是多少"}, {"Q": "它们的净利润同比增长率和行业均值相比如何"}]</t>
+        </is>
+      </c>
+      <c r="D45" s="1" t="inlineStr">
+        <is>
+          <t>SELECT stock_abbr, report_year, report_period, total_operating_revenue FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END</t>
+        </is>
+      </c>
+      <c r="E45" s="1" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="F45" s="1" t="inlineStr">
+        <is>
+          <t>{
+  "问题编号": "B1044",
+  "问题类型": "数据基本查询",
+  "子问题": [
+    {
+      "Q": "2025年第三季度营业总收入排名前五的中药公司有哪些？",
+      "A": "营业总收入 排名 Top5：1) 白云山 616.06 亿元; 2) 同仁堂 133.08 亿元; 3) 步长制药 84.69 亿元; 4) 太极集团 80.88 亿元; 5) 片仔癀 74.42 亿元",
+      "SQL": "SELECT stock_abbr, report_year, report_period, total_operating_revenue FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY total_operating_revenue DESC LIMIT 10",
+      "image": "B1044_1.jpg"
+    },
+    {
+      "Q": "这五家公司的净利润分别是多少",
+      "A": "澄清：请问要查询哪家公司？",
+      "SQL": "",
+      "image": ""
+    },
+    {
+      "Q": "它们的净利润同比增长率和行业均值相比如何",
+      "A": "金花股份的营业总收入从2025三季报的 3.84 亿元 变化到2025三季报的 12.53 亿元（+226.46%）",
+      "SQL": "SELECT stock_abbr, report_year, report_period, total_operating_revenue FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
+      "image": "B1044_3.jpg"
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G45" s="1" t="inlineStr">
+        <is>
+          <t>B1044_3.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="120" customHeight="1">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>B1045</t>
+        </is>
+      </c>
+      <c r="B46" s="1" t="inlineStr">
+        <is>
+          <t>数据基本查询</t>
+        </is>
+      </c>
+      <c r="C46" s="1" t="inlineStr">
+        <is>
+          <t>[{"Q": "云南白药2022-2025年第三季度的资产负债率变化趋势"}, {"Q": "这个趋势和白云山的同期变化趋势对比，差异在哪里"}, {"Q": "导致两者差异的核心财务指标（如负债总额、资产总额）变化是什么"}]</t>
+        </is>
+      </c>
+      <c r="D46" s="1" t="inlineStr">
+        <is>
+          <t>SELECT stock_abbr, report_year, report_period, asset_liability_ratio FROM balance_sheet WHERE (stock_abbr='云南白药' OR stock_abbr='白云山') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END</t>
+        </is>
+      </c>
+      <c r="E46" s="1" t="inlineStr">
+        <is>
+          <t>line</t>
+        </is>
+      </c>
+      <c r="F46" s="1" t="inlineStr">
+        <is>
+          <t>{
+  "问题编号": "B1045",
+  "问题类型": "数据基本查询",
+  "子问题": [
+    {
+      "Q": "云南白药2022-2025年第三季度的资产负债率变化趋势",
+      "A": "未查询到有效数据",
+      "SQL": "SELECT stock_abbr, report_year, report_period, asset_liability_ratio FROM balance_sheet WHERE (stock_abbr='云南白药') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
+      "image": "B1045_1.jpg"
+    },
+    {
+      "Q": "这个趋势和白云山的同期变化趋势对比，差异在哪里",
+      "A": "未查询到有效数据",
+      "SQL": "SELECT stock_abbr, report_year, report_period, asset_liability_ratio FROM balance_sheet WHERE (stock_abbr='云南白药' OR stock_abbr='白云山') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
+      "image": "B1045_2.jpg"
+    },
+    {
+      "Q": "导致两者差异的核心财务指标（如负债总额、资产总额）变化是什么",
+      "A": "未查询到有效数据",
+      "SQL": "SELECT stock_abbr, report_year, report_period, asset_liability_ratio FROM balance_sheet WHERE (stock_abbr='云南白药' OR stock_abbr='白云山') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
+      "image": "B1045_3.jpg"
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G46" s="1" t="inlineStr">
+        <is>
+          <t>B1045_3.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="120" customHeight="1">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>B1046</t>
+        </is>
+      </c>
+      <c r="B47" s="1" t="inlineStr">
+        <is>
+          <t>数据基本查询</t>
+        </is>
+      </c>
+      <c r="C47" s="1" t="inlineStr">
+        <is>
+          <t>[{"Q": "2025年第三季度经营性现金流量净额为负的公司有多少家"}, {"Q": "这些公司中，资产负债率超过60%的有几家"}]</t>
+        </is>
+      </c>
+      <c r="D47" s="1" t="inlineStr"/>
+      <c r="E47" s="1" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="F47" s="1" t="inlineStr">
+        <is>
+          <t>{
+  "问题编号": "B1046",
+  "问题类型": "数据基本查询",
+  "子问题": [
+    {
+      "Q": "2025年第三季度经营性现金流量净额为负的公司有多少家",
+      "A": "澄清：请问要查询哪家公司？",
+      "SQL": "",
+      "image": ""
+    },
+    {
+      "Q": "这些公司中，资产负债率超过60%的有几家",
+      "A": "澄清：请问要查询哪家公司？",
+      "SQL": "",
+      "image": ""
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G47" s="1" t="inlineStr"/>
+    </row>
+    <row r="48" ht="120" customHeight="1">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>B1047</t>
+        </is>
+      </c>
+      <c r="B48" s="1" t="inlineStr">
+        <is>
+          <t>数据基本查询</t>
+        </is>
+      </c>
+      <c r="C48" s="1" t="inlineStr">
+        <is>
+          <t>[{"Q": "2025年第三季度研发费用占比前十的中药公司"}, {"Q": "这些公司的销售毛利率在利润表中表现如何"}]</t>
+        </is>
+      </c>
+      <c r="D48" s="1" t="inlineStr">
+        <is>
+          <t>SELECT stock_abbr, report_year, report_period, operating_expense_rnd_expenses FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY operating_expense_rnd_expenses DESC LIMIT 10</t>
+        </is>
+      </c>
+      <c r="E48" s="1" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="F48" s="1" t="inlineStr">
+        <is>
+          <t>{
+  "问题编号": "B1047",
+  "问题类型": "数据基本查询",
+  "子问题": [
+    {
+      "Q": "2025年第三季度研发费用占比前十的中药公司",
+      "A": "研发费用 排名 Top5：1) 天士力 5.53 亿元; 2) 白云山 4.44 亿元; 3) 康缘药业 3.52 亿元; 4) 济川药业 2.72 亿元; 5) 太极集团 1.95 亿元",
+      "SQL": "SELECT stock_abbr, report_year, report_period, operating_expense_rnd_expenses FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY operating_expense_rnd_expenses DESC LIMIT 10",
+      "image": "B1047_1.jpg"
+    },
+    {
+      "Q": "这些公司的销售毛利率在利润表中表现如何",
+      "A": "澄清：请问要查询哪家公司？",
+      "SQL": "",
+      "image": ""
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G48" s="1" t="inlineStr">
+        <is>
+          <t>B1047_1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="120" customHeight="1">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>B1048</t>
+        </is>
+      </c>
+      <c r="B49" s="1" t="inlineStr">
+        <is>
+          <t>数据基本查询</t>
+        </is>
+      </c>
+      <c r="C49" s="1" t="inlineStr">
+        <is>
+          <t>[{"Q": "2024年第三季度净利润排名前三的公司？"}, {"Q": "这些公司2025年第三季度的净利润排名有没有变化？"}, {"Q": "排名变化最大的公司，其营业总收入的变化幅度是多少？"}]</t>
+        </is>
+      </c>
+      <c r="D49" s="1" t="inlineStr">
+        <is>
+          <t>SELECT stock_abbr, report_year, report_period, net_profit FROM income_sheet WHERE report_year IN (2024) AND report_period IN ('Q3') ORDER BY net_profit DESC LIMIT 10</t>
+        </is>
+      </c>
+      <c r="E49" s="1" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="F49" s="1" t="inlineStr">
+        <is>
+          <t>{
+  "问题编号": "B1048",
+  "问题类型": "数据基本查询",
+  "子问题": [
+    {
+      "Q": "2024年第三季度净利润排名前三的公司？",
+      "A": "净利润 排名 Top5：1) 白云山 32.89 亿元; 2) 片仔癀 27.18 亿元; 3) 同仁堂 19.84 亿元; 4) 济川药业 19.07 亿元; 5) 天士力 8.28 亿元",
+      "SQL": "SELECT stock_abbr, report_year, report_period, net_profit FROM income_sheet WHERE report_year IN (2024) AND report_period IN ('Q3') ORDER BY net_profit DESC LIMIT 10",
+      "image": "B1048_1.jpg"
+    },
+    {
+      "Q": "这些公司2025年第三季度的净利润排名有没有变化？",
+      "A": "澄清：请问要分析哪家公司的趋势？",
+      "SQL": "",
+      "image": ""
+    },
+    {
+      "Q": "排名变化最大的公司，其营业总收入的变化幅度是多少？",
+      "A": "澄清：请问要分析哪家公司的趋势？",
+      "SQL": "",
+      "image": ""
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G49" s="1" t="inlineStr">
+        <is>
+          <t>B1048_1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="120" customHeight="1">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>B1049</t>
+        </is>
+      </c>
+      <c r="B50" s="1" t="inlineStr">
+        <is>
+          <t>数据统计分析查询</t>
+        </is>
+      </c>
+      <c r="C50" s="1" t="inlineStr">
+        <is>
+          <t>[{"Q": "查询2025年第三季度66家中药公司营业总收入排名前十的公司，用条形图展示排名"}]</t>
+        </is>
+      </c>
+      <c r="D50" s="1" t="inlineStr">
+        <is>
+          <t>SELECT stock_abbr, report_year, report_period, total_operating_revenue FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY total_operating_revenue DESC LIMIT 10</t>
+        </is>
+      </c>
+      <c r="E50" s="1" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="F50" s="1" t="inlineStr">
+        <is>
+          <t>{
+  "问题编号": "B1049",
+  "问题类型": "数据统计分析查询",
+  "子问题": [
+    {
+      "Q": "查询2025年第三季度66家中药公司营业总收入排名前十的公司，用条形图展示排名",
+      "A": "营业总收入 排名 Top5：1) 白云山 616.06 亿元; 2) 同仁堂 133.08 亿元; 3) 步长制药 84.69 亿元; 4) 太极集团 80.88 亿元; 5) 片仔癀 74.42 亿元",
+      "SQL": "SELECT stock_abbr, report_year, report_period, total_operating_revenue FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY total_operating_revenue DESC LIMIT 10",
+      "image": "B1049_1.jpg"
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G50" s="1" t="inlineStr">
+        <is>
+          <t>B1049_1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="120" customHeight="1">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>B1050</t>
+        </is>
+      </c>
+      <c r="B51" s="1" t="inlineStr">
+        <is>
+          <t>数据统计分析查询</t>
+        </is>
+      </c>
+      <c r="C51" s="1" t="inlineStr">
+        <is>
+          <t>[{"Q": "分析云南白药2022-2025年第三季度净利润的变化趋势，用折线图展示"}]</t>
+        </is>
+      </c>
+      <c r="D51" s="1" t="inlineStr">
+        <is>
+          <t>SELECT stock_abbr, report_year, report_period, net_profit FROM income_sheet WHERE (stock_abbr='云南白药') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END</t>
+        </is>
+      </c>
+      <c r="E51" s="1" t="inlineStr">
+        <is>
+          <t>line</t>
+        </is>
+      </c>
+      <c r="F51" s="1" t="inlineStr">
+        <is>
+          <t>{
+  "问题编号": "B1050",
+  "问题类型": "数据统计分析查询",
+  "子问题": [
+    {
+      "Q": "分析云南白药2022-2025年第三季度净利润的变化趋势，用折线图展示",
+      "A": "未查询到有效数据",
+      "SQL": "SELECT stock_abbr, report_year, report_period, net_profit FROM income_sheet WHERE (stock_abbr='云南白药') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
+      "image": "B1050_1.jpg"
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G51" s="1" t="inlineStr">
+        <is>
+          <t>B1050_1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="120" customHeight="1">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>B1051</t>
+        </is>
+      </c>
+      <c r="B52" s="1" t="inlineStr">
+        <is>
+          <t>数据统计分析查询</t>
+        </is>
+      </c>
+      <c r="C52" s="1" t="inlineStr">
+        <is>
+          <t>[{"Q": "对比白云山、云南白药、片仔癀2025年第三季度的核心盈利能力指标（销售毛利率、销售净利率、ROE），用雷达图展示差异"}]</t>
+        </is>
+      </c>
+      <c r="D52" s="1" t="inlineStr">
+        <is>
+          <t>SELECT stock_abbr, report_year, report_period, roe FROM core_performance_indicators_sheet WHERE (stock_abbr='白云山' OR stock_abbr='云南白药' OR stock_abbr='片仔癀') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END</t>
+        </is>
+      </c>
+      <c r="E52" s="1" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="F52" s="1" t="inlineStr">
+        <is>
+          <t>{
+  "问题编号": "B1051",
+  "问题类型": "数据统计分析查询",
+  "子问题": [
+    {
+      "Q": "对比白云山、云南白药、片仔癀2025年第三季度的核心盈利能力指标（销售毛利率、销售净利率、ROE），用雷达图展示差异",
+      "A": "ROE 对比：云南白药 2025三季报 —; 白云山 2025三季报 —; 片仔癀 2025三季报 4.68%",
+      "SQL": "SELECT stock_abbr, report_year, report_period, roe FROM core_performance_indicators_sheet WHERE (stock_abbr='白云山' OR stock_abbr='云南白药' OR stock_abbr='片仔癀') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
+      "image": "B1051_1.jpg"
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G52" s="1" t="inlineStr">
+        <is>
+          <t>B1051_1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="120" customHeight="1">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>B1052</t>
+        </is>
+      </c>
+      <c r="B53" s="1" t="inlineStr">
+        <is>
+          <t>数据统计分析查询</t>
+        </is>
+      </c>
+      <c r="C53" s="1" t="inlineStr">
+        <is>
+          <t>[{"Q": "统计2025年第三季度中药公司资产负债率的分布情况（按0-30%、30%-50%、50%-70%、70%以上分组），用饼图展示各组公司数量占比"}]</t>
+        </is>
+      </c>
+      <c r="D53" s="1" t="inlineStr"/>
+      <c r="E53" s="1" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="F53" s="1" t="inlineStr">
+        <is>
+          <t>{
+  "问题编号": "B1052",
+  "问题类型": "数据统计分析查询",
+  "子问题": [
+    {
+      "Q": "统计2025年第三季度中药公司资产负债率的分布情况（按0-30%、30%-50%、50%-70%、70%以上分组），用饼图展示各组公司数量占比",
+      "A": "澄清：请问要查询哪家公司？",
+      "SQL": "",
+      "image": ""
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G53" s="1" t="inlineStr"/>
+    </row>
+    <row r="54" ht="120" customHeight="1">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>B1053</t>
+        </is>
+      </c>
+      <c r="B54" s="1" t="inlineStr">
+        <is>
+          <t>数据统计分析查询</t>
+        </is>
+      </c>
+      <c r="C54" s="1" t="inlineStr">
+        <is>
+          <t>[{"Q": "查询2025年第三季度经营性现金流量净额与净利润的比值分布，用直方图展示"}]</t>
+        </is>
+      </c>
+      <c r="D54" s="1" t="inlineStr"/>
+      <c r="E54" s="1" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="F54" s="1" t="inlineStr">
+        <is>
+          <t>{
+  "问题编号": "B1053",
+  "问题类型": "数据统计分析查询",
+  "子问题": [
+    {
+      "Q": "查询2025年第三季度经营性现金流量净额与净利润的比值分布，用直方图展示",
+      "A": "澄清：请问要查询哪家公司？",
+      "SQL": "",
+      "image": ""
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G54" s="1" t="inlineStr"/>
+    </row>
+    <row r="55" ht="120" customHeight="1">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>B1054</t>
+        </is>
+      </c>
+      <c r="B55" s="1" t="inlineStr">
+        <is>
+          <t>数据统计分析查询</t>
+        </is>
+      </c>
+      <c r="C55" s="1" t="inlineStr">
+        <is>
+          <t>[{"Q": "分析2022-2025年第三季度中药行业平均研发费用占比的变化趋势，用折线图展示"}]</t>
+        </is>
+      </c>
+      <c r="D55" s="1" t="inlineStr"/>
+      <c r="E55" s="1" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="F55" s="1" t="inlineStr">
+        <is>
+          <t>{
+  "问题编号": "B1054",
+  "问题类型": "数据统计分析查询",
+  "子问题": [
+    {
+      "Q": "分析2022-2025年第三季度中药行业平均研发费用占比的变化趋势，用折线图展示",
+      "A": "澄清：请问要分析哪家公司的趋势？",
+      "SQL": "",
+      "image": ""
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G55" s="1" t="inlineStr"/>
+    </row>
+    <row r="56" ht="120" customHeight="1">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>B1055</t>
+        </is>
+      </c>
+      <c r="B56" s="1" t="inlineStr">
+        <is>
+          <t>数据统计分析查询</t>
+        </is>
+      </c>
+      <c r="C56" s="1" t="inlineStr">
+        <is>
+          <t>[{"Q": "对比2024年和2025年第三季度净利润同比增长率前十公司的名单变化，用双条形图展示两年排名及增长率"}]</t>
+        </is>
+      </c>
+      <c r="D56" s="1" t="inlineStr"/>
+      <c r="E56" s="1" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="F56" s="1" t="inlineStr">
+        <is>
+          <t>{
+  "问题编号": "B1055",
+  "问题类型": "数据统计分析查询",
+  "子问题": [
+    {
+      "Q": "对比2024年和2025年第三季度净利润同比增长率前十公司的名单变化，用双条形图展示两年排名及增长率",
+      "A": "澄清：请问要分析哪家公司的趋势？",
+      "SQL": "",
+      "image": ""
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G56" s="1" t="inlineStr"/>
+    </row>
+    <row r="57" ht="120" customHeight="1">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>B1056</t>
+        </is>
+      </c>
+      <c r="B57" s="1" t="inlineStr">
+        <is>
+          <t>数据统计分析查询</t>
+        </is>
+      </c>
+      <c r="C57" s="1" t="inlineStr">
+        <is>
+          <t>[{"Q": "查询2025年第三季度存货周转率最高的五家公司，用条形图展示其周转率数值"}]</t>
+        </is>
+      </c>
+      <c r="D57" s="1" t="inlineStr">
+        <is>
+          <t>SELECT stock_abbr, report_year, report_period, asset_inventory FROM balance_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY asset_inventory DESC LIMIT 10</t>
+        </is>
+      </c>
+      <c r="E57" s="1" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="F57" s="1" t="inlineStr">
+        <is>
+          <t>{
+  "问题编号": "B1056",
+  "问题类型": "数据统计分析查询",
+  "子问题": [
+    {
+      "Q": "查询2025年第三季度存货周转率最高的五家公司，用条形图展示其周转率数值",
+      "A": "存货 排名 Top5：1) 同仁堂 111.25 亿元; 2) 白云山 110.81 亿元; 3) 华润三九 63.87 亿元; 4) 片仔癀 61.60 亿元; 5) 云南白药 57.77 亿元",
+      "SQL": "SELECT stock_abbr, report_year, report_period, asset_inventory FROM balance_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY asset_inventory DESC LIMIT 10",
+      "image": "B1056_1.jpg"
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G57" s="1" t="inlineStr">
+        <is>
+          <t>B1056_1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="120" customHeight="1">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>B1057</t>
+        </is>
+      </c>
+      <c r="B58" s="1" t="inlineStr">
+        <is>
+          <t>数据统计分析查询</t>
+        </is>
+      </c>
+      <c r="C58" s="1" t="inlineStr">
+        <is>
+          <t>[{"Q": "分析2025年第三季度营业总收入与净利润的相关性，用散点图展示"}]</t>
+        </is>
+      </c>
+      <c r="D58" s="1" t="inlineStr"/>
+      <c r="E58" s="1" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="F58" s="1" t="inlineStr">
+        <is>
+          <t>{
+  "问题编号": "B1057",
+  "问题类型": "数据统计分析查询",
+  "子问题": [
+    {
+      "Q": "分析2025年第三季度营业总收入与净利润的相关性，用散点图展示",
+      "A": "澄清：请问要查询哪家公司？",
+      "SQL": "",
+      "image": ""
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G58" s="1" t="inlineStr"/>
+    </row>
+    <row r="59" ht="120" customHeight="1">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
+          <t>B1058</t>
+        </is>
+      </c>
+      <c r="B59" s="1" t="inlineStr">
+        <is>
+          <t>数据统计分析查询</t>
+        </is>
+      </c>
+      <c r="C59" s="1" t="inlineStr">
+        <is>
+          <t>[{"Q": "查询2025年第三季度短期借款超过货币资金的公司，用表格列出具体数据，并用柱状图对比这两项指标的差额"}]</t>
+        </is>
+      </c>
+      <c r="D59" s="1" t="inlineStr">
+        <is>
+          <t>SELECT stock_abbr, report_year, report_period, asset_cash_and_cash_equivalents FROM balance_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END</t>
+        </is>
+      </c>
+      <c r="E59" s="1" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="F59" s="1" t="inlineStr">
+        <is>
+          <t>{
+  "问题编号": "B1058",
+  "问题类型": "数据统计分析查询",
+  "子问题": [
+    {
+      "Q": "查询2025年第三季度短期借款超过货币资金的公司，用表格列出具体数据，并用柱状图对比这两项指标的差额",
+      "A": "货币资金 对比：贵州百灵 2025三季报 1.82 亿元; 东阿阿胶 2025三季报 55.62 亿元; 云南白药 2025三季报 86.18 亿元; 启迪药业 2025三季报 1.56 亿元; 仁和药业 2025三季报 10.95 亿元; 通化金马 2025三季报 3.22 亿元; 华神科技 2025三季报 1.49 亿元; 九芝堂 2025三季报 3.02 亿元; 华润三九 2025三季报 56.23 亿元; 万邦德 2025三季报 8,307.08 万元; 沃华医药 2025三季报 3.93 亿元; 莱茵生物 2025三季报 2.55 亿元; 嘉应制药 2025三季报 1.28 亿元; 新里程 2025三季报 3.08 亿元; 桂林三金 2025三季报 10.78 亿元; 奇正藏药 2025三季报 2.84 亿元; 众生药业 2025三季报 9.32 亿元; 精华制药 2025三季报 7.24 亿元; 信邦制药 2025三季报 9.62 亿元; 益盛药业 2025三季报 1.16 亿元; 瑞康医药 2025三季报 42.41 亿元; 以岭药业 2025三季报 10.34 亿元; 特一药业 2025三季报 2.15 亿元; 葵花药业 2025三季报 6.85 亿元; 康弘药业 2025三季报 38.28 亿元; 盘龙药业 2025三季报 11.65 亿元; 新天药业 2025三季报 1.69 亿元; 华森制药 2025三季报 3.03 亿元; 红日药业 2025三季报 14.14 亿元; 振东制药 2025三季报 2.90 亿元; 佐力药业 2025三季报 6.93 亿元; 新光药业 2025三季报 2.91 亿元; 陇神戎发 2025三季报 —; 康泰医学 2025三季报 7.78 亿元; 维康药业 2025三季报 —; 粤万年青 2025三季报 1.42 亿元; 恩威医药 2025三季报 3.20 亿元; 金花股份 2025三季报 2.35 亿元; 同仁堂 2025三季报 109.10 亿元; 太极集团 2025三季报 5.78 亿元; 太龙药业 2025三季报 3.44 亿元; 中恒集团 2025三季报 40.57 亿元; 羚锐制药 2025三季报 4.60 亿元; 达仁堂 2025三季报 10.49 亿元; 白云山 2025三季报 137.08 亿元; 亚宝药业 2025三季报 6.45 亿元; 昆药集团 2025三季报 7.94 亿元; 片仔癀 2025三季报 13.47 亿元; 千金药业 2025三季报 5.65 亿元; 康美药业 2025三季报 11.81 亿元; 天士力 2025三季报 26.03 亿元; 康缘药业 2025三季报 21.57 亿元; 济川药业 2025三季报 51.30 亿元; 康恩贝 2025三季报 8.36 亿元; 益佰制药 2025三季报 5.94 亿元; 神奇制药 2025三季报 6.11 亿元; 天目药业 2025三季报 1,174.03 万元; 江中药业 2025三季报 19.99 亿元; 广誉远 2025三季报 2.96 亿元; 健民集团 2025三季报 1.75 亿元; 马应龙 2025三季报 15.41 亿元; 康惠制药 2025三季报 7,849.49 万元; 贵州三力 2025三季报 2.66 亿元; 珍宝岛 2025三季报 2.04 亿元; 步长制药 2025三季报 8.86 亿元; 寿仙谷 2025三季报 6.97 亿元; 方盛制药 2025三季报 1.80 亿元",
+      "SQL": "SELECT stock_abbr, report_year, report_period, asset_cash_and_cash_equivalents FROM balance_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
+      "image": "B1058_1.jpg"
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G59" s="1" t="inlineStr">
+        <is>
+          <t>B1058_1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="120" customHeight="1">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
+          <t>B1059</t>
+        </is>
+      </c>
+      <c r="B60" s="1" t="inlineStr">
+        <is>
+          <t>数据统计分析查询</t>
+        </is>
+      </c>
+      <c r="C60" s="1" t="inlineStr">
+        <is>
+          <t>[{"Q": "分析片仔癀2022-2025年第三季度扣非净利润占净利润的比例变化，用折线图展示"}]</t>
+        </is>
+      </c>
+      <c r="D60" s="1" t="inlineStr">
+        <is>
+          <t>SELECT stock_abbr, report_year, report_period, net_profit FROM income_sheet WHERE (stock_abbr='片仔癀') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END</t>
+        </is>
+      </c>
+      <c r="E60" s="1" t="inlineStr">
+        <is>
+          <t>line</t>
+        </is>
+      </c>
+      <c r="F60" s="1" t="inlineStr">
+        <is>
+          <t>{
+  "问题编号": "B1059",
+  "问题类型": "数据统计分析查询",
+  "子问题": [
+    {
+      "Q": "分析片仔癀2022-2025年第三季度扣非净利润占净利润的比例变化，用折线图展示",
+      "A": "片仔癀 2025三季报 的净利润为 21.33 亿元（仅有效值）",
+      "SQL": "SELECT stock_abbr, report_year, report_period, net_profit FROM income_sheet WHERE (stock_abbr='片仔癀') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
+      "image": "B1059_1.jpg"
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G60" s="1" t="inlineStr">
+        <is>
+          <t>B1059_1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="120" customHeight="1">
+      <c r="A61" s="1" t="inlineStr">
+        <is>
+          <t>B1060</t>
+        </is>
+      </c>
+      <c r="B61" s="1" t="inlineStr">
+        <is>
+          <t>数据统计分析查询</t>
+        </is>
+      </c>
+      <c r="C61" s="1" t="inlineStr">
+        <is>
+          <t>[{"Q": "对比2025年第三季度研发费用占比前十与后十公司的净利润同比增长率，用箱线图展示两组数据的分布差异"}]</t>
+        </is>
+      </c>
+      <c r="D61" s="1" t="inlineStr">
+        <is>
+          <t>SELECT stock_abbr, report_year, report_period, net_profit FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY net_profit DESC LIMIT 10</t>
+        </is>
+      </c>
+      <c r="E61" s="1" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="F61" s="1" t="inlineStr">
+        <is>
+          <t>{
+  "问题编号": "B1060",
+  "问题类型": "数据统计分析查询",
+  "子问题": [
+    {
+      "Q": "对比2025年第三季度研发费用占比前十与后十公司的净利润同比增长率，用箱线图展示两组数据的分布差异",
+      "A": "净利润 排名 Top5：1) 白云山 33.98 亿元; 2) 达仁堂 21.46 亿元; 3) 片仔癀 21.33 亿元; 4) 同仁堂 15.93 亿元; 5) 济川药业 10.24 亿元",
+      "SQL": "SELECT stock_abbr, report_year, report_period, net_profit FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY net_profit DESC LIMIT 10",
+      "image": "B1060_1.jpg"
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G61" s="1" t="inlineStr">
+        <is>
+          <t>B1060_1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="120" customHeight="1">
+      <c r="A62" s="1" t="inlineStr">
+        <is>
+          <t>B1061</t>
+        </is>
+      </c>
+      <c r="B62" s="1" t="inlineStr">
+        <is>
+          <t>数据统计分析查询</t>
+        </is>
+      </c>
+      <c r="C62" s="1" t="inlineStr">
+        <is>
+          <t>[{"Q": "查询2025年第三季度投资性现金流量净额的正负分布情况，用柱状图展示正负公司的数量及净额均值"}]</t>
+        </is>
+      </c>
+      <c r="D62" s="1" t="inlineStr"/>
+      <c r="E62" s="1" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="F62" s="1" t="inlineStr">
+        <is>
+          <t>{
+  "问题编号": "B1061",
+  "问题类型": "数据统计分析查询",
+  "子问题": [
+    {
+      "Q": "查询2025年第三季度投资性现金流量净额的正负分布情况，用柱状图展示正负公司的数量及净额均值",
+      "A": "澄清：请问要查询哪家公司？",
+      "SQL": "",
+      "image": ""
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G62" s="1" t="inlineStr"/>
+    </row>
+    <row r="63" ht="120" customHeight="1">
+      <c r="A63" s="1" t="inlineStr">
+        <is>
+          <t>B1062</t>
+        </is>
+      </c>
+      <c r="B63" s="1" t="inlineStr">
+        <is>
+          <t>数据统计分析查询</t>
+        </is>
+      </c>
+      <c r="C63" s="1" t="inlineStr">
+        <is>
+          <t>[{"Q": "分析2025年第三季度营业成本占营业总收入的比例排名后十的公司，用条形图展示占比数值"}]</t>
+        </is>
+      </c>
+      <c r="D63" s="1" t="inlineStr">
+        <is>
+          <t>SELECT stock_abbr, report_year, report_period, total_operating_revenue FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY total_operating_revenue DESC LIMIT 10</t>
+        </is>
+      </c>
+      <c r="E63" s="1" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="F63" s="1" t="inlineStr">
+        <is>
+          <t>{
+  "问题编号": "B1062",
+  "问题类型": "数据统计分析查询",
+  "子问题": [
+    {
+      "Q": "分析2025年第三季度营业成本占营业总收入的比例排名后十的公司，用条形图展示占比数值",
+      "A": "营业总收入 排名 Top5：1) 白云山 616.06 亿元; 2) 同仁堂 133.08 亿元; 3) 步长制药 84.69 亿元; 4) 太极集团 80.88 亿元; 5) 片仔癀 74.42 亿元",
+      "SQL": "SELECT stock_abbr, report_year, report_period, total_operating_revenue FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY total_operating_revenue DESC LIMIT 10",
+      "image": "B1062_1.jpg"
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G63" s="1" t="inlineStr">
+        <is>
+          <t>B1062_1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="120" customHeight="1">
+      <c r="A64" s="1" t="inlineStr">
+        <is>
+          <t>B1063</t>
+        </is>
+      </c>
+      <c r="B64" s="1" t="inlineStr">
+        <is>
+          <t>数据统计分析查询</t>
+        </is>
+      </c>
+      <c r="C64" s="1" t="inlineStr">
+        <is>
+          <t>[{"Q": "分析2022-2025年第三季度66家中药公司营业总收入的复合增长率分布，用直方图展示"}]</t>
+        </is>
+      </c>
+      <c r="D64" s="1" t="inlineStr"/>
+      <c r="E64" s="1" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="F64" s="1" t="inlineStr">
+        <is>
+          <t>{
+  "问题编号": "B1063",
+  "问题类型": "数据统计分析查询",
+  "子问题": [
+    {
+      "Q": "分析2022-2025年第三季度66家中药公司营业总收入的复合增长率分布，用直方图展示",
+      "A": "澄清：请问要查询哪家公司？",
+      "SQL": "",
+      "image": ""
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G64" s="1" t="inlineStr"/>
+    </row>
+    <row r="65" ht="120" customHeight="1">
+      <c r="A65" s="1" t="inlineStr">
+        <is>
+          <t>B1064</t>
+        </is>
+      </c>
+      <c r="B65" s="1" t="inlineStr">
+        <is>
+          <t>数据统计分析查询</t>
+        </is>
+      </c>
+      <c r="C65" s="1" t="inlineStr">
+        <is>
+          <t>[{"Q": "对比2025年第三季度销售费用率低于行业均值和高于行业均值公司的平均净利润率，用柱状图展示差异"}]</t>
+        </is>
+      </c>
+      <c r="D65" s="1" t="inlineStr">
+        <is>
+          <t>SELECT stock_abbr, report_year, report_period, net_profit FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END</t>
+        </is>
+      </c>
+      <c r="E65" s="1" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="F65" s="1" t="inlineStr">
+        <is>
+          <t>{
+  "问题编号": "B1064",
+  "问题类型": "数据统计分析查询",
+  "子问题": [
+    {
+      "Q": "对比2025年第三季度销售费用率低于行业均值和高于行业均值公司的平均净利润率，用柱状图展示差异",
+      "A": "净利润 对比：贵州百灵 2025三季报 —; 东阿阿胶 2025三季报 —; 云南白药 2025三季报 —; 启迪药业 2025三季报 —; 仁和药业 2025三季报 —; 通化金马 2025三季报 —; 华神科技 2025三季报 —; 九芝堂 2025三季报 —; 华润三九 2025三季报 —; 万邦德 2025三季报 —; 沃华医药 2025三季报 —; 莱茵生物 2025三季报 —; 嘉应制药 2025三季报 —; 新里程 2025三季报 —; 桂林三金 2025三季报 —; 奇正藏药 2025三季报 —; 众生药业 2025三季报 —; 精华制药 2025三季报 —; 信邦制药 2025三季报 —; 益盛药业 2025三季报 —; 瑞康医药 2025三季报 —; 以岭药业 2025三季报 —; 特一药业 2025三季报 —; 葵花药业 2025三季报 —; 康弘药业 2025三季报 —; 盘龙药业 2025三季报 —; 新天药业 2025三季报 —; 华森制药 2025三季报 —; 红日药业 2025三季报 —; 振东制药 2025三季报 —; 佐力药业 2025三季报 —; 新光药业 2025三季报 —; 陇神戎发 2025三季报 —; 康泰医学 2025三季报 —; 维康药业 2025三季报 —; 粤万年青 2025三季报 —; 恩威医药 2025三季报 —; 金花股份 2025三季报 3,423.74 万元; 同仁堂 2025三季报 15.93 亿元; 太极集团 2025三季报 1.64 亿元; 太龙药业 2025三季报 3,047.46 万元; 中恒集团 2025三季报 -931.86 万元; 羚锐制药 2025三季报 6.54 亿元; 达仁堂 2025三季报 21.46 亿元; 白云山 2025三季报 33.98 亿元; 亚宝药业 2025三季报 1.98 亿元; 昆药集团 2025三季报 3.23 亿元; 片仔癀 2025三季报 21.33 亿元; 千金药业 2025三季报 2.58 亿元; 康美药业 2025三季报 1,509.11 万元; 天士力 2025三季报 9.93 亿元; 康缘药业 2025三季报 2.08 亿元; 济川药业 2025三季报 10.24 亿元; 康恩贝 2025三季报 5.96 亿元; 益佰制药 2025三季报 -9,062.98 万元; 神奇制药 2025三季报 5,109.10 万元; 天目药业 2025三季报 750.81 万元; 江中药业 2025三季报 7.43 亿元; 广誉远 2025三季报 8,215.46 万元; 健民集团 2025三季报 2.89 亿元; 马应龙 2025三季报 5.19 亿元; 康惠制药 2025三季报 -1.57 亿元; 贵州三力 2025三季报 8,367.73 万元; 珍宝岛 2025三季报 -3.76 亿元; 步长制药 2025三季报 7.91 亿元; 寿仙谷 2025三季报 7,634.62 万元; 方盛制药 2025三季报 2.65 亿元",
+      "SQL": "SELECT stock_abbr, report_year, report_period, net_profit FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
+      "image": "B1064_1.jpg"
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G65" s="1" t="inlineStr">
+        <is>
+          <t>B1064_1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="120" customHeight="1">
+      <c r="A66" s="1" t="inlineStr">
+        <is>
+          <t>B1065</t>
+        </is>
+      </c>
+      <c r="B66" s="1" t="inlineStr">
+        <is>
+          <t>数据统计分析查询</t>
+        </is>
+      </c>
+      <c r="C66" s="1" t="inlineStr">
+        <is>
+          <t>[{"Q": "查询2025年第三季度出口业务占比超过10%的中药公司，用表格列出其出口占比、营业总收入增长率，并用折线图展示它们的营收增长趋势"}]</t>
+        </is>
+      </c>
+      <c r="D66" s="1" t="inlineStr"/>
+      <c r="E66" s="1" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="F66" s="1" t="inlineStr">
+        <is>
+          <t>{
+  "问题编号": "B1065",
+  "问题类型": "数据统计分析查询",
+  "子问题": [
+    {
+      "Q": "查询2025年第三季度出口业务占比超过10%的中药公司，用表格列出其出口占比、营业总收入增长率，并用折线图展示它们的营收增长趋势",
+      "A": "澄清：请问要分析哪家公司的趋势？",
+      "SQL": "",
+      "image": ""
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G66" s="1" t="inlineStr"/>
+    </row>
+    <row r="67" ht="120" customHeight="1">
+      <c r="A67" s="1" t="inlineStr">
+        <is>
+          <t>B1066</t>
+        </is>
+      </c>
+      <c r="B67" s="1" t="inlineStr">
+        <is>
+          <t>数据统计分析查询</t>
+        </is>
+      </c>
+      <c r="C67" s="1" t="inlineStr">
+        <is>
+          <t>[{"Q": "哪些公司的业绩比较好？"}, {"Q": "2025年第三季度，2家中药上市公司中，营业总收入和净利润均排名前十的公司"}]</t>
+        </is>
+      </c>
+      <c r="D67" s="1" t="inlineStr">
+        <is>
+          <t>SELECT stock_abbr, report_year, report_period, net_profit FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY net_profit DESC LIMIT 10</t>
+        </is>
+      </c>
+      <c r="E67" s="1" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="F67" s="1" t="inlineStr">
+        <is>
+          <t>{
+  "问题编号": "B1066",
+  "问题类型": "数据统计分析查询",
+  "子问题": [
+    {
+      "Q": "哪些公司的业绩比较好？",
+      "A": "信息不足，无法生成 SQL",
+      "SQL": "",
+      "image": ""
+    },
+    {
+      "Q": "2025年第三季度，2家中药上市公司中，营业总收入和净利润均排名前十的公司",
+      "A": "净利润 排名 Top5：1) 白云山 33.98 亿元; 2) 达仁堂 21.46 亿元; 3) 片仔癀 21.33 亿元; 4) 同仁堂 15.93 亿元; 5) 济川药业 10.24 亿元",
+      "SQL": "SELECT stock_abbr, report_year, report_period, net_profit FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY net_profit DESC LIMIT 10",
+      "image": "B1066_2.jpg"
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G67" s="1" t="inlineStr">
+        <is>
+          <t>B1066_2.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="120" customHeight="1">
+      <c r="A68" s="1" t="inlineStr">
+        <is>
+          <t>B1067</t>
+        </is>
+      </c>
+      <c r="B68" s="1" t="inlineStr">
+        <is>
+          <t>数据统计分析查询</t>
+        </is>
+      </c>
+      <c r="C68" s="1" t="inlineStr">
+        <is>
+          <t>[{"Q": "中药公司的资产负债率情况如何"}, {"Q": "2025年第三季度，66家中药上市公司的资产负债率均值是多少"}]</t>
+        </is>
+      </c>
+      <c r="D68" s="1" t="inlineStr"/>
+      <c r="E68" s="1" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="F68" s="1" t="inlineStr">
+        <is>
+          <t>{
+  "问题编号": "B1067",
+  "问题类型": "数据统计分析查询",
+  "子问题": [
+    {
+      "Q": "中药公司的资产负债率情况如何",
+      "A": "澄清：请问要查询哪家公司？",
+      "SQL": "",
+      "image": ""
+    },
+    {
+      "Q": "2025年第三季度，66家中药上市公司的资产负债率均值是多少",
+      "A": "澄清：请问要查询哪家公司？",
+      "SQL": "",
+      "image": ""
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G68" s="1" t="inlineStr"/>
+    </row>
+    <row r="69" ht="120" customHeight="1">
+      <c r="A69" s="1" t="inlineStr">
+        <is>
+          <t>B1068</t>
+        </is>
+      </c>
+      <c r="B69" s="1" t="inlineStr">
+        <is>
+          <t>数据统计分析查询</t>
+        </is>
+      </c>
+      <c r="C69" s="1" t="inlineStr">
+        <is>
+          <t>[{"Q": "分析中药行业的盈利能力"}, {"Q": "2025年第三季度，66家中药上市公司的平均销售毛利率、销售净利率分别是多少？请结合数值分析行业整体盈利能力"}]</t>
+        </is>
+      </c>
+      <c r="D69" s="1" t="inlineStr"/>
+      <c r="E69" s="1" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="F69" s="1" t="inlineStr">
+        <is>
+          <t>{
+  "问题编号": "B1068",
+  "问题类型": "数据统计分析查询",
+  "子问题": [
+    {
+      "Q": "分析中药行业的盈利能力",
+      "A": "澄清：请问要查询哪家公司？",
+      "SQL": "",
+      "image": ""
+    },
+    {
+      "Q": "2025年第三季度，66家中药上市公司的平均销售毛利率、销售净利率分别是多少？请结合数值分析行业整体盈利能力",
+      "A": "澄清：请问要查询哪家公司？",
+      "SQL": "",
+      "image": ""
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G69" s="1" t="inlineStr"/>
+    </row>
+    <row r="70" ht="120" customHeight="1">
+      <c r="A70" s="1" t="inlineStr">
+        <is>
+          <t>B1069</t>
+        </is>
+      </c>
+      <c r="B70" s="1" t="inlineStr">
+        <is>
+          <t>数据统计分析查询</t>
+        </is>
+      </c>
+      <c r="C70" s="1" t="inlineStr">
+        <is>
+          <t>[{"Q": "2025年的财务数据怎么样？"}, {"Q": "2025年第三季度，66家中药上市公司的营业总收入、净利润均值分别是多少？与2024年同期相比增长率如何？"}]</t>
+        </is>
+      </c>
+      <c r="D70" s="1" t="inlineStr">
+        <is>
+          <t>SELECT stock_abbr, report_year, report_period, net_profit FROM income_sheet WHERE report_year IN (2025,2024) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END</t>
+        </is>
+      </c>
+      <c r="E70" s="1" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="F70" s="1" t="inlineStr">
+        <is>
+          <t>{
+  "问题编号": "B1069",
+  "问题类型": "数据统计分析查询",
+  "子问题": [
+    {
+      "Q": "2025年的财务数据怎么样？",
+      "A": "澄清：请问要查询哪家公司？",
+      "SQL": "",
+      "image": ""
+    },
+    {
+      "Q": "2025年第三季度，66家中药上市公司的营业总收入、净利润均值分别是多少？与2024年同期相比增长率如何？",
+      "A": "金花股份的净利润从2024三季报的 3,077.02 万元 变化到2025三季报的 2.65 亿元（+762.37%）",
+      "SQL": "SELECT stock_abbr, report_year, report_period, net_profit FROM income_sheet WHERE report_year IN (2025,2024) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
+      "image": "B1069_2.jpg"
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G70" s="1" t="inlineStr">
+        <is>
+          <t>B1069_2.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="120" customHeight="1">
+      <c r="A71" s="1" t="inlineStr">
+        <is>
+          <t>B1070</t>
+        </is>
+      </c>
+      <c r="B71" s="1" t="inlineStr">
+        <is>
+          <t>数据统计分析查询</t>
+        </is>
+      </c>
+      <c r="C71" s="1" t="inlineStr">
+        <is>
+          <t>[{"Q": "查询净利润同比增长的公司"}, {"Q": "2025年第三季度，66家中药上市公司中，净利润同比增长率超过20%的公司有哪些？列出股票代码、简称及具体增长率"}]</t>
+        </is>
+      </c>
+      <c r="D71" s="1" t="inlineStr"/>
+      <c r="E71" s="1" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="F71" s="1" t="inlineStr">
+        <is>
+          <t>{
+  "问题编号": "B1070",
+  "问题类型": "数据统计分析查询",
+  "子问题": [
+    {
+      "Q": "查询净利润同比增长的公司",
+      "A": "澄清：请问要查询哪家公司？",
+      "SQL": "",
+      "image": ""
+    },
+    {
+      "Q": "2025年第三季度，66家中药上市公司中，净利润同比增长率超过20%的公司有哪些？列出股票代码、简称及具体增长率",
+      "A": "澄清：请问要查询哪家公司？",
+      "SQL": "",
+      "image": ""
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G71" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/result/result_2.xlsx
+++ b/result/result_2.xlsx
@@ -208,7 +208,7 @@
     <from>
       <col>6</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2286000" cy="1428750"/>
@@ -233,7 +233,7 @@
     <from>
       <col>6</col>
       <colOff>0</colOff>
-      <row>10</row>
+      <row>5</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2286000" cy="1428750"/>
@@ -258,7 +258,7 @@
     <from>
       <col>6</col>
       <colOff>0</colOff>
-      <row>14</row>
+      <row>6</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2286000" cy="1428750"/>
@@ -283,7 +283,7 @@
     <from>
       <col>6</col>
       <colOff>0</colOff>
-      <row>16</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2286000" cy="1428750"/>
@@ -308,7 +308,7 @@
     <from>
       <col>6</col>
       <colOff>0</colOff>
-      <row>18</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2286000" cy="1428750"/>
@@ -333,7 +333,7 @@
     <from>
       <col>6</col>
       <colOff>0</colOff>
-      <row>19</row>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2286000" cy="1428750"/>
@@ -358,7 +358,7 @@
     <from>
       <col>6</col>
       <colOff>0</colOff>
-      <row>20</row>
+      <row>13</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2286000" cy="1428750"/>
@@ -383,7 +383,7 @@
     <from>
       <col>6</col>
       <colOff>0</colOff>
-      <row>23</row>
+      <row>14</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2286000" cy="1428750"/>
@@ -408,7 +408,7 @@
     <from>
       <col>6</col>
       <colOff>0</colOff>
-      <row>25</row>
+      <row>15</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2286000" cy="1428750"/>
@@ -433,7 +433,7 @@
     <from>
       <col>6</col>
       <colOff>0</colOff>
-      <row>26</row>
+      <row>16</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2286000" cy="1428750"/>
@@ -458,7 +458,7 @@
     <from>
       <col>6</col>
       <colOff>0</colOff>
-      <row>28</row>
+      <row>17</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2286000" cy="1428750"/>
@@ -483,7 +483,7 @@
     <from>
       <col>6</col>
       <colOff>0</colOff>
-      <row>29</row>
+      <row>18</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2286000" cy="1428750"/>
@@ -508,7 +508,7 @@
     <from>
       <col>6</col>
       <colOff>0</colOff>
-      <row>30</row>
+      <row>19</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2286000" cy="1428750"/>
@@ -533,7 +533,7 @@
     <from>
       <col>6</col>
       <colOff>0</colOff>
-      <row>34</row>
+      <row>20</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2286000" cy="1428750"/>
@@ -558,7 +558,7 @@
     <from>
       <col>6</col>
       <colOff>0</colOff>
-      <row>40</row>
+      <row>23</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2286000" cy="1428750"/>
@@ -583,7 +583,7 @@
     <from>
       <col>6</col>
       <colOff>0</colOff>
-      <row>42</row>
+      <row>25</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2286000" cy="1428750"/>
@@ -608,7 +608,7 @@
     <from>
       <col>6</col>
       <colOff>0</colOff>
-      <row>44</row>
+      <row>26</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2286000" cy="1428750"/>
@@ -633,7 +633,7 @@
     <from>
       <col>6</col>
       <colOff>0</colOff>
-      <row>45</row>
+      <row>28</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2286000" cy="1428750"/>
@@ -658,7 +658,7 @@
     <from>
       <col>6</col>
       <colOff>0</colOff>
-      <row>47</row>
+      <row>29</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2286000" cy="1428750"/>
@@ -683,7 +683,7 @@
     <from>
       <col>6</col>
       <colOff>0</colOff>
-      <row>48</row>
+      <row>30</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2286000" cy="1428750"/>
@@ -708,7 +708,7 @@
     <from>
       <col>6</col>
       <colOff>0</colOff>
-      <row>49</row>
+      <row>31</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2286000" cy="1428750"/>
@@ -733,7 +733,7 @@
     <from>
       <col>6</col>
       <colOff>0</colOff>
-      <row>50</row>
+      <row>34</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2286000" cy="1428750"/>
@@ -758,7 +758,7 @@
     <from>
       <col>6</col>
       <colOff>0</colOff>
-      <row>51</row>
+      <row>36</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2286000" cy="1428750"/>
@@ -783,7 +783,7 @@
     <from>
       <col>6</col>
       <colOff>0</colOff>
-      <row>56</row>
+      <row>37</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2286000" cy="1428750"/>
@@ -808,7 +808,7 @@
     <from>
       <col>6</col>
       <colOff>0</colOff>
-      <row>58</row>
+      <row>42</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2286000" cy="1428750"/>
@@ -833,7 +833,7 @@
     <from>
       <col>6</col>
       <colOff>0</colOff>
-      <row>59</row>
+      <row>43</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2286000" cy="1428750"/>
@@ -858,7 +858,7 @@
     <from>
       <col>6</col>
       <colOff>0</colOff>
-      <row>60</row>
+      <row>44</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2286000" cy="1428750"/>
@@ -883,7 +883,7 @@
     <from>
       <col>6</col>
       <colOff>0</colOff>
-      <row>62</row>
+      <row>45</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2286000" cy="1428750"/>
@@ -908,7 +908,7 @@
     <from>
       <col>6</col>
       <colOff>0</colOff>
-      <row>64</row>
+      <row>46</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2286000" cy="1428750"/>
@@ -933,7 +933,7 @@
     <from>
       <col>6</col>
       <colOff>0</colOff>
-      <row>66</row>
+      <row>47</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2286000" cy="1428750"/>
@@ -958,7 +958,7 @@
     <from>
       <col>6</col>
       <colOff>0</colOff>
-      <row>69</row>
+      <row>48</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2286000" cy="1428750"/>
@@ -969,6 +969,406 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId34"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>49</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2286000" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="35" name="Image 35" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId35"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>50</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2286000" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="36" name="Image 36" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId36"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>51</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2286000" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="37" name="Image 37" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId37"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>52</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2286000" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="38" name="Image 38" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId38"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>54</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2286000" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="39" name="Image 39" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId39"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>56</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2286000" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="40" name="Image 40" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId40"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>58</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2286000" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="41" name="Image 41" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId41"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>59</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2286000" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="42" name="Image 42" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId42"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>60</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2286000" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="43" name="Image 43" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId43"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>61</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2286000" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="44" name="Image 44" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId44"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>62</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2286000" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="45" name="Image 45" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId45"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>64</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2286000" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="46" name="Image 46" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId46"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>66</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2286000" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="47" name="Image 47" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId47"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>67</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2286000" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="48" name="Image 48" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId48"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>68</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2286000" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="49" name="Image 49" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId49"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>69</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2286000" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="50" name="Image 50" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId50"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1338,7 +1738,7 @@
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>SELECT stock_abbr, report_year, report_period, total_profit FROM income_sheet WHERE (stock_abbr='金花股份') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END</t>
+          <t>SELECT stock_abbr, stock_code, report_year, report_period, total_profit FROM income_sheet WHERE (stock_abbr='金花股份') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
@@ -1354,14 +1754,14 @@
   "子问题": [
     {
       "Q": "金花股份利润总额是多少",
-      "A": "金花股份的利润总额从2024三季报的 3,245.72 万元 变化到2025三季报的 3,533.59 万元（+8.87%）",
-      "SQL": "SELECT stock_abbr, report_year, report_period, total_profit FROM income_sheet WHERE (stock_abbr='金花股份') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
+      "A": "符合条件共 12 家，前5：金花股份(600080) —; 金花股份(600080) —; 金花股份(600080) —; 金花股份(600080) —; 金花股份(600080) —",
+      "SQL": "SELECT stock_abbr, stock_code, report_year, report_period, total_profit FROM income_sheet WHERE (stock_abbr='金花股份') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
       "image": "B1001_1.jpg"
     },
     {
       "Q": "2025年第三季度的",
       "A": "金花股份 2025三季报的利润总额为 3,533.59 万元",
-      "SQL": "SELECT stock_abbr, report_year, report_period, total_profit FROM income_sheet WHERE (stock_abbr='金花股份') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
+      "SQL": "SELECT stock_abbr, stock_code, report_year, report_period, total_profit FROM income_sheet WHERE (stock_abbr='金花股份') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
       "image": "B1001_2.jpg"
     }
   ]
@@ -1392,7 +1792,7 @@
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>SELECT stock_abbr, report_year, report_period, total_profit FROM income_sheet WHERE (stock_abbr='金花股份') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END</t>
+          <t>SELECT stock_abbr, stock_code, report_year, report_period, total_profit FROM income_sheet WHERE (stock_abbr='金花股份') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END</t>
         </is>
       </c>
       <c r="E3" s="1" t="inlineStr">
@@ -1409,7 +1809,7 @@
     {
       "Q": "金花股份近几年的利润总额变化趋势是什么样的",
       "A": "金花股份的利润总额从2024三季报的 3,245.72 万元 变化到2025三季报的 3,533.59 万元（+8.87%）",
-      "SQL": "SELECT stock_abbr, report_year, report_period, total_profit FROM income_sheet WHERE (stock_abbr='金花股份') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
+      "SQL": "SELECT stock_abbr, stock_code, report_year, report_period, total_profit FROM income_sheet WHERE (stock_abbr='金花股份') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
       "image": "B1002_1.jpg"
     }
   ]
@@ -1440,7 +1840,7 @@
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>SELECT stock_abbr, report_year, report_period, roe FROM core_performance_indicators_sheet WHERE (stock_abbr='白云山' OR stock_code='000999') AND report_period='FY' ORDER BY roe DESC LIMIT 10</t>
+          <t>SELECT stock_abbr, stock_code, report_year, report_period, roe FROM core_performance_indicators_sheet WHERE (stock_abbr='白云山' OR stock_code='000999') AND report_period='FY' ORDER BY roe DESC LIMIT 10</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
@@ -1457,7 +1857,7 @@
     {
       "Q": "999与白云山相比，去年收益率最高的是",
       "A": "ROE 排名 Top5：1) 华润三九 15.86%; 2) 白云山 13.46%; 3) 白云山 12.97%; 4) 白云山 11.55%; 5) 华润三九 —",
-      "SQL": "SELECT stock_abbr, report_year, report_period, roe FROM core_performance_indicators_sheet WHERE (stock_abbr='白云山' OR stock_code='000999') AND report_period='FY' ORDER BY roe DESC LIMIT 10",
+      "SQL": "SELECT stock_abbr, stock_code, report_year, report_period, roe FROM core_performance_indicators_sheet WHERE (stock_abbr='白云山' OR stock_code='000999') AND report_period='FY' ORDER BY roe DESC LIMIT 10",
       "image": "B1003_1.jpg"
     }
   ]
@@ -1486,10 +1886,14 @@
           <t>[{"Q": "2025年前三季度，公司实现收入超过200亿元的企业有哪些"}]</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr"/>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>SELECT stock_abbr, stock_code, report_year, report_period, total_operating_revenue FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') AND total_operating_revenue &gt; 2000000.0 AND total_operating_revenue IS NOT NULL ORDER BY total_operating_revenue DESC LIMIT 10</t>
+        </is>
+      </c>
       <c r="E5" s="1" t="inlineStr">
         <is>
-          <t>table</t>
+          <t>bar</t>
         </is>
       </c>
       <c r="F5" s="1" t="inlineStr">
@@ -1500,15 +1904,19 @@
   "子问题": [
     {
       "Q": "2025年前三季度，公司实现收入超过200亿元的企业有哪些",
-      "A": "信息不足，无法生成 SQL",
-      "SQL": "",
-      "image": ""
-    }
-  ]
-}</t>
-        </is>
-      </c>
-      <c r="G5" s="1" t="inlineStr"/>
+      "A": "营业收入 排名 Top1：1) 白云山 616.06 亿元",
+      "SQL": "SELECT stock_abbr, stock_code, report_year, report_period, total_operating_revenue FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') AND total_operating_revenue &gt; 2000000.0 AND total_operating_revenue IS NOT NULL ORDER BY total_operating_revenue DESC LIMIT 10",
+      "image": "B1004_1.jpg"
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G5" s="1" t="inlineStr">
+        <is>
+          <t>B1004_1.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="120" customHeight="1">
       <c r="A6" s="1" t="inlineStr">
@@ -1526,7 +1934,11 @@
           <t>[{"Q": "企业名称：三金，第三季度公司主营业务收入是多少"}, {"Q": "2025年第三季度的"}]</t>
         </is>
       </c>
-      <c r="D6" s="1" t="inlineStr"/>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>SELECT stock_abbr, stock_code, report_year, report_period, total_operating_revenue FROM income_sheet WHERE (stock_abbr='桂林三金') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END</t>
+        </is>
+      </c>
       <c r="E6" s="1" t="inlineStr">
         <is>
           <t>table</t>
@@ -1540,21 +1952,25 @@
   "子问题": [
     {
       "Q": "企业名称：三金，第三季度公司主营业务收入是多少",
-      "A": "澄清：请问要查询哪家公司？",
-      "SQL": "",
-      "image": ""
+      "A": "符合条件共 3 家，前3：桂林三金(002275) —; 桂林三金(002275) —; 桂林三金(002275) —",
+      "SQL": "SELECT stock_abbr, stock_code, report_year, report_period, total_operating_revenue FROM income_sheet WHERE (stock_abbr='桂林三金') AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
+      "image": "B1005_1.jpg"
     },
     {
       "Q": "2025年第三季度的",
-      "A": "澄清：请问要查询哪家公司？",
-      "SQL": "",
-      "image": ""
-    }
-  ]
-}</t>
-        </is>
-      </c>
-      <c r="G6" s="1" t="inlineStr"/>
+      "A": "桂林三金 2025三季报的主营业务收入为 —",
+      "SQL": "SELECT stock_abbr, stock_code, report_year, report_period, total_operating_revenue FROM income_sheet WHERE (stock_abbr='桂林三金') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
+      "image": "B1005_2.jpg"
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G6" s="1" t="inlineStr">
+        <is>
+          <t>B1005_2.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="120" customHeight="1">
       <c r="A7" s="1" t="inlineStr">
@@ -1572,7 +1988,11 @@
           <t>[{"Q": "分析一下千金药业2025收入情况，看看有什么变化。"}, {"Q": "绘制近3年的收入趋势图"}, {"Q": "绘制水平柱状图"}]</t>
         </is>
       </c>
-      <c r="D7" s="1" t="inlineStr"/>
+      <c r="D7" s="1" t="inlineStr">
+        <is>
+          <t>SELECT stock_abbr, stock_code, report_year, report_period, total_operating_revenue FROM income_sheet WHERE (stock_abbr='千金药业') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END</t>
+        </is>
+      </c>
       <c r="E7" s="1" t="inlineStr">
         <is>
           <t>table</t>
@@ -1586,27 +2006,31 @@
   "子问题": [
     {
       "Q": "分析一下千金药业2025收入情况，看看有什么变化。",
-      "A": "信息不足，无法生成 SQL",
-      "SQL": "",
-      "image": ""
+      "A": "千金药业的营业收入从2022年报的 40.26 亿元 变化到2025三季报的 27.18 亿元（-32.49%）",
+      "SQL": "SELECT stock_abbr, stock_code, report_year, report_period, total_operating_revenue FROM income_sheet WHERE (stock_abbr='千金药业') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
+      "image": "B1006_1.jpg"
     },
     {
       "Q": "绘制近3年的收入趋势图",
-      "A": "澄清：请问要分析哪家公司的趋势？",
-      "SQL": "",
-      "image": ""
+      "A": "千金药业的营业收入从2022年报的 40.26 亿元 变化到2025三季报的 27.18 亿元（-32.49%）",
+      "SQL": "SELECT stock_abbr, stock_code, report_year, report_period, total_operating_revenue FROM income_sheet WHERE (stock_abbr='千金药业') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
+      "image": "B1006_2.jpg"
     },
     {
       "Q": "绘制水平柱状图",
-      "A": "澄清：请问要查询哪家公司？",
-      "SQL": "",
-      "image": ""
-    }
-  ]
-}</t>
-        </is>
-      </c>
-      <c r="G7" s="1" t="inlineStr"/>
+      "A": "符合条件共 12 家，前5：千金药业(600479) 40.26 亿元; 千金药业(600479) 9.60 亿元; 千金药业(600479) 19.13 亿元; 千金药业(600479) 27.79 亿元; 千金药业(600479) 37.98 亿元",
+      "SQL": "SELECT stock_abbr, stock_code, report_year, report_period, total_operating_revenue FROM income_sheet WHERE (stock_abbr='千金药业') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
+      "image": "B1006_3.jpg"
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G7" s="1" t="inlineStr">
+        <is>
+          <t>B1006_3.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="120" customHeight="1">
       <c r="A8" s="1" t="inlineStr">
@@ -1624,10 +2048,14 @@
           <t>[{"Q": "哪些企业是亏钱的？"}, {"Q": "“亏钱”在业务场景中，指的是经审计财务报表的核心利润指标为负的数据。"}]</t>
         </is>
       </c>
-      <c r="D8" s="1" t="inlineStr"/>
+      <c r="D8" s="1" t="inlineStr">
+        <is>
+          <t>SELECT stock_abbr, stock_code, report_year, report_period, net_profit FROM income_sheet WHERE net_profit &lt; 0 AND net_profit IS NOT NULL ORDER BY net_profit DESC LIMIT 50</t>
+        </is>
+      </c>
       <c r="E8" s="1" t="inlineStr">
         <is>
-          <t>table</t>
+          <t>bar</t>
         </is>
       </c>
       <c r="F8" s="1" t="inlineStr">
@@ -1638,21 +2066,25 @@
   "子问题": [
     {
       "Q": "哪些企业是亏钱的？",
-      "A": "澄清：请问要查询哪家公司？",
-      "SQL": "",
-      "image": ""
+      "A": "符合条件共 43 家，前5：康惠制药(603139) -248.30 万元; 天目药业(600671) -376.11 万元; 华神科技(000790) -743.69 万元; 中恒集团(600252) -918.55 万元; 中恒集团(600252) -931.86 万元",
+      "SQL": "SELECT stock_abbr, stock_code, report_year, report_period, net_profit FROM income_sheet WHERE net_profit &lt; 0 ORDER BY net_profit DESC LIMIT 50",
+      "image": "B1007_1.jpg"
     },
     {
       "Q": "“亏钱”在业务场景中，指的是经审计财务报表的核心利润指标为负的数据。",
-      "A": "澄清：请问要查询哪家公司？",
-      "SQL": "",
-      "image": ""
-    }
-  ]
-}</t>
-        </is>
-      </c>
-      <c r="G8" s="1" t="inlineStr"/>
+      "A": "符合条件共 43 家，前5：康惠制药(603139) -248.30 万元; 天目药业(600671) -376.11 万元; 华神科技(000790) -743.69 万元; 中恒集团(600252) -918.55 万元; 中恒集团(600252) -931.86 万元",
+      "SQL": "SELECT stock_abbr, stock_code, report_year, report_period, net_profit FROM income_sheet WHERE net_profit &lt; 0 AND net_profit IS NOT NULL ORDER BY net_profit DESC LIMIT 50",
+      "image": "B1007_2.jpg"
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G8" s="1" t="inlineStr">
+        <is>
+          <t>B1007_2.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="120" customHeight="1">
       <c r="A9" s="1" t="inlineStr">
@@ -1718,7 +2150,7 @@
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>SELECT stock_abbr, report_year, report_period, net_profit FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY net_profit DESC LIMIT 10</t>
+          <t>SELECT stock_abbr, stock_code, report_year, report_period, net_profit FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY net_profit DESC LIMIT 10</t>
         </is>
       </c>
       <c r="E10" s="1" t="inlineStr">
@@ -1735,7 +2167,7 @@
     {
       "Q": "2025年第三季度，66家中药公司中“营业总收入”和“净利润”均排名前五的公司有哪些？请列出其股票代码、简称、营业总收入（万元）、净利润（万元）",
       "A": "净利润 排名 Top5：1) 白云山 33.98 亿元; 2) 达仁堂 21.46 亿元; 3) 片仔癀 21.33 亿元; 4) 同仁堂 15.93 亿元; 5) 济川药业 10.24 亿元",
-      "SQL": "SELECT stock_abbr, report_year, report_period, net_profit FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY net_profit DESC LIMIT 10",
+      "SQL": "SELECT stock_abbr, stock_code, report_year, report_period, net_profit FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY net_profit DESC LIMIT 10",
       "image": "B1009_1.jpg"
     }
   ]
@@ -1766,7 +2198,7 @@
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
-          <t>SELECT stock_abbr, report_year, report_period, total_operating_revenue FROM income_sheet WHERE (stock_abbr='白云山' OR stock_code='600332') AND report_year IN (2022,2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END</t>
+          <t>SELECT stock_abbr, stock_code, report_year, report_period, operating_revenue_yoy_growth FROM income_sheet WHERE (stock_abbr='白云山' OR stock_code='600332') AND report_year IN (2022,2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END</t>
         </is>
       </c>
       <c r="E11" s="1" t="inlineStr">
@@ -1782,8 +2214,8 @@
   "子问题": [
     {
       "Q": "对比白云山（600332）2022年至2025年第三季度的“营业总收入同比增长率”，展示各报告期的增长率数据，并生成趋势折线图。",
-      "A": "白云山 2025三季报 的营业总收入为 616.06 亿元（仅有效值）",
-      "SQL": "SELECT stock_abbr, report_year, report_period, total_operating_revenue FROM income_sheet WHERE (stock_abbr='白云山' OR stock_code='600332') AND report_year IN (2022,2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
+      "A": "未查询到有效数据",
+      "SQL": "SELECT stock_abbr, stock_code, report_year, report_period, operating_revenue_yoy_growth FROM income_sheet WHERE (stock_abbr='白云山' OR stock_code='600332') AND report_year IN (2022,2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
       "image": "B1010_1.jpg"
     }
   ]
@@ -1812,10 +2244,14 @@
           <t>[{"Q": "2025年第三季度，资产负债率（负债总额/资产总额）超过60%的中药公司有哪些？请列出股票代码、简称、资产负债率（%）。"}]</t>
         </is>
       </c>
-      <c r="D12" s="1" t="inlineStr"/>
+      <c r="D12" s="1" t="inlineStr">
+        <is>
+          <t>SELECT stock_abbr, stock_code, report_year, report_period, asset_liability_ratio FROM balance_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') AND asset_liability_ratio &gt; 60.0 AND asset_liability_ratio IS NOT NULL ORDER BY asset_liability_ratio DESC LIMIT 50</t>
+        </is>
+      </c>
       <c r="E12" s="1" t="inlineStr">
         <is>
-          <t>table</t>
+          <t>bar</t>
         </is>
       </c>
       <c r="F12" s="1" t="inlineStr">
@@ -1826,8 +2262,8 @@
   "子问题": [
     {
       "Q": "2025年第三季度，资产负债率（负债总额/资产总额）超过60%的中药公司有哪些？请列出股票代码、简称、资产负债率（%）。",
-      "A": "澄清：请问要查询哪家公司？",
-      "SQL": "",
+      "A": "未查询到数据",
+      "SQL": "SELECT stock_abbr, stock_code, report_year, report_period, asset_liability_ratio FROM balance_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') AND asset_liability_ratio &gt; 60.0 AND asset_liability_ratio IS NOT NULL ORDER BY asset_liability_ratio DESC LIMIT 50",
       "image": ""
     }
   ]
@@ -1852,10 +2288,14 @@
           <t>[{"Q": "2025年第三季度，“经营性现金流量净额”为负数且“净利润”为正数的公司有哪些？请列出其股票代码、简称、经营性现金流净额（万元）、净利润（万元）。"}]</t>
         </is>
       </c>
-      <c r="D13" s="1" t="inlineStr"/>
+      <c r="D13" s="1" t="inlineStr">
+        <is>
+          <t>SELECT stock_abbr, stock_code, report_year, report_period, net_cash_flow FROM cash_flow_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') AND net_cash_flow &lt; 0 AND net_cash_flow &gt; 0 AND net_cash_flow IS NOT NULL ORDER BY net_cash_flow DESC LIMIT 50</t>
+        </is>
+      </c>
       <c r="E13" s="1" t="inlineStr">
         <is>
-          <t>table</t>
+          <t>bar</t>
         </is>
       </c>
       <c r="F13" s="1" t="inlineStr">
@@ -1866,8 +2306,8 @@
   "子问题": [
     {
       "Q": "2025年第三季度，“经营性现金流量净额”为负数且“净利润”为正数的公司有哪些？请列出其股票代码、简称、经营性现金流净额（万元）、净利润（万元）。",
-      "A": "澄清：请问要查询哪家公司？",
-      "SQL": "",
+      "A": "未查询到数据",
+      "SQL": "SELECT stock_abbr, stock_code, report_year, report_period, net_cash_flow FROM cash_flow_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') AND net_cash_flow &lt; 0 AND net_cash_flow &gt; 0 AND net_cash_flow IS NOT NULL ORDER BY net_cash_flow DESC LIMIT 50",
       "image": ""
     }
   ]
@@ -1892,7 +2332,11 @@
           <t>[{"Q": "2025年第三季度，“销售毛利率”和“销售净利率”均高于行业均值的中药公司有哪些？请同步输出行业均值和公司具体数值。"}]</t>
         </is>
       </c>
-      <c r="D14" s="1" t="inlineStr"/>
+      <c r="D14" s="1" t="inlineStr">
+        <is>
+          <t>SELECT AVG(gross_profit_margin) AS gross_profit_margin_avg FROM core_performance_indicators_sheet WHERE gross_profit_margin IS NOT NULL AND report_year IN (2025) AND report_period IN ('Q3')</t>
+        </is>
+      </c>
       <c r="E14" s="1" t="inlineStr">
         <is>
           <t>table</t>
@@ -1906,15 +2350,19 @@
   "子问题": [
     {
       "Q": "2025年第三季度，“销售毛利率”和“销售净利率”均高于行业均值的中药公司有哪些？请同步输出行业均值和公司具体数值。",
-      "A": "澄清：请问要查询哪家公司？",
-      "SQL": "",
-      "image": ""
-    }
-  ]
-}</t>
-        </is>
-      </c>
-      <c r="G14" s="1" t="inlineStr"/>
+      "A": "毛利率均值：—",
+      "SQL": "SELECT AVG(gross_profit_margin) AS gross_profit_margin_avg FROM core_performance_indicators_sheet WHERE gross_profit_margin IS NOT NULL AND report_year IN (2025) AND report_period IN ('Q3')",
+      "image": "B1013_1.jpg"
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G14" s="1" t="inlineStr">
+        <is>
+          <t>B1013_1.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="120" customHeight="1">
       <c r="A15" s="1" t="inlineStr">
@@ -1934,7 +2382,7 @@
       </c>
       <c r="D15" s="1" t="inlineStr">
         <is>
-          <t>SELECT stock_abbr, report_year, report_period, total_operating_revenue FROM income_sheet WHERE (stock_abbr='云南白药' OR stock_code='000538') AND report_year IN (2025,2024) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END</t>
+          <t>SELECT stock_abbr, stock_code, report_year, report_period, total_operating_revenue FROM income_sheet WHERE (stock_abbr='云南白药' OR stock_code='000538') AND report_year IN (2025,2024) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END</t>
         </is>
       </c>
       <c r="E15" s="1" t="inlineStr">
@@ -1951,7 +2399,7 @@
     {
       "Q": "云南白药（000538）2025年第三季度的“营业总收入环比增长率”与2024年第三季度的环比增长率相比，变化了多少？请展示两年同期的环比数据。",
       "A": "未查询到有效数据",
-      "SQL": "SELECT stock_abbr, report_year, report_period, total_operating_revenue FROM income_sheet WHERE (stock_abbr='云南白药' OR stock_code='000538') AND report_year IN (2025,2024) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
+      "SQL": "SELECT stock_abbr, stock_code, report_year, report_period, total_operating_revenue FROM income_sheet WHERE (stock_abbr='云南白药' OR stock_code='000538') AND report_year IN (2025,2024) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
       "image": "B1014_1.jpg"
     }
   ]
@@ -1980,7 +2428,11 @@
           <t>[{"Q": "2022-2025年第三季度，“加权平均净资产收益率（扣非）”连续四个报告期均超过10%的公司有哪些？请列出股票代码、简称及各期收益率。"}]</t>
         </is>
       </c>
-      <c r="D16" s="1" t="inlineStr"/>
+      <c r="D16" s="1" t="inlineStr">
+        <is>
+          <t>SELECT AVG(roe) AS roe_avg FROM core_performance_indicators_sheet WHERE roe IS NOT NULL AND report_year IN (2025) AND report_period IN ('Q3') AND roe &gt; 10.0</t>
+        </is>
+      </c>
       <c r="E16" s="1" t="inlineStr">
         <is>
           <t>table</t>
@@ -1994,15 +2446,19 @@
   "子问题": [
     {
       "Q": "2022-2025年第三季度，“加权平均净资产收益率（扣非）”连续四个报告期均超过10%的公司有哪些？请列出股票代码、简称及各期收益率。",
-      "A": "澄清：请问要查询哪家公司？",
-      "SQL": "",
-      "image": ""
-    }
-  ]
-}</t>
-        </is>
-      </c>
-      <c r="G16" s="1" t="inlineStr"/>
+      "A": "净资产收益率均值：—",
+      "SQL": "SELECT AVG(roe) AS roe_avg FROM core_performance_indicators_sheet WHERE roe IS NOT NULL AND report_year IN (2025) AND report_period IN ('Q3') AND roe &gt; 10.0",
+      "image": "B1015_1.jpg"
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G16" s="1" t="inlineStr">
+        <is>
+          <t>B1015_1.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="120" customHeight="1">
       <c r="A17" s="1" t="inlineStr">
@@ -2022,7 +2478,7 @@
       </c>
       <c r="D17" s="1" t="inlineStr">
         <is>
-          <t>SELECT stock_abbr, report_year, report_period, total_operating_revenue FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY total_operating_revenue DESC LIMIT 10</t>
+          <t>SELECT stock_abbr, stock_code, report_year, report_period, asset_inventory FROM balance_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY asset_inventory DESC LIMIT 10</t>
         </is>
       </c>
       <c r="E17" s="1" t="inlineStr">
@@ -2038,8 +2494,8 @@
   "子问题": [
     {
       "Q": "2025年第三季度，“资产-存货”金额排名前三的公司，其“营业总收入”与存货金额的比值分别是多少？请列出公司简称、存货（万元）、营业总收入（万元）及比值。",
-      "A": "营业总收入 排名 Top5：1) 白云山 616.06 亿元; 2) 同仁堂 133.08 亿元; 3) 步长制药 84.69 亿元; 4) 太极集团 80.88 亿元; 5) 片仔癀 74.42 亿元",
-      "SQL": "SELECT stock_abbr, report_year, report_period, total_operating_revenue FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY total_operating_revenue DESC LIMIT 10",
+      "A": "存货 排名 Top5：1) 同仁堂 111.25 亿元; 2) 白云山 110.81 亿元; 3) 华润三九 63.87 亿元; 4) 片仔癀 61.60 亿元; 5) 云南白药 57.77 亿元",
+      "SQL": "SELECT stock_abbr, stock_code, report_year, report_period, asset_inventory FROM balance_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY asset_inventory DESC LIMIT 10",
       "image": "B1016_1.jpg"
     }
   ]
@@ -2068,10 +2524,14 @@
           <t>[{"Q": "2025年第三季度，“资产-应收账款”占“营业总收入”比例超过30%的公司有哪些？请列出股票代码、简称、应收账款占比（%）。"}]</t>
         </is>
       </c>
-      <c r="D18" s="1" t="inlineStr"/>
+      <c r="D18" s="1" t="inlineStr">
+        <is>
+          <t>SELECT stock_abbr, stock_code, report_year, report_period, asset_accounts_receivable FROM balance_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') AND asset_accounts_receivable &gt; 30.0 AND asset_accounts_receivable IS NOT NULL ORDER BY asset_accounts_receivable DESC LIMIT 50</t>
+        </is>
+      </c>
       <c r="E18" s="1" t="inlineStr">
         <is>
-          <t>table</t>
+          <t>bar</t>
         </is>
       </c>
       <c r="F18" s="1" t="inlineStr">
@@ -2082,15 +2542,19 @@
   "子问题": [
     {
       "Q": "2025年第三季度，“资产-应收账款”占“营业总收入”比例超过30%的公司有哪些？请列出股票代码、简称、应收账款占比（%）。",
-      "A": "澄清：请问要查询哪家公司？",
-      "SQL": "",
-      "image": ""
-    }
-  ]
-}</t>
-        </is>
-      </c>
-      <c r="G18" s="1" t="inlineStr"/>
+      "A": "符合条件共 50 家，前5：白云山(600332) 191.35 亿元; 云南白药(000538) 102.56 亿元; 华润三九(000999) 76.66 亿元; 瑞康医药(002589) 37.33 亿元; 昆药集团(600422) 31.20 亿元",
+      "SQL": "SELECT stock_abbr, stock_code, report_year, report_period, asset_accounts_receivable FROM balance_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') AND asset_accounts_receivable &gt; 30.0 AND asset_accounts_receivable IS NOT NULL ORDER BY asset_accounts_receivable DESC LIMIT 50",
+      "image": "B1017_1.jpg"
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G18" s="1" t="inlineStr">
+        <is>
+          <t>B1017_1.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="120" customHeight="1">
       <c r="A19" s="1" t="inlineStr">
@@ -2110,7 +2574,7 @@
       </c>
       <c r="D19" s="1" t="inlineStr">
         <is>
-          <t>SELECT stock_abbr, report_year, report_period, net_profit FROM income_sheet WHERE report_year IN (2025,2024) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END</t>
+          <t>SELECT stock_abbr, stock_code, report_year, report_period, net_profit_yoy_growth FROM income_sheet WHERE report_year IN (2025,2024) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END</t>
         </is>
       </c>
       <c r="E19" s="1" t="inlineStr">
@@ -2126,8 +2590,8 @@
   "子问题": [
     {
       "Q": "2025年第三季度，“净利润同比增长率”波动最大（即与2024年同期相比，增幅或降幅绝对值最大）的3家公司是哪些？请展示具体增长率。",
-      "A": "净利润 对比：赛隆药业 2024三季报 —; 贵州百灵 2025三季报 —; 东阿阿胶 2024三季报 —; 东阿阿胶 2025三季报 —; 云南白药 2024三季报 —; 云南白药 2025三季报 —; 启迪药业 2024三季报 —; 启迪药业 2025三季报 —; 仁和药业 2024三季报 —; 仁和药业 2025三季报 —; 通化金马 2024三季报 —; 通化金马 2025三季报 —; 华神科技 2024三季报 —; 华神科技 2025三季报 —; 九芝堂 2025三季报 —; 华润三九 2024三季报 —; 华润三九 2025三季报 —; 万邦德 2024三季报 —; 万邦德 2025三季报 —; 沃华医药 2024三季报 —; 沃华医药 2025三季报 —; 莱茵生物 2024三季报 —; 莱茵生物 2025三季报 —; 嘉应制药 2024三季报 —; 嘉应制药 2025三季报 —; 新里程 2024三季报 —; 新里程 2025三季报 —; 桂林三金 2024三季报 —; 桂林三金 2025三季报 —; 奇正藏药 2024三季报 —; 奇正藏药 2025三季报 —; 众生药业 2024三季报 —; 众生药业 2025三季报 —; 精华制药 2024三季报 —; 精华制药 2025三季报 —; 信邦制药 2024三季报 —; 信邦制药 2025三季报 —; 益盛药业 2024三季报 —; 益盛药业 2025三季报 —; 瑞康医药 2024三季报 —; 瑞康医药 2025三季报 —; 以岭药业 2024三季报 —; 以岭药业 2025三季报 —; 特一药业 2024三季报 —; 特一药业 2025三季报 —; 葵花药业 2024三季报 —; 葵花药业 2025三季报 —; 康弘药业 2024三季报 —; 康弘药业 2025三季报 —; 盘龙药业 2024三季报 —; 盘龙药业 2025三季报 —; 新天药业 2024三季报 —; 新天药业 2025三季报 —; 华森制药 2024三季报 —; 华森制药 2025三季报 —; 红日药业 2024三季报 —; 红日药业 2025三季报 —; 振东制药 2024三季报 —; 振东制药 2025三季报 —; 佐力药业 2024三季报 —; 佐力药业 2025三季报 —; 新光药业 2024三季报 —; 新光药业 2025三季报 —; 陇神戎发 2024三季报 —; 陇神戎发 2025三季报 —; 康泰医学 2024三季报 —; 康泰医学 2025三季报 —; 维康药业 2024三季报 —; 维康药业 2025三季报 —; 粤万年青 2024三季报 —; 粤万年青 2025三季报 —; 恩威医药 2024三季报 —; 恩威医药 2025三季报 —; 金花股份 2024三季报 3,077.02 万元; 金花股份 2025三季报 3,423.74 万元; 同仁堂 2024三季报 19.84 亿元; 同仁堂 2025三季报 15.93 亿元; 太极集团 2024三季报 5.52 亿元; 太极集团 2025三季报 1.64 亿元; 太龙药业 2024三季报 2,994.75 万元; 太龙药业 2025三季报 3,047.46 万元; 中恒集团 2024三季报 -918.55 万元; 中恒集团 2025三季报 -931.86 万元; 羚锐制药 2024三季报 5.74 亿元; 羚锐制药 2025三季报 6.54 亿元; 达仁堂 2024三季报 7.93 亿元; 达仁堂 2025三季报 21.46 亿元; 白云山 2024三季报 32.89 亿元; 白云山 2025三季报 33.98 亿元; 亚宝药业 2024三季报 2.28 亿元; 亚宝药业 2025三季报 1.98 亿元; 昆药集团 2024三季报 3.91 亿元; 昆药集团 2025三季报 3.23 亿元; 片仔癀 2024三季报 27.18 亿元; 片仔癀 2025三季报 21.33 亿元; 千金药业 2024三季报 2.13 亿元; 千金药业 2025三季报 2.58 亿元; 康美药业 2024三季报 811.09 万元; 康美药业 2025三季报 1,509.11 万元; 天士力 2024三季报 8.28 亿元; 天士力 2025三季报 9.93 亿元; 康缘药业 2024三季报 3.64 亿元; 康缘药业 2025三季报 2.08 亿元; 济川药业 2024三季报 19.07 亿元; 济川药业 2025三季报 10.24 亿元; 康恩贝 2024三季报 5.46 亿元; 康恩贝 2025三季报 5.96 亿元; 益佰制药 2024三季报 —; 益佰制药 2025三季报 -9,062.98 万元; 神奇制药 2024三季报 5,881.42 万元; 神奇制药 2025三季报 5,109.10 万元; 天目药业 2024三季报 -376.11 万元; 天目药业 2025三季报 750.81 万元; 江中药业 2024三季报 6.84 亿元; 江中药业 2025三季报 7.43 亿元; 广誉远 2024三季报 8,032.73 万元; 广誉远 2025三季报 8,215.46 万元; 健民集团 2024三季报 3.25 亿元; 健民集团 2025三季报 2.89 亿元; 马应龙 2024三季报 4.72 亿元; 马应龙 2025三季报 5.19 亿元; 康惠制药 2024三季报 -4,778.22 万元; 康惠制药 2025三季报 -1.57 亿元; 贵州三力 2024三季报 1.99 亿元; 贵州三力 2025三季报 8,367.73 万元; 珍宝岛 2024三季报 3.96 亿元; 珍宝岛 2025三季报 -3.76 亿元; 步长制药 2024三季报 —; 步长制药 2025三季报 7.91 亿元; 寿仙谷 2024三季报 1.19 亿元; 寿仙谷 2025三季报 7,634.62 万元; 方盛制药 2024三季报 2.27 亿元; 方盛制药 2025三季报 2.65 亿元",
-      "SQL": "SELECT stock_abbr, report_year, report_period, net_profit FROM income_sheet WHERE report_year IN (2025,2024) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
+      "A": "净利润同比 对比：赛隆药业 2024三季报 —; 贵州百灵 2025三季报 —; 东阿阿胶 2024三季报 —; 东阿阿胶 2025三季报 —; 云南白药 2024三季报 —; 云南白药 2025三季报 —; 启迪药业 2024三季报 —; 启迪药业 2025三季报 —; 仁和药业 2024三季报 —; 仁和药业 2025三季报 —; 通化金马 2024三季报 —; 通化金马 2025三季报 —; 华神科技 2024三季报 —; 华神科技 2025三季报 —; 九芝堂 2025三季报 —; 华润三九 2024三季报 —; 华润三九 2025三季报 —; 万邦德 2024三季报 —; 万邦德 2025三季报 —; 沃华医药 2024三季报 —; 沃华医药 2025三季报 —; 莱茵生物 2024三季报 —; 莱茵生物 2025三季报 —; 嘉应制药 2024三季报 —; 嘉应制药 2025三季报 —; 新里程 2024三季报 —; 新里程 2025三季报 —; 桂林三金 2024三季报 —; 桂林三金 2025三季报 —; 奇正藏药 2024三季报 —; 奇正藏药 2025三季报 —; 众生药业 2024三季报 —; 众生药业 2025三季报 —; 精华制药 2024三季报 —; 精华制药 2025三季报 —; 信邦制药 2024三季报 —; 信邦制药 2025三季报 —; 益盛药业 2024三季报 —; 益盛药业 2025三季报 —; 瑞康医药 2024三季报 —; 瑞康医药 2025三季报 —; 以岭药业 2024三季报 —; 以岭药业 2025三季报 —; 特一药业 2024三季报 —; 特一药业 2025三季报 —; 葵花药业 2024三季报 —; 葵花药业 2025三季报 —; 康弘药业 2024三季报 —; 康弘药业 2025三季报 —; 盘龙药业 2024三季报 —; 盘龙药业 2025三季报 —; 新天药业 2024三季报 —; 新天药业 2025三季报 —; 华森制药 2024三季报 —; 华森制药 2025三季报 —; 红日药业 2024三季报 —; 红日药业 2025三季报 —; 振东制药 2024三季报 —; 振东制药 2025三季报 —; 佐力药业 2024三季报 —; 佐力药业 2025三季报 —; 新光药业 2024三季报 —; 新光药业 2025三季报 —; 陇神戎发 2024三季报 —; 陇神戎发 2025三季报 —; 康泰医学 2024三季报 —; 康泰医学 2025三季报 —; 维康药业 2024三季报 —; 维康药业 2025三季报 —; 粤万年青 2024三季报 —; 粤万年青 2025三季报 —; 恩威医药 2024三季报 —; 恩威医药 2025三季报 —; 金花股份 2024三季报 —; 金花股份 2025三季报 —; 同仁堂 2024三季报 —; 同仁堂 2025三季报 —; 太极集团 2024三季报 —; 太极集团 2025三季报 —; 太龙药业 2024三季报 —; 太龙药业 2025三季报 —; 中恒集团 2024三季报 —; 中恒集团 2025三季报 —; 羚锐制药 2024三季报 —; 羚锐制药 2025三季报 —; 达仁堂 2024三季报 —; 达仁堂 2025三季报 —; 白云山 2024三季报 —; 白云山 2025三季报 —; 亚宝药业 2024三季报 —; 亚宝药业 2025三季报 —; 昆药集团 2024三季报 —; 昆药集团 2025三季报 —; 片仔癀 2024三季报 —; 片仔癀 2025三季报 —; 千金药业 2024三季报 —; 千金药业 2025三季报 —; 康美药业 2024三季报 —; 康美药业 2025三季报 —; 天士力 2024三季报 —; 天士力 2025三季报 —; 康缘药业 2024三季报 —; 康缘药业 2025三季报 —; 济川药业 2024三季报 —; 济川药业 2025三季报 —; 康恩贝 2024三季报 —; 康恩贝 2025三季报 —; 益佰制药 2024三季报 —; 益佰制药 2025三季报 —; 神奇制药 2024三季报 —; 神奇制药 2025三季报 —; 天目药业 2024三季报 —; 天目药业 2025三季报 —; 江中药业 2024三季报 —; 江中药业 2025三季报 —; 广誉远 2024三季报 —; 广誉远 2025三季报 —; 健民集团 2024三季报 —; 健民集团 2025三季报 —; 马应龙 2024三季报 —; 马应龙 2025三季报 —; 康惠制药 2024三季报 —; 康惠制药 2025三季报 —; 贵州三力 2024三季报 —; 贵州三力 2025三季报 —; 珍宝岛 2024三季报 —; 珍宝岛 2025三季报 —; 步长制药 2024三季报 —; 步长制药 2025三季报 —; 寿仙谷 2024三季报 —; 寿仙谷 2025三季报 —; 方盛制药 2024三季报 —; 方盛制药 2025三季报 —",
+      "SQL": "SELECT stock_abbr, stock_code, report_year, report_period, net_profit_yoy_growth FROM income_sheet WHERE report_year IN (2025,2024) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
       "image": "B1018_1.jpg"
     }
   ]
@@ -2158,7 +2622,7 @@
       </c>
       <c r="D20" s="1" t="inlineStr">
         <is>
-          <t>SELECT stock_abbr, report_year, report_period, total_operating_revenue FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY total_operating_revenue DESC LIMIT 10</t>
+          <t>SELECT stock_abbr, stock_code, report_year, report_period, total_operating_expenses FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY total_operating_expenses DESC LIMIT 10</t>
         </is>
       </c>
       <c r="E20" s="1" t="inlineStr">
@@ -2174,8 +2638,8 @@
   "子问题": [
     {
       "Q": "2025年第三季度，“营业总支出-研发费用”占“营业总收入”比例排名前五的公司有哪些？请列出简称、研发费用占比（%）。",
-      "A": "营业总收入 排名 Top5：1) 白云山 616.06 亿元; 2) 同仁堂 133.08 亿元; 3) 步长制药 84.69 亿元; 4) 太极集团 80.88 亿元; 5) 片仔癀 74.42 亿元",
-      "SQL": "SELECT stock_abbr, report_year, report_period, total_operating_revenue FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY total_operating_revenue DESC LIMIT 10",
+      "A": "营业总支出 排名 Top5：1) 白云山 577.75 亿元; 2) 同仁堂 113.18 亿元; 3) 太极集团 79.46 亿元; 4) 步长制药 75.32 亿元; 5) 片仔癀 53.24 亿元",
+      "SQL": "SELECT stock_abbr, stock_code, report_year, report_period, total_operating_expenses FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY total_operating_expenses DESC LIMIT 10",
       "image": "B1019_1.jpg"
     }
   ]
@@ -2206,7 +2670,7 @@
       </c>
       <c r="D21" s="1" t="inlineStr">
         <is>
-          <t>SELECT stock_abbr, report_year, report_period, net_profit FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY net_profit DESC LIMIT 10</t>
+          <t>SELECT stock_abbr, stock_code, report_year, report_period, equity_unappropriated_profit FROM balance_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY equity_unappropriated_profit DESC LIMIT 10</t>
         </is>
       </c>
       <c r="E21" s="1" t="inlineStr">
@@ -2222,8 +2686,8 @@
   "子问题": [
     {
       "Q": "2025年第三季度，“股东权益-未分配利润”金额排名前五的公司，其2025年的“净利润”占未分配利润的比例是多少？请展示具体数值。",
-      "A": "净利润 排名 Top5：1) 白云山 33.98 亿元; 2) 达仁堂 21.46 亿元; 3) 片仔癀 21.33 亿元; 4) 同仁堂 15.93 亿元; 5) 济川药业 10.24 亿元",
-      "SQL": "SELECT stock_abbr, report_year, report_period, net_profit FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY net_profit DESC LIMIT 10",
+      "A": "未分配利润 排名 Top5：1) 云南白药 178.26 亿元; 2) 华润三九 172.56 亿元; 3) 片仔癀 107.93 亿元; 4) 东阿阿胶 85.54 亿元; 5) 以岭药业 57.80 亿元",
+      "SQL": "SELECT stock_abbr, stock_code, report_year, report_period, equity_unappropriated_profit FROM balance_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY equity_unappropriated_profit DESC LIMIT 10",
       "image": "B1020_1.jpg"
     }
   ]
@@ -2334,7 +2798,7 @@
       </c>
       <c r="D24" s="1" t="inlineStr">
         <is>
-          <t>SELECT stock_abbr, report_year, report_period, total_operating_revenue FROM income_sheet WHERE report_year IN (2022,2025) AND report_period IN ('Q3') ORDER BY total_operating_revenue DESC LIMIT 10</t>
+          <t>SELECT stock_abbr, stock_code, report_year, report_period, total_operating_revenue FROM income_sheet WHERE report_year IN (2022,2025) AND report_period IN ('Q3') ORDER BY total_operating_revenue DESC LIMIT 10</t>
         </is>
       </c>
       <c r="E24" s="1" t="inlineStr">
@@ -2351,7 +2815,7 @@
     {
       "Q": "计算2022年财报至2025年第三季度，66家公司的营业总收入复合增长率，排名前三的公司是哪些？请展示复合增长率（%）。",
       "A": "营业总收入 排名 Top5：1) 白云山 616.06 亿元; 2) 同仁堂 133.08 亿元; 3) 步长制药 84.69 亿元; 4) 太极集团 80.88 亿元; 5) 片仔癀 74.42 亿元",
-      "SQL": "SELECT stock_abbr, report_year, report_period, total_operating_revenue FROM income_sheet WHERE report_year IN (2022,2025) AND report_period IN ('Q3') ORDER BY total_operating_revenue DESC LIMIT 10",
+      "SQL": "SELECT stock_abbr, stock_code, report_year, report_period, total_operating_revenue FROM income_sheet WHERE report_year IN (2022,2025) AND report_period IN ('Q3') ORDER BY total_operating_revenue DESC LIMIT 10",
       "image": "B1023_1.jpg"
     }
   ]
@@ -2422,12 +2886,12 @@
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
-          <t>SELECT stock_abbr, report_year, report_period, net_cash_flow FROM cash_flow_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY net_cash_flow DESC LIMIT 10</t>
+          <t>SELECT COUNT(*) AS 数量 FROM cash_flow_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') AND net_cash_flow &gt; 0 AND net_cash_flow IS NOT NULL</t>
         </is>
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
-          <t>bar</t>
+          <t>table</t>
         </is>
       </c>
       <c r="F26" s="1" t="inlineStr">
@@ -2438,8 +2902,8 @@
   "子问题": [
     {
       "Q": "2025年第三季度，“投资性现金流量净额”为正数（即投资现金流入大于流出）的公司有多少家？请列出其中营收排名前三的公司简称及投资现金流净额（万元）。",
-      "A": "现金流净额 排名 Top5：1) 广誉远 1.80 亿元; 2) 太龙药业 1.75 亿元; 3) 江中药业 1.15 亿元; 4) 益佰制药 7,268.83 万元; 5) 亚宝药业 6,714.99 万元",
-      "SQL": "SELECT stock_abbr, report_year, report_period, net_cash_flow FROM cash_flow_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY net_cash_flow DESC LIMIT 10",
+      "A": "共 8 家",
+      "SQL": "SELECT COUNT(*) AS 数量 FROM cash_flow_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') AND net_cash_flow &gt; 0 AND net_cash_flow IS NOT NULL",
       "image": "B1025_1.jpg"
     }
   ]
@@ -2470,12 +2934,12 @@
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
-          <t>SELECT stock_abbr, report_year, report_period, net_profit FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY net_profit DESC LIMIT 10</t>
+          <t>SELECT AVG(total_operating_expenses) AS total_operating_expenses_avg FROM income_sheet WHERE total_operating_expenses IS NOT NULL AND report_year IN (2025) AND report_period IN ('Q3')</t>
         </is>
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
-          <t>bar</t>
+          <t>table</t>
         </is>
       </c>
       <c r="F27" s="1" t="inlineStr">
@@ -2486,8 +2950,8 @@
   "子问题": [
     {
       "Q": "2025年第三季度，“营业总支出-销售费用”占“营业总收入”比例低于行业均值的公司中，“净利润”最高的3家是哪些？请同步展示行业均值。",
-      "A": "净利润 排名 Top5：1) 白云山 33.98 亿元; 2) 达仁堂 21.46 亿元; 3) 片仔癀 21.33 亿元; 4) 同仁堂 15.93 亿元; 5) 济川药业 10.24 亿元",
-      "SQL": "SELECT stock_abbr, report_year, report_period, net_profit FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY net_profit DESC LIMIT 10",
+      "A": "营业总支出均值：46.76 亿元",
+      "SQL": "SELECT AVG(total_operating_expenses) AS total_operating_expenses_avg FROM income_sheet WHERE total_operating_expenses IS NOT NULL AND report_year IN (2025) AND report_period IN ('Q3')",
       "image": "B1026_1.jpg"
     }
   ]
@@ -2558,7 +3022,7 @@
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
-          <t>SELECT stock_abbr, report_year, report_period, net_profit FROM income_sheet WHERE (stock_abbr='白云山' OR stock_abbr='云南白药' OR stock_abbr='片仔癀' OR stock_code='600332' OR stock_code='000538' OR stock_code='600436') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END</t>
+          <t>SELECT stock_abbr, stock_code, report_year, report_period, net_profit FROM income_sheet WHERE (stock_abbr='白云山' OR stock_abbr='云南白药' OR stock_abbr='片仔癀' OR stock_code='600332' OR stock_code='000538' OR stock_code='600436') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END</t>
         </is>
       </c>
       <c r="E29" s="1" t="inlineStr">
@@ -2575,7 +3039,7 @@
     {
       "Q": "对比白云山（600332）、云南白药（000538）、片仔癀（600436）2022-2025年第三季度的“净利润（万元）”，生成多系列折线图展示趋势。",
       "A": "白云山的净利润从2025三季报的 33.98 亿元 变化到2025三季报的 21.33 亿元（-37.22%）",
-      "SQL": "SELECT stock_abbr, report_year, report_period, net_profit FROM income_sheet WHERE (stock_abbr='白云山' OR stock_abbr='云南白药' OR stock_abbr='片仔癀' OR stock_code='600332' OR stock_code='000538' OR stock_code='600436') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
+      "SQL": "SELECT stock_abbr, stock_code, report_year, report_period, net_profit FROM income_sheet WHERE (stock_abbr='白云山' OR stock_abbr='云南白药' OR stock_abbr='片仔癀' OR stock_code='600332' OR stock_code='000538' OR stock_code='600436') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
       "image": "B1028_1.jpg"
     }
   ]
@@ -2606,7 +3070,7 @@
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
-          <t>SELECT stock_abbr, report_year, report_period, total_operating_revenue FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY total_operating_revenue DESC LIMIT 10</t>
+          <t>SELECT stock_abbr, stock_code, report_year, report_period, total_operating_revenue FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY total_operating_revenue DESC LIMIT 10</t>
         </is>
       </c>
       <c r="E30" s="1" t="inlineStr">
@@ -2623,7 +3087,7 @@
     {
       "Q": "2025年第三季度所有上市公司的股票代码、公司简称和营业总收入（单位：万元），按营业总收入从高到低排序。",
       "A": "营业总收入 排名 Top5：1) 白云山 616.06 亿元; 2) 同仁堂 133.08 亿元; 3) 步长制药 84.69 亿元; 4) 太极集团 80.88 亿元; 5) 片仔癀 74.42 亿元",
-      "SQL": "SELECT stock_abbr, report_year, report_period, total_operating_revenue FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY total_operating_revenue DESC LIMIT 10",
+      "SQL": "SELECT stock_abbr, stock_code, report_year, report_period, total_operating_revenue FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY total_operating_revenue DESC LIMIT 10",
       "image": "B1029_1.jpg"
     }
   ]
@@ -2654,7 +3118,7 @@
       </c>
       <c r="D31" s="1" t="inlineStr">
         <is>
-          <t>SELECT stock_abbr, report_year, report_period, equity_total_equity FROM balance_sheet WHERE (stock_abbr='片仔癀' OR stock_code='600436') AND report_year IN (2022) AND report_period IN ('FY') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END</t>
+          <t>SELECT stock_abbr, stock_code, report_year, report_period, equity_total_equity FROM balance_sheet WHERE (stock_abbr='片仔癀' OR stock_code='600436') AND report_year IN (2022) AND report_period IN ('FY') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END</t>
         </is>
       </c>
       <c r="E31" s="1" t="inlineStr">
@@ -2671,7 +3135,7 @@
     {
       "Q": "从资产负债表中提取片仔癀（600436）2022年全年的资产总额、负债总额、股东权益总额（单位：万元）",
       "A": "片仔癀 2022年报的股东权益为 —",
-      "SQL": "SELECT stock_abbr, report_year, report_period, equity_total_equity FROM balance_sheet WHERE (stock_abbr='片仔癀' OR stock_code='600436') AND report_year IN (2022) AND report_period IN ('FY') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
+      "SQL": "SELECT stock_abbr, stock_code, report_year, report_period, equity_total_equity FROM balance_sheet WHERE (stock_abbr='片仔癀' OR stock_code='600436') AND report_year IN (2022) AND report_period IN ('FY') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
       "image": "B1030_1.jpg"
     }
   ]
@@ -2700,7 +3164,11 @@
           <t>[{"Q": "统计2025年第三季度净利润为负数的中药公司数量，并列出这些公司的股票代码和简称。"}]</t>
         </is>
       </c>
-      <c r="D32" s="1" t="inlineStr"/>
+      <c r="D32" s="1" t="inlineStr">
+        <is>
+          <t>SELECT COUNT(*) AS 数量 FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') AND net_profit &lt; 0 AND net_profit IS NOT NULL</t>
+        </is>
+      </c>
       <c r="E32" s="1" t="inlineStr">
         <is>
           <t>table</t>
@@ -2714,15 +3182,19 @@
   "子问题": [
     {
       "Q": "统计2025年第三季度净利润为负数的中药公司数量，并列出这些公司的股票代码和简称。",
-      "A": "澄清：请问要查询哪家公司？",
-      "SQL": "",
-      "image": ""
-    }
-  ]
-}</t>
-        </is>
-      </c>
-      <c r="G32" s="1" t="inlineStr"/>
+      "A": "共 4 家",
+      "SQL": "SELECT COUNT(*) AS 数量 FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') AND net_profit &lt; 0 AND net_profit IS NOT NULL",
+      "image": "B1031_1.jpg"
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G32" s="1" t="inlineStr">
+        <is>
+          <t>B1031_1.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="120" customHeight="1">
       <c r="A33" s="1" t="inlineStr">
@@ -2742,7 +3214,7 @@
       </c>
       <c r="D33" s="1" t="inlineStr">
         <is>
-          <t>SELECT stock_abbr, report_year, report_period, total_operating_revenue FROM income_sheet WHERE (stock_code='000100') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END</t>
+          <t>SELECT stock_abbr, stock_code, report_year, report_period, operating_expense_cost_of_sales FROM income_sheet WHERE (stock_code='000100') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END</t>
         </is>
       </c>
       <c r="E33" s="1" t="inlineStr">
@@ -2759,7 +3231,7 @@
     {
       "Q": "关联核心业绩指标表和利润表，查询2025年第三季度每家公司的股票代码、简称、营业总收入（取自核心业绩指标表）、销售毛利率（利润表中（营业收入-营业成本）/营业收入*100），保留两位小数。",
       "A": "未查询到数据",
-      "SQL": "SELECT stock_abbr, report_year, report_period, total_operating_revenue FROM income_sheet WHERE (stock_code='000100') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
+      "SQL": "SELECT stock_abbr, stock_code, report_year, report_period, operating_expense_cost_of_sales FROM income_sheet WHERE (stock_code='000100') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
       "image": ""
     }
   ]
@@ -2826,7 +3298,7 @@
       </c>
       <c r="D35" s="1" t="inlineStr">
         <is>
-          <t>SELECT stock_abbr, report_year, report_period, total_operating_revenue FROM income_sheet WHERE (stock_abbr='云南白药' OR stock_code='000538' OR stock_code='000100') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END</t>
+          <t>SELECT stock_abbr, stock_code, report_year, report_period, total_operating_revenue FROM income_sheet WHERE (stock_abbr='云南白药' OR stock_code='000538' OR stock_code='000100') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END</t>
         </is>
       </c>
       <c r="E35" s="1" t="inlineStr">
@@ -2843,7 +3315,7 @@
     {
       "Q": "计算云南白药（000538）2025年第三季度营业总收入的环比增长率（环比增长率=(本季度值-上季度值)/上季度值*100），并展示2025年第二季度和第三季度的营业总收入（万元）及环比增长率（保留两位小数）。",
       "A": "云南白药 2025三季报的营业总收入为 —",
-      "SQL": "SELECT stock_abbr, report_year, report_period, total_operating_revenue FROM income_sheet WHERE (stock_abbr='云南白药' OR stock_code='000538' OR stock_code='000100') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
+      "SQL": "SELECT stock_abbr, stock_code, report_year, report_period, total_operating_revenue FROM income_sheet WHERE (stock_abbr='云南白药' OR stock_code='000538' OR stock_code='000100') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
       "image": "B1034_1.jpg"
     }
   ]
@@ -2874,12 +3346,12 @@
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
-          <t>SELECT stock_abbr, report_year, report_period, net_profit FROM income_sheet WHERE (stock_code='000100') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END</t>
+          <t>SELECT stock_abbr, stock_code, report_year, report_period, net_profit_yoy_growth FROM income_sheet WHERE (stock_code='000100') AND report_year IN (2025) AND report_period IN ('Q3') AND net_profit_yoy_growth &gt; 50.0 AND net_profit_yoy_growth IS NOT NULL ORDER BY net_profit_yoy_growth DESC LIMIT 50</t>
         </is>
       </c>
       <c r="E36" s="1" t="inlineStr">
         <is>
-          <t>table</t>
+          <t>bar</t>
         </is>
       </c>
       <c r="F36" s="1" t="inlineStr">
@@ -2891,7 +3363,7 @@
     {
       "Q": "统计2025年第三季度各公司净利润同比增长率（同比增长率=(2025Q3值-2024Q3值)/2024Q3值*100），找出同比增长率超过50%的公司，列出股票代码、简称和同比增长率",
       "A": "未查询到数据",
-      "SQL": "SELECT stock_abbr, report_year, report_period, net_profit FROM income_sheet WHERE (stock_code='000100') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
+      "SQL": "SELECT stock_abbr, stock_code, report_year, report_period, net_profit_yoy_growth FROM income_sheet WHERE (stock_code='000100') AND report_year IN (2025) AND report_period IN ('Q3') AND net_profit_yoy_growth &gt; 50.0 AND net_profit_yoy_growth IS NOT NULL ORDER BY net_profit_yoy_growth DESC LIMIT 50",
       "image": ""
     }
   ]
@@ -2918,12 +3390,12 @@
       </c>
       <c r="D37" s="1" t="inlineStr">
         <is>
-          <t>SELECT stock_abbr, report_year, report_period, asset_liability_ratio FROM balance_sheet WHERE (stock_code='000100') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY asset_liability_ratio DESC LIMIT 10</t>
+          <t>SELECT AVG(asset_liability_ratio) AS asset_liability_ratio_avg FROM balance_sheet WHERE asset_liability_ratio IS NOT NULL AND report_year IN (2025) AND report_period IN ('Q3')</t>
         </is>
       </c>
       <c r="E37" s="1" t="inlineStr">
         <is>
-          <t>bar</t>
+          <t>table</t>
         </is>
       </c>
       <c r="F37" s="1" t="inlineStr">
@@ -2934,15 +3406,19 @@
   "子问题": [
     {
       "Q": "计算2025年第三季度66家中药公司的资产负债率（负债总额/资产总额*100）行业均值，同时列出资产负债率最高的前10家公司的股票代码、简称和资产负债率（保留两位小数）。",
-      "A": "未查询到数据",
-      "SQL": "SELECT stock_abbr, report_year, report_period, asset_liability_ratio FROM balance_sheet WHERE (stock_code='000100') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY asset_liability_ratio DESC LIMIT 10",
-      "image": ""
-    }
-  ]
-}</t>
-        </is>
-      </c>
-      <c r="G37" s="1" t="inlineStr"/>
+      "A": "资产负债率均值：—",
+      "SQL": "SELECT AVG(asset_liability_ratio) AS asset_liability_ratio_avg FROM balance_sheet WHERE asset_liability_ratio IS NOT NULL AND report_year IN (2025) AND report_period IN ('Q3')",
+      "image": "B1036_1.jpg"
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G37" s="1" t="inlineStr">
+        <is>
+          <t>B1036_1.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="120" customHeight="1">
       <c r="A38" s="1" t="inlineStr">
@@ -2962,7 +3438,7 @@
       </c>
       <c r="D38" s="1" t="inlineStr">
         <is>
-          <t>SELECT stock_abbr, report_year, report_period, net_profit FROM income_sheet WHERE (stock_code='000100') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END</t>
+          <t>SELECT COUNT(*) AS 数量 FROM core_performance_indicators_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') AND net_profit_margin IS NOT NULL</t>
         </is>
       </c>
       <c r="E38" s="1" t="inlineStr">
@@ -2978,15 +3454,19 @@
   "子问题": [
     {
       "Q": "按2025年第三季度的销售净利率（净利润/营业总收入*100）分组，统计销售净利率在0-5%、5%-10%、10%以上三个区间的公司数量。",
-      "A": "未查询到数据",
-      "SQL": "SELECT stock_abbr, report_year, report_period, net_profit FROM income_sheet WHERE (stock_code='000100') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
-      "image": ""
-    }
-  ]
-}</t>
-        </is>
-      </c>
-      <c r="G38" s="1" t="inlineStr"/>
+      "A": "共 0 家",
+      "SQL": "SELECT COUNT(*) AS 数量 FROM core_performance_indicators_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') AND net_profit_margin IS NOT NULL",
+      "image": "B1037_1.jpg"
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G38" s="1" t="inlineStr">
+        <is>
+          <t>B1037_1.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="120" customHeight="1">
       <c r="A39" s="1" t="inlineStr">
@@ -3006,12 +3486,12 @@
       </c>
       <c r="D39" s="1" t="inlineStr">
         <is>
-          <t>SELECT stock_abbr, report_year, report_period, total_operating_revenue FROM income_sheet WHERE (stock_code='100000') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END</t>
+          <t>SELECT stock_abbr, stock_code, report_year, report_period, asset_liability_ratio FROM balance_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') AND asset_liability_ratio &gt; 10.0 AND asset_liability_ratio &lt; 40.0 AND asset_liability_ratio &gt; 0 AND asset_liability_ratio IS NOT NULL ORDER BY asset_liability_ratio DESC LIMIT 50</t>
         </is>
       </c>
       <c r="E39" s="1" t="inlineStr">
         <is>
-          <t>table</t>
+          <t>bar</t>
         </is>
       </c>
       <c r="F39" s="1" t="inlineStr">
@@ -3023,7 +3503,7 @@
     {
       "Q": "查询2025年第三季度满足以下条件的公司：营业总收入超过10亿元（即100000万元）、资产负债率低于40%、经营性现金流量净额为正，列出股票代码、简称、营业总收入、资产负债率、经营性现金流量净额。",
       "A": "未查询到数据",
-      "SQL": "SELECT stock_abbr, report_year, report_period, total_operating_revenue FROM income_sheet WHERE (stock_code='100000') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
+      "SQL": "SELECT stock_abbr, stock_code, report_year, report_period, asset_liability_ratio FROM balance_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') AND asset_liability_ratio &gt; 10.0 AND asset_liability_ratio &lt; 40.0 AND asset_liability_ratio &gt; 0 AND asset_liability_ratio IS NOT NULL ORDER BY asset_liability_ratio DESC LIMIT 50",
       "image": ""
     }
   ]
@@ -3048,10 +3528,14 @@
           <t>[{"Q": "找出2022-2025年第三季度期间，连续四个报告期扣非净利润均超过1亿元的公司，列出股票代码、简称及各报告期的扣非净利润（万元）"}]</t>
         </is>
       </c>
-      <c r="D40" s="1" t="inlineStr"/>
+      <c r="D40" s="1" t="inlineStr">
+        <is>
+          <t>SELECT stock_abbr, stock_code, report_year, report_period, net_profit_excl_non_recurring FROM core_performance_indicators_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') AND net_profit_excl_non_recurring &gt; 10000.0 AND net_profit_excl_non_recurring IS NOT NULL ORDER BY net_profit_excl_non_recurring DESC LIMIT 50</t>
+        </is>
+      </c>
       <c r="E40" s="1" t="inlineStr">
         <is>
-          <t>table</t>
+          <t>bar</t>
         </is>
       </c>
       <c r="F40" s="1" t="inlineStr">
@@ -3062,8 +3546,8 @@
   "子问题": [
     {
       "Q": "找出2022-2025年第三季度期间，连续四个报告期扣非净利润均超过1亿元的公司，列出股票代码、简称及各报告期的扣非净利润（万元）",
-      "A": "澄清：请问要查询哪家公司？",
-      "SQL": "",
+      "A": "未查询到数据",
+      "SQL": "SELECT stock_abbr, stock_code, report_year, report_period, net_profit_excl_non_recurring FROM core_performance_indicators_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') AND net_profit_excl_non_recurring &gt; 10000.0 AND net_profit_excl_non_recurring IS NOT NULL ORDER BY net_profit_excl_non_recurring DESC LIMIT 50",
       "image": ""
     }
   ]
@@ -3090,7 +3574,7 @@
       </c>
       <c r="D41" s="1" t="inlineStr">
         <is>
-          <t>SELECT stock_abbr, report_year, report_period, asset_total_assets FROM balance_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY asset_total_assets DESC LIMIT 10</t>
+          <t>SELECT stock_abbr, stock_code, report_year, report_period, asset_total_assets FROM balance_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') AND asset_total_assets &gt; 20.0 AND asset_total_assets &lt; 0 AND asset_total_assets IS NOT NULL ORDER BY asset_total_assets DESC LIMIT 10</t>
         </is>
       </c>
       <c r="E41" s="1" t="inlineStr">
@@ -3106,19 +3590,15 @@
   "子问题": [
     {
       "Q": "关联资产负债表和现金流量表，查询2025年第三季度货币资金占总资产比例超过20%，且投资性现金流量净额为负数的公司，按货币资金占比从高到低排序。",
-      "A": "总资产 排名 Top5：1) 白云山 831.69 亿元; 2) 华润三九 565.64 亿元; 3) 云南白药 533.43 亿元; 4) 同仁堂 318.19 亿元; 5) 步长制药 195.70 亿元",
-      "SQL": "SELECT stock_abbr, report_year, report_period, asset_total_assets FROM balance_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY asset_total_assets DESC LIMIT 10",
-      "image": "B1040_1.jpg"
-    }
-  ]
-}</t>
-        </is>
-      </c>
-      <c r="G41" s="1" t="inlineStr">
-        <is>
-          <t>B1040_1.jpg</t>
-        </is>
-      </c>
+      "A": "未查询到数据",
+      "SQL": "SELECT stock_abbr, stock_code, report_year, report_period, asset_total_assets FROM balance_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') AND asset_total_assets &gt; 20.0 AND asset_total_assets &lt; 0 AND asset_total_assets IS NOT NULL ORDER BY asset_total_assets DESC LIMIT 10",
+      "image": ""
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G41" s="1" t="inlineStr"/>
     </row>
     <row r="42" ht="120" customHeight="1">
       <c r="A42" s="1" t="inlineStr">
@@ -3178,7 +3658,7 @@
       </c>
       <c r="D43" s="1" t="inlineStr">
         <is>
-          <t>SELECT stock_abbr, report_year, report_period, total_operating_revenue FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY total_operating_revenue DESC LIMIT 10</t>
+          <t>SELECT stock_abbr, stock_code, report_year, report_period, operating_expense_rnd_expenses FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY operating_expense_rnd_expenses DESC LIMIT 10</t>
         </is>
       </c>
       <c r="E43" s="1" t="inlineStr">
@@ -3194,8 +3674,8 @@
   "子问题": [
     {
       "Q": "统计2025年第三季度研发费用占营业总收入比例最高的5家公司，要求同时展示研发费用（万元）、营业总收入（万元）、研发费用占比（保留两位小数）",
-      "A": "营业总收入 排名 Top5：1) 白云山 616.06 亿元; 2) 同仁堂 133.08 亿元; 3) 步长制药 84.69 亿元; 4) 太极集团 80.88 亿元; 5) 片仔癀 74.42 亿元",
-      "SQL": "SELECT stock_abbr, report_year, report_period, total_operating_revenue FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY total_operating_revenue DESC LIMIT 10",
+      "A": "研发费用 排名 Top5：1) 天士力 5.53 亿元; 2) 白云山 4.44 亿元; 3) 康缘药业 3.52 亿元; 4) 济川药业 2.72 亿元; 5) 太极集团 1.95 亿元",
+      "SQL": "SELECT stock_abbr, stock_code, report_year, report_period, operating_expense_rnd_expenses FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY operating_expense_rnd_expenses DESC LIMIT 10",
       "image": "B1042_1.jpg"
     }
   ]
@@ -3224,7 +3704,11 @@
           <t>[{"Q": "计算2025年第三季度66家公司的净利润中位数，找出净利润高于中位数且销售毛利率低于行业均值的公司，列出股票代码、简称、净利润、销售毛利率。"}]</t>
         </is>
       </c>
-      <c r="D44" s="1" t="inlineStr"/>
+      <c r="D44" s="1" t="inlineStr">
+        <is>
+          <t>SELECT AVG(gross_profit_margin) AS gross_profit_margin_avg FROM core_performance_indicators_sheet WHERE gross_profit_margin IS NOT NULL AND report_year IN (2025) AND report_period IN ('Q3')</t>
+        </is>
+      </c>
       <c r="E44" s="1" t="inlineStr">
         <is>
           <t>table</t>
@@ -3238,15 +3722,19 @@
   "子问题": [
     {
       "Q": "计算2025年第三季度66家公司的净利润中位数，找出净利润高于中位数且销售毛利率低于行业均值的公司，列出股票代码、简称、净利润、销售毛利率。",
-      "A": "澄清：请问要查询哪家公司？",
-      "SQL": "",
-      "image": ""
-    }
-  ]
-}</t>
-        </is>
-      </c>
-      <c r="G44" s="1" t="inlineStr"/>
+      "A": "毛利率均值：—",
+      "SQL": "SELECT AVG(gross_profit_margin) AS gross_profit_margin_avg FROM core_performance_indicators_sheet WHERE gross_profit_margin IS NOT NULL AND report_year IN (2025) AND report_period IN ('Q3')",
+      "image": "B1043_1.jpg"
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G44" s="1" t="inlineStr">
+        <is>
+          <t>B1043_1.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="120" customHeight="1">
       <c r="A45" s="1" t="inlineStr">
@@ -3266,7 +3754,7 @@
       </c>
       <c r="D45" s="1" t="inlineStr">
         <is>
-          <t>SELECT stock_abbr, report_year, report_period, total_operating_revenue FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END</t>
+          <t>SELECT AVG(net_profit_yoy_growth) AS net_profit_yoy_growth_avg FROM income_sheet WHERE net_profit_yoy_growth IS NOT NULL AND report_year IN (2025) AND report_period IN ('Q3')</t>
         </is>
       </c>
       <c r="E45" s="1" t="inlineStr">
@@ -3283,7 +3771,7 @@
     {
       "Q": "2025年第三季度营业总收入排名前五的中药公司有哪些？",
       "A": "营业总收入 排名 Top5：1) 白云山 616.06 亿元; 2) 同仁堂 133.08 亿元; 3) 步长制药 84.69 亿元; 4) 太极集团 80.88 亿元; 5) 片仔癀 74.42 亿元",
-      "SQL": "SELECT stock_abbr, report_year, report_period, total_operating_revenue FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY total_operating_revenue DESC LIMIT 10",
+      "SQL": "SELECT stock_abbr, stock_code, report_year, report_period, total_operating_revenue FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY total_operating_revenue DESC LIMIT 10",
       "image": "B1044_1.jpg"
     },
     {
@@ -3294,8 +3782,8 @@
     },
     {
       "Q": "它们的净利润同比增长率和行业均值相比如何",
-      "A": "金花股份的营业总收入从2025三季报的 3.84 亿元 变化到2025三季报的 12.53 亿元（+226.46%）",
-      "SQL": "SELECT stock_abbr, report_year, report_period, total_operating_revenue FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
+      "A": "净利润同比均值：—",
+      "SQL": "SELECT AVG(net_profit_yoy_growth) AS net_profit_yoy_growth_avg FROM income_sheet WHERE net_profit_yoy_growth IS NOT NULL AND report_year IN (2025) AND report_period IN ('Q3')",
       "image": "B1044_3.jpg"
     }
   ]
@@ -3326,7 +3814,7 @@
       </c>
       <c r="D46" s="1" t="inlineStr">
         <is>
-          <t>SELECT stock_abbr, report_year, report_period, asset_liability_ratio FROM balance_sheet WHERE (stock_abbr='云南白药' OR stock_abbr='白云山') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END</t>
+          <t>SELECT stock_abbr, stock_code, report_year, report_period, asset_liability_ratio FROM balance_sheet WHERE (stock_abbr='云南白药' OR stock_abbr='白云山') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END</t>
         </is>
       </c>
       <c r="E46" s="1" t="inlineStr">
@@ -3343,19 +3831,19 @@
     {
       "Q": "云南白药2022-2025年第三季度的资产负债率变化趋势",
       "A": "未查询到有效数据",
-      "SQL": "SELECT stock_abbr, report_year, report_period, asset_liability_ratio FROM balance_sheet WHERE (stock_abbr='云南白药') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
+      "SQL": "SELECT stock_abbr, stock_code, report_year, report_period, asset_liability_ratio FROM balance_sheet WHERE (stock_abbr='云南白药') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
       "image": "B1045_1.jpg"
     },
     {
       "Q": "这个趋势和白云山的同期变化趋势对比，差异在哪里",
       "A": "未查询到有效数据",
-      "SQL": "SELECT stock_abbr, report_year, report_period, asset_liability_ratio FROM balance_sheet WHERE (stock_abbr='云南白药' OR stock_abbr='白云山') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
+      "SQL": "SELECT stock_abbr, stock_code, report_year, report_period, asset_liability_ratio FROM balance_sheet WHERE (stock_abbr='云南白药' OR stock_abbr='白云山') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
       "image": "B1045_2.jpg"
     },
     {
       "Q": "导致两者差异的核心财务指标（如负债总额、资产总额）变化是什么",
       "A": "未查询到有效数据",
-      "SQL": "SELECT stock_abbr, report_year, report_period, asset_liability_ratio FROM balance_sheet WHERE (stock_abbr='云南白药' OR stock_abbr='白云山') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
+      "SQL": "SELECT stock_abbr, stock_code, report_year, report_period, asset_liability_ratio FROM balance_sheet WHERE (stock_abbr='云南白药' OR stock_abbr='白云山') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
       "image": "B1045_3.jpg"
     }
   ]
@@ -3384,7 +3872,11 @@
           <t>[{"Q": "2025年第三季度经营性现金流量净额为负的公司有多少家"}, {"Q": "这些公司中，资产负债率超过60%的有几家"}]</t>
         </is>
       </c>
-      <c r="D47" s="1" t="inlineStr"/>
+      <c r="D47" s="1" t="inlineStr">
+        <is>
+          <t>SELECT COUNT(*) AS 数量 FROM balance_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') AND asset_liability_ratio &gt; 60.0 AND asset_liability_ratio IS NOT NULL</t>
+        </is>
+      </c>
       <c r="E47" s="1" t="inlineStr">
         <is>
           <t>table</t>
@@ -3398,21 +3890,25 @@
   "子问题": [
     {
       "Q": "2025年第三季度经营性现金流量净额为负的公司有多少家",
-      "A": "澄清：请问要查询哪家公司？",
-      "SQL": "",
-      "image": ""
+      "A": "共 6 家",
+      "SQL": "SELECT COUNT(*) AS 数量 FROM cash_flow_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') AND operating_cf_net_amount &lt; 0 AND operating_cf_net_amount IS NOT NULL",
+      "image": "B1046_1.jpg"
     },
     {
       "Q": "这些公司中，资产负债率超过60%的有几家",
-      "A": "澄清：请问要查询哪家公司？",
-      "SQL": "",
-      "image": ""
-    }
-  ]
-}</t>
-        </is>
-      </c>
-      <c r="G47" s="1" t="inlineStr"/>
+      "A": "共 0 家",
+      "SQL": "SELECT COUNT(*) AS 数量 FROM balance_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') AND asset_liability_ratio &gt; 60.0 AND asset_liability_ratio IS NOT NULL",
+      "image": "B1046_2.jpg"
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G47" s="1" t="inlineStr">
+        <is>
+          <t>B1046_2.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="120" customHeight="1">
       <c r="A48" s="1" t="inlineStr">
@@ -3432,7 +3928,7 @@
       </c>
       <c r="D48" s="1" t="inlineStr">
         <is>
-          <t>SELECT stock_abbr, report_year, report_period, operating_expense_rnd_expenses FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY operating_expense_rnd_expenses DESC LIMIT 10</t>
+          <t>SELECT stock_abbr, stock_code, report_year, report_period, operating_expense_rnd_expenses FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY operating_expense_rnd_expenses DESC LIMIT 10</t>
         </is>
       </c>
       <c r="E48" s="1" t="inlineStr">
@@ -3449,7 +3945,7 @@
     {
       "Q": "2025年第三季度研发费用占比前十的中药公司",
       "A": "研发费用 排名 Top5：1) 天士力 5.53 亿元; 2) 白云山 4.44 亿元; 3) 康缘药业 3.52 亿元; 4) 济川药业 2.72 亿元; 5) 太极集团 1.95 亿元",
-      "SQL": "SELECT stock_abbr, report_year, report_period, operating_expense_rnd_expenses FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY operating_expense_rnd_expenses DESC LIMIT 10",
+      "SQL": "SELECT stock_abbr, stock_code, report_year, report_period, operating_expense_rnd_expenses FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY operating_expense_rnd_expenses DESC LIMIT 10",
       "image": "B1047_1.jpg"
     },
     {
@@ -3486,7 +3982,7 @@
       </c>
       <c r="D49" s="1" t="inlineStr">
         <is>
-          <t>SELECT stock_abbr, report_year, report_period, net_profit FROM income_sheet WHERE report_year IN (2024) AND report_period IN ('Q3') ORDER BY net_profit DESC LIMIT 10</t>
+          <t>SELECT stock_abbr, stock_code, report_year, report_period, net_profit FROM income_sheet WHERE report_year IN (2024) AND report_period IN ('Q3') ORDER BY net_profit DESC LIMIT 10</t>
         </is>
       </c>
       <c r="E49" s="1" t="inlineStr">
@@ -3503,7 +3999,7 @@
     {
       "Q": "2024年第三季度净利润排名前三的公司？",
       "A": "净利润 排名 Top5：1) 白云山 32.89 亿元; 2) 片仔癀 27.18 亿元; 3) 同仁堂 19.84 亿元; 4) 济川药业 19.07 亿元; 5) 天士力 8.28 亿元",
-      "SQL": "SELECT stock_abbr, report_year, report_period, net_profit FROM income_sheet WHERE report_year IN (2024) AND report_period IN ('Q3') ORDER BY net_profit DESC LIMIT 10",
+      "SQL": "SELECT stock_abbr, stock_code, report_year, report_period, net_profit FROM income_sheet WHERE report_year IN (2024) AND report_period IN ('Q3') ORDER BY net_profit DESC LIMIT 10",
       "image": "B1048_1.jpg"
     },
     {
@@ -3546,7 +4042,7 @@
       </c>
       <c r="D50" s="1" t="inlineStr">
         <is>
-          <t>SELECT stock_abbr, report_year, report_period, total_operating_revenue FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY total_operating_revenue DESC LIMIT 10</t>
+          <t>SELECT stock_abbr, stock_code, report_year, report_period, total_operating_revenue FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY total_operating_revenue DESC LIMIT 10</t>
         </is>
       </c>
       <c r="E50" s="1" t="inlineStr">
@@ -3563,7 +4059,7 @@
     {
       "Q": "查询2025年第三季度66家中药公司营业总收入排名前十的公司，用条形图展示排名",
       "A": "营业总收入 排名 Top5：1) 白云山 616.06 亿元; 2) 同仁堂 133.08 亿元; 3) 步长制药 84.69 亿元; 4) 太极集团 80.88 亿元; 5) 片仔癀 74.42 亿元",
-      "SQL": "SELECT stock_abbr, report_year, report_period, total_operating_revenue FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY total_operating_revenue DESC LIMIT 10",
+      "SQL": "SELECT stock_abbr, stock_code, report_year, report_period, total_operating_revenue FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY total_operating_revenue DESC LIMIT 10",
       "image": "B1049_1.jpg"
     }
   ]
@@ -3594,7 +4090,7 @@
       </c>
       <c r="D51" s="1" t="inlineStr">
         <is>
-          <t>SELECT stock_abbr, report_year, report_period, net_profit FROM income_sheet WHERE (stock_abbr='云南白药') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END</t>
+          <t>SELECT stock_abbr, stock_code, report_year, report_period, net_profit FROM income_sheet WHERE (stock_abbr='云南白药') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END</t>
         </is>
       </c>
       <c r="E51" s="1" t="inlineStr">
@@ -3611,7 +4107,7 @@
     {
       "Q": "分析云南白药2022-2025年第三季度净利润的变化趋势，用折线图展示",
       "A": "未查询到有效数据",
-      "SQL": "SELECT stock_abbr, report_year, report_period, net_profit FROM income_sheet WHERE (stock_abbr='云南白药') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
+      "SQL": "SELECT stock_abbr, stock_code, report_year, report_period, net_profit FROM income_sheet WHERE (stock_abbr='云南白药') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
       "image": "B1050_1.jpg"
     }
   ]
@@ -3642,7 +4138,7 @@
       </c>
       <c r="D52" s="1" t="inlineStr">
         <is>
-          <t>SELECT stock_abbr, report_year, report_period, roe FROM core_performance_indicators_sheet WHERE (stock_abbr='白云山' OR stock_abbr='云南白药' OR stock_abbr='片仔癀') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END</t>
+          <t>SELECT stock_abbr, stock_code, report_year, report_period, roe FROM core_performance_indicators_sheet WHERE (stock_abbr='白云山' OR stock_abbr='云南白药' OR stock_abbr='片仔癀') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END</t>
         </is>
       </c>
       <c r="E52" s="1" t="inlineStr">
@@ -3659,7 +4155,7 @@
     {
       "Q": "对比白云山、云南白药、片仔癀2025年第三季度的核心盈利能力指标（销售毛利率、销售净利率、ROE），用雷达图展示差异",
       "A": "ROE 对比：云南白药 2025三季报 —; 白云山 2025三季报 —; 片仔癀 2025三季报 4.68%",
-      "SQL": "SELECT stock_abbr, report_year, report_period, roe FROM core_performance_indicators_sheet WHERE (stock_abbr='白云山' OR stock_abbr='云南白药' OR stock_abbr='片仔癀') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
+      "SQL": "SELECT stock_abbr, stock_code, report_year, report_period, roe FROM core_performance_indicators_sheet WHERE (stock_abbr='白云山' OR stock_abbr='云南白药' OR stock_abbr='片仔癀') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
       "image": "B1051_1.jpg"
     }
   ]
@@ -3688,7 +4184,11 @@
           <t>[{"Q": "统计2025年第三季度中药公司资产负债率的分布情况（按0-30%、30%-50%、50%-70%、70%以上分组），用饼图展示各组公司数量占比"}]</t>
         </is>
       </c>
-      <c r="D53" s="1" t="inlineStr"/>
+      <c r="D53" s="1" t="inlineStr">
+        <is>
+          <t>SELECT COUNT(*) AS 数量 FROM balance_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') AND asset_liability_ratio IS NOT NULL</t>
+        </is>
+      </c>
       <c r="E53" s="1" t="inlineStr">
         <is>
           <t>table</t>
@@ -3702,15 +4202,19 @@
   "子问题": [
     {
       "Q": "统计2025年第三季度中药公司资产负债率的分布情况（按0-30%、30%-50%、50%-70%、70%以上分组），用饼图展示各组公司数量占比",
-      "A": "澄清：请问要查询哪家公司？",
-      "SQL": "",
-      "image": ""
-    }
-  ]
-}</t>
-        </is>
-      </c>
-      <c r="G53" s="1" t="inlineStr"/>
+      "A": "共 0 家",
+      "SQL": "SELECT COUNT(*) AS 数量 FROM balance_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') AND asset_liability_ratio IS NOT NULL",
+      "image": "B1052_1.jpg"
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G53" s="1" t="inlineStr">
+        <is>
+          <t>B1052_1.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="120" customHeight="1">
       <c r="A54" s="1" t="inlineStr">
@@ -3768,7 +4272,11 @@
           <t>[{"Q": "分析2022-2025年第三季度中药行业平均研发费用占比的变化趋势，用折线图展示"}]</t>
         </is>
       </c>
-      <c r="D55" s="1" t="inlineStr"/>
+      <c r="D55" s="1" t="inlineStr">
+        <is>
+          <t>SELECT AVG(operating_expense_rnd_expenses) AS operating_expense_rnd_expenses_avg FROM income_sheet WHERE operating_expense_rnd_expenses IS NOT NULL AND report_year IN (2025) AND report_period IN ('Q3')</t>
+        </is>
+      </c>
       <c r="E55" s="1" t="inlineStr">
         <is>
           <t>table</t>
@@ -3782,15 +4290,19 @@
   "子问题": [
     {
       "Q": "分析2022-2025年第三季度中药行业平均研发费用占比的变化趋势，用折线图展示",
-      "A": "澄清：请问要分析哪家公司的趋势？",
-      "SQL": "",
-      "image": ""
-    }
-  ]
-}</t>
-        </is>
-      </c>
-      <c r="G55" s="1" t="inlineStr"/>
+      "A": "研发费用均值：1.23 亿元",
+      "SQL": "SELECT AVG(operating_expense_rnd_expenses) AS operating_expense_rnd_expenses_avg FROM income_sheet WHERE operating_expense_rnd_expenses IS NOT NULL AND report_year IN (2025) AND report_period IN ('Q3')",
+      "image": "B1054_1.jpg"
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G55" s="1" t="inlineStr">
+        <is>
+          <t>B1054_1.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="120" customHeight="1">
       <c r="A56" s="1" t="inlineStr">
@@ -3850,7 +4362,7 @@
       </c>
       <c r="D57" s="1" t="inlineStr">
         <is>
-          <t>SELECT stock_abbr, report_year, report_period, asset_inventory FROM balance_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY asset_inventory DESC LIMIT 10</t>
+          <t>SELECT stock_abbr, stock_code, report_year, report_period, asset_inventory FROM balance_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY asset_inventory DESC LIMIT 10</t>
         </is>
       </c>
       <c r="E57" s="1" t="inlineStr">
@@ -3867,7 +4379,7 @@
     {
       "Q": "查询2025年第三季度存货周转率最高的五家公司，用条形图展示其周转率数值",
       "A": "存货 排名 Top5：1) 同仁堂 111.25 亿元; 2) 白云山 110.81 亿元; 3) 华润三九 63.87 亿元; 4) 片仔癀 61.60 亿元; 5) 云南白药 57.77 亿元",
-      "SQL": "SELECT stock_abbr, report_year, report_period, asset_inventory FROM balance_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY asset_inventory DESC LIMIT 10",
+      "SQL": "SELECT stock_abbr, stock_code, report_year, report_period, asset_inventory FROM balance_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY asset_inventory DESC LIMIT 10",
       "image": "B1056_1.jpg"
     }
   ]
@@ -3938,7 +4450,7 @@
       </c>
       <c r="D59" s="1" t="inlineStr">
         <is>
-          <t>SELECT stock_abbr, report_year, report_period, asset_cash_and_cash_equivalents FROM balance_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END</t>
+          <t>SELECT stock_abbr, stock_code, report_year, report_period, asset_cash_and_cash_equivalents FROM balance_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END</t>
         </is>
       </c>
       <c r="E59" s="1" t="inlineStr">
@@ -3955,7 +4467,7 @@
     {
       "Q": "查询2025年第三季度短期借款超过货币资金的公司，用表格列出具体数据，并用柱状图对比这两项指标的差额",
       "A": "货币资金 对比：贵州百灵 2025三季报 1.82 亿元; 东阿阿胶 2025三季报 55.62 亿元; 云南白药 2025三季报 86.18 亿元; 启迪药业 2025三季报 1.56 亿元; 仁和药业 2025三季报 10.95 亿元; 通化金马 2025三季报 3.22 亿元; 华神科技 2025三季报 1.49 亿元; 九芝堂 2025三季报 3.02 亿元; 华润三九 2025三季报 56.23 亿元; 万邦德 2025三季报 8,307.08 万元; 沃华医药 2025三季报 3.93 亿元; 莱茵生物 2025三季报 2.55 亿元; 嘉应制药 2025三季报 1.28 亿元; 新里程 2025三季报 3.08 亿元; 桂林三金 2025三季报 10.78 亿元; 奇正藏药 2025三季报 2.84 亿元; 众生药业 2025三季报 9.32 亿元; 精华制药 2025三季报 7.24 亿元; 信邦制药 2025三季报 9.62 亿元; 益盛药业 2025三季报 1.16 亿元; 瑞康医药 2025三季报 42.41 亿元; 以岭药业 2025三季报 10.34 亿元; 特一药业 2025三季报 2.15 亿元; 葵花药业 2025三季报 6.85 亿元; 康弘药业 2025三季报 38.28 亿元; 盘龙药业 2025三季报 11.65 亿元; 新天药业 2025三季报 1.69 亿元; 华森制药 2025三季报 3.03 亿元; 红日药业 2025三季报 14.14 亿元; 振东制药 2025三季报 2.90 亿元; 佐力药业 2025三季报 6.93 亿元; 新光药业 2025三季报 2.91 亿元; 陇神戎发 2025三季报 —; 康泰医学 2025三季报 7.78 亿元; 维康药业 2025三季报 —; 粤万年青 2025三季报 1.42 亿元; 恩威医药 2025三季报 3.20 亿元; 金花股份 2025三季报 2.35 亿元; 同仁堂 2025三季报 109.10 亿元; 太极集团 2025三季报 5.78 亿元; 太龙药业 2025三季报 3.44 亿元; 中恒集团 2025三季报 40.57 亿元; 羚锐制药 2025三季报 4.60 亿元; 达仁堂 2025三季报 10.49 亿元; 白云山 2025三季报 137.08 亿元; 亚宝药业 2025三季报 6.45 亿元; 昆药集团 2025三季报 7.94 亿元; 片仔癀 2025三季报 13.47 亿元; 千金药业 2025三季报 5.65 亿元; 康美药业 2025三季报 11.81 亿元; 天士力 2025三季报 26.03 亿元; 康缘药业 2025三季报 21.57 亿元; 济川药业 2025三季报 51.30 亿元; 康恩贝 2025三季报 8.36 亿元; 益佰制药 2025三季报 5.94 亿元; 神奇制药 2025三季报 6.11 亿元; 天目药业 2025三季报 1,174.03 万元; 江中药业 2025三季报 19.99 亿元; 广誉远 2025三季报 2.96 亿元; 健民集团 2025三季报 1.75 亿元; 马应龙 2025三季报 15.41 亿元; 康惠制药 2025三季报 7,849.49 万元; 贵州三力 2025三季报 2.66 亿元; 珍宝岛 2025三季报 2.04 亿元; 步长制药 2025三季报 8.86 亿元; 寿仙谷 2025三季报 6.97 亿元; 方盛制药 2025三季报 1.80 亿元",
-      "SQL": "SELECT stock_abbr, report_year, report_period, asset_cash_and_cash_equivalents FROM balance_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
+      "SQL": "SELECT stock_abbr, stock_code, report_year, report_period, asset_cash_and_cash_equivalents FROM balance_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
       "image": "B1058_1.jpg"
     }
   ]
@@ -3986,7 +4498,7 @@
       </c>
       <c r="D60" s="1" t="inlineStr">
         <is>
-          <t>SELECT stock_abbr, report_year, report_period, net_profit FROM income_sheet WHERE (stock_abbr='片仔癀') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END</t>
+          <t>SELECT stock_abbr, stock_code, report_year, report_period, net_profit_excl_non_recurring FROM core_performance_indicators_sheet WHERE (stock_abbr='片仔癀') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END</t>
         </is>
       </c>
       <c r="E60" s="1" t="inlineStr">
@@ -4002,8 +4514,8 @@
   "子问题": [
     {
       "Q": "分析片仔癀2022-2025年第三季度扣非净利润占净利润的比例变化，用折线图展示",
-      "A": "片仔癀 2025三季报 的净利润为 21.33 亿元（仅有效值）",
-      "SQL": "SELECT stock_abbr, report_year, report_period, net_profit FROM income_sheet WHERE (stock_abbr='片仔癀') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
+      "A": "未查询到有效数据",
+      "SQL": "SELECT stock_abbr, stock_code, report_year, report_period, net_profit_excl_non_recurring FROM core_performance_indicators_sheet WHERE (stock_abbr='片仔癀') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
       "image": "B1059_1.jpg"
     }
   ]
@@ -4034,7 +4546,7 @@
       </c>
       <c r="D61" s="1" t="inlineStr">
         <is>
-          <t>SELECT stock_abbr, report_year, report_period, net_profit FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY net_profit DESC LIMIT 10</t>
+          <t>SELECT stock_abbr, stock_code, report_year, report_period, operating_expense_rnd_expenses FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY operating_expense_rnd_expenses DESC LIMIT 10</t>
         </is>
       </c>
       <c r="E61" s="1" t="inlineStr">
@@ -4050,8 +4562,8 @@
   "子问题": [
     {
       "Q": "对比2025年第三季度研发费用占比前十与后十公司的净利润同比增长率，用箱线图展示两组数据的分布差异",
-      "A": "净利润 排名 Top5：1) 白云山 33.98 亿元; 2) 达仁堂 21.46 亿元; 3) 片仔癀 21.33 亿元; 4) 同仁堂 15.93 亿元; 5) 济川药业 10.24 亿元",
-      "SQL": "SELECT stock_abbr, report_year, report_period, net_profit FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY net_profit DESC LIMIT 10",
+      "A": "研发费用 排名 Top5：1) 天士力 5.53 亿元; 2) 白云山 4.44 亿元; 3) 康缘药业 3.52 亿元; 4) 济川药业 2.72 亿元; 5) 太极集团 1.95 亿元",
+      "SQL": "SELECT stock_abbr, stock_code, report_year, report_period, operating_expense_rnd_expenses FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY operating_expense_rnd_expenses DESC LIMIT 10",
       "image": "B1060_1.jpg"
     }
   ]
@@ -4080,7 +4592,11 @@
           <t>[{"Q": "查询2025年第三季度投资性现金流量净额的正负分布情况，用柱状图展示正负公司的数量及净额均值"}]</t>
         </is>
       </c>
-      <c r="D62" s="1" t="inlineStr"/>
+      <c r="D62" s="1" t="inlineStr">
+        <is>
+          <t>SELECT AVG(investing_cf_net_amount) AS investing_cf_net_amount_avg FROM cash_flow_sheet WHERE investing_cf_net_amount IS NOT NULL AND report_year IN (2025) AND report_period IN ('Q3')</t>
+        </is>
+      </c>
       <c r="E62" s="1" t="inlineStr">
         <is>
           <t>table</t>
@@ -4094,15 +4610,19 @@
   "子问题": [
     {
       "Q": "查询2025年第三季度投资性现金流量净额的正负分布情况，用柱状图展示正负公司的数量及净额均值",
-      "A": "澄清：请问要查询哪家公司？",
-      "SQL": "",
-      "image": ""
-    }
-  ]
-}</t>
-        </is>
-      </c>
-      <c r="G62" s="1" t="inlineStr"/>
+      "A": "投资活动现金流均值：-2.90 亿元",
+      "SQL": "SELECT AVG(investing_cf_net_amount) AS investing_cf_net_amount_avg FROM cash_flow_sheet WHERE investing_cf_net_amount IS NOT NULL AND report_year IN (2025) AND report_period IN ('Q3')",
+      "image": "B1061_1.jpg"
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G62" s="1" t="inlineStr">
+        <is>
+          <t>B1061_1.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="120" customHeight="1">
       <c r="A63" s="1" t="inlineStr">
@@ -4122,7 +4642,7 @@
       </c>
       <c r="D63" s="1" t="inlineStr">
         <is>
-          <t>SELECT stock_abbr, report_year, report_period, total_operating_revenue FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY total_operating_revenue DESC LIMIT 10</t>
+          <t>SELECT stock_abbr, stock_code, report_year, report_period, operating_expense_cost_of_sales FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY operating_expense_cost_of_sales DESC LIMIT 10</t>
         </is>
       </c>
       <c r="E63" s="1" t="inlineStr">
@@ -4138,8 +4658,8 @@
   "子问题": [
     {
       "Q": "分析2025年第三季度营业成本占营业总收入的比例排名后十的公司，用条形图展示占比数值",
-      "A": "营业总收入 排名 Top5：1) 白云山 616.06 亿元; 2) 同仁堂 133.08 亿元; 3) 步长制药 84.69 亿元; 4) 太极集团 80.88 亿元; 5) 片仔癀 74.42 亿元",
-      "SQL": "SELECT stock_abbr, report_year, report_period, total_operating_revenue FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY total_operating_revenue DESC LIMIT 10",
+      "A": "营业成本 排名 Top5：1) 白云山 507.61 亿元; 2) 同仁堂 74.71 亿元; 3) 太极集团 57.78 亿元; 4) 片仔癀 45.45 亿元; 5) 康美药业 32.05 亿元",
+      "SQL": "SELECT stock_abbr, stock_code, report_year, report_period, operating_expense_cost_of_sales FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY operating_expense_cost_of_sales DESC LIMIT 10",
       "image": "B1062_1.jpg"
     }
   ]
@@ -4210,12 +4730,12 @@
       </c>
       <c r="D65" s="1" t="inlineStr">
         <is>
-          <t>SELECT stock_abbr, report_year, report_period, net_profit FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END</t>
+          <t>SELECT AVG(operating_expense_selling_expenses) AS operating_expense_selling_expenses_avg FROM income_sheet WHERE operating_expense_selling_expenses IS NOT NULL AND report_year IN (2025) AND report_period IN ('Q3')</t>
         </is>
       </c>
       <c r="E65" s="1" t="inlineStr">
         <is>
-          <t>bar</t>
+          <t>table</t>
         </is>
       </c>
       <c r="F65" s="1" t="inlineStr">
@@ -4226,8 +4746,8 @@
   "子问题": [
     {
       "Q": "对比2025年第三季度销售费用率低于行业均值和高于行业均值公司的平均净利润率，用柱状图展示差异",
-      "A": "净利润 对比：贵州百灵 2025三季报 —; 东阿阿胶 2025三季报 —; 云南白药 2025三季报 —; 启迪药业 2025三季报 —; 仁和药业 2025三季报 —; 通化金马 2025三季报 —; 华神科技 2025三季报 —; 九芝堂 2025三季报 —; 华润三九 2025三季报 —; 万邦德 2025三季报 —; 沃华医药 2025三季报 —; 莱茵生物 2025三季报 —; 嘉应制药 2025三季报 —; 新里程 2025三季报 —; 桂林三金 2025三季报 —; 奇正藏药 2025三季报 —; 众生药业 2025三季报 —; 精华制药 2025三季报 —; 信邦制药 2025三季报 —; 益盛药业 2025三季报 —; 瑞康医药 2025三季报 —; 以岭药业 2025三季报 —; 特一药业 2025三季报 —; 葵花药业 2025三季报 —; 康弘药业 2025三季报 —; 盘龙药业 2025三季报 —; 新天药业 2025三季报 —; 华森制药 2025三季报 —; 红日药业 2025三季报 —; 振东制药 2025三季报 —; 佐力药业 2025三季报 —; 新光药业 2025三季报 —; 陇神戎发 2025三季报 —; 康泰医学 2025三季报 —; 维康药业 2025三季报 —; 粤万年青 2025三季报 —; 恩威医药 2025三季报 —; 金花股份 2025三季报 3,423.74 万元; 同仁堂 2025三季报 15.93 亿元; 太极集团 2025三季报 1.64 亿元; 太龙药业 2025三季报 3,047.46 万元; 中恒集团 2025三季报 -931.86 万元; 羚锐制药 2025三季报 6.54 亿元; 达仁堂 2025三季报 21.46 亿元; 白云山 2025三季报 33.98 亿元; 亚宝药业 2025三季报 1.98 亿元; 昆药集团 2025三季报 3.23 亿元; 片仔癀 2025三季报 21.33 亿元; 千金药业 2025三季报 2.58 亿元; 康美药业 2025三季报 1,509.11 万元; 天士力 2025三季报 9.93 亿元; 康缘药业 2025三季报 2.08 亿元; 济川药业 2025三季报 10.24 亿元; 康恩贝 2025三季报 5.96 亿元; 益佰制药 2025三季报 -9,062.98 万元; 神奇制药 2025三季报 5,109.10 万元; 天目药业 2025三季报 750.81 万元; 江中药业 2025三季报 7.43 亿元; 广誉远 2025三季报 8,215.46 万元; 健民集团 2025三季报 2.89 亿元; 马应龙 2025三季报 5.19 亿元; 康惠制药 2025三季报 -1.57 亿元; 贵州三力 2025三季报 8,367.73 万元; 珍宝岛 2025三季报 -3.76 亿元; 步长制药 2025三季报 7.91 亿元; 寿仙谷 2025三季报 7,634.62 万元; 方盛制药 2025三季报 2.65 亿元",
-      "SQL": "SELECT stock_abbr, report_year, report_period, net_profit FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
+      "A": "销售费用均值：9.84 亿元",
+      "SQL": "SELECT AVG(operating_expense_selling_expenses) AS operating_expense_selling_expenses_avg FROM income_sheet WHERE operating_expense_selling_expenses IS NOT NULL AND report_year IN (2025) AND report_period IN ('Q3')",
       "image": "B1064_1.jpg"
     }
   ]
@@ -4298,7 +4818,7 @@
       </c>
       <c r="D67" s="1" t="inlineStr">
         <is>
-          <t>SELECT stock_abbr, report_year, report_period, net_profit FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY net_profit DESC LIMIT 10</t>
+          <t>SELECT stock_abbr, stock_code, report_year, report_period, net_profit FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY net_profit DESC LIMIT 10</t>
         </is>
       </c>
       <c r="E67" s="1" t="inlineStr">
@@ -4321,7 +4841,7 @@
     {
       "Q": "2025年第三季度，2家中药上市公司中，营业总收入和净利润均排名前十的公司",
       "A": "净利润 排名 Top5：1) 白云山 33.98 亿元; 2) 达仁堂 21.46 亿元; 3) 片仔癀 21.33 亿元; 4) 同仁堂 15.93 亿元; 5) 济川药业 10.24 亿元",
-      "SQL": "SELECT stock_abbr, report_year, report_period, net_profit FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY net_profit DESC LIMIT 10",
+      "SQL": "SELECT stock_abbr, stock_code, report_year, report_period, net_profit FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY net_profit DESC LIMIT 10",
       "image": "B1066_2.jpg"
     }
   ]
@@ -4350,7 +4870,11 @@
           <t>[{"Q": "中药公司的资产负债率情况如何"}, {"Q": "2025年第三季度，66家中药上市公司的资产负债率均值是多少"}]</t>
         </is>
       </c>
-      <c r="D68" s="1" t="inlineStr"/>
+      <c r="D68" s="1" t="inlineStr">
+        <is>
+          <t>SELECT AVG(asset_liability_ratio) AS asset_liability_ratio_avg FROM balance_sheet WHERE asset_liability_ratio IS NOT NULL AND report_year IN (2025) AND report_period IN ('Q3')</t>
+        </is>
+      </c>
       <c r="E68" s="1" t="inlineStr">
         <is>
           <t>table</t>
@@ -4370,15 +4894,19 @@
     },
     {
       "Q": "2025年第三季度，66家中药上市公司的资产负债率均值是多少",
-      "A": "澄清：请问要查询哪家公司？",
-      "SQL": "",
-      "image": ""
-    }
-  ]
-}</t>
-        </is>
-      </c>
-      <c r="G68" s="1" t="inlineStr"/>
+      "A": "资产负债率均值：—",
+      "SQL": "SELECT AVG(asset_liability_ratio) AS asset_liability_ratio_avg FROM balance_sheet WHERE asset_liability_ratio IS NOT NULL AND report_year IN (2025) AND report_period IN ('Q3')",
+      "image": "B1067_2.jpg"
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G68" s="1" t="inlineStr">
+        <is>
+          <t>B1067_2.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="120" customHeight="1">
       <c r="A69" s="1" t="inlineStr">
@@ -4396,7 +4924,11 @@
           <t>[{"Q": "分析中药行业的盈利能力"}, {"Q": "2025年第三季度，66家中药上市公司的平均销售毛利率、销售净利率分别是多少？请结合数值分析行业整体盈利能力"}]</t>
         </is>
       </c>
-      <c r="D69" s="1" t="inlineStr"/>
+      <c r="D69" s="1" t="inlineStr">
+        <is>
+          <t>SELECT AVG(gross_profit_margin) AS gross_profit_margin_avg FROM core_performance_indicators_sheet WHERE gross_profit_margin IS NOT NULL AND report_year IN (2025) AND report_period IN ('Q3')</t>
+        </is>
+      </c>
       <c r="E69" s="1" t="inlineStr">
         <is>
           <t>table</t>
@@ -4416,15 +4948,19 @@
     },
     {
       "Q": "2025年第三季度，66家中药上市公司的平均销售毛利率、销售净利率分别是多少？请结合数值分析行业整体盈利能力",
-      "A": "澄清：请问要查询哪家公司？",
-      "SQL": "",
-      "image": ""
-    }
-  ]
-}</t>
-        </is>
-      </c>
-      <c r="G69" s="1" t="inlineStr"/>
+      "A": "毛利率均值：—",
+      "SQL": "SELECT AVG(gross_profit_margin) AS gross_profit_margin_avg FROM core_performance_indicators_sheet WHERE gross_profit_margin IS NOT NULL AND report_year IN (2025) AND report_period IN ('Q3')",
+      "image": "B1068_2.jpg"
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G69" s="1" t="inlineStr">
+        <is>
+          <t>B1068_2.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="120" customHeight="1">
       <c r="A70" s="1" t="inlineStr">
@@ -4444,7 +4980,7 @@
       </c>
       <c r="D70" s="1" t="inlineStr">
         <is>
-          <t>SELECT stock_abbr, report_year, report_period, net_profit FROM income_sheet WHERE report_year IN (2025,2024) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END</t>
+          <t>SELECT AVG(net_profit) AS net_profit_avg FROM income_sheet WHERE net_profit IS NOT NULL AND report_year IN (2025,2024) AND report_period IN ('Q3')</t>
         </is>
       </c>
       <c r="E70" s="1" t="inlineStr">
@@ -4466,8 +5002,8 @@
     },
     {
       "Q": "2025年第三季度，66家中药上市公司的营业总收入、净利润均值分别是多少？与2024年同期相比增长率如何？",
-      "A": "金花股份的净利润从2024三季报的 3,077.02 万元 变化到2025三季报的 2.65 亿元（+762.37%）",
-      "SQL": "SELECT stock_abbr, report_year, report_period, net_profit FROM income_sheet WHERE report_year IN (2025,2024) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
+      "A": "净利润均值：5.69 亿元",
+      "SQL": "SELECT AVG(net_profit) AS net_profit_avg FROM income_sheet WHERE net_profit IS NOT NULL AND report_year IN (2025,2024) AND report_period IN ('Q3')",
       "image": "B1069_2.jpg"
     }
   ]
@@ -4496,10 +5032,14 @@
           <t>[{"Q": "查询净利润同比增长的公司"}, {"Q": "2025年第三季度，66家中药上市公司中，净利润同比增长率超过20%的公司有哪些？列出股票代码、简称及具体增长率"}]</t>
         </is>
       </c>
-      <c r="D71" s="1" t="inlineStr"/>
+      <c r="D71" s="1" t="inlineStr">
+        <is>
+          <t>SELECT stock_abbr, stock_code, report_year, report_period, net_profit_yoy_growth FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') AND net_profit_yoy_growth &gt; 20.0 AND net_profit_yoy_growth IS NOT NULL ORDER BY net_profit_yoy_growth DESC LIMIT 50</t>
+        </is>
+      </c>
       <c r="E71" s="1" t="inlineStr">
         <is>
-          <t>table</t>
+          <t>bar</t>
         </is>
       </c>
       <c r="F71" s="1" t="inlineStr">
@@ -4516,8 +5056,8 @@
     },
     {
       "Q": "2025年第三季度，66家中药上市公司中，净利润同比增长率超过20%的公司有哪些？列出股票代码、简称及具体增长率",
-      "A": "澄清：请问要查询哪家公司？",
-      "SQL": "",
+      "A": "未查询到数据",
+      "SQL": "SELECT stock_abbr, stock_code, report_year, report_period, net_profit_yoy_growth FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') AND net_profit_yoy_growth &gt; 20.0 AND net_profit_yoy_growth IS NOT NULL ORDER BY net_profit_yoy_growth DESC LIMIT 50",
       "image": ""
     }
   ]

--- a/result/result_2.xlsx
+++ b/result/result_2.xlsx
@@ -358,7 +358,7 @@
     <from>
       <col>6</col>
       <colOff>0</colOff>
-      <row>13</row>
+      <row>14</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2286000" cy="1428750"/>
@@ -383,7 +383,7 @@
     <from>
       <col>6</col>
       <colOff>0</colOff>
-      <row>14</row>
+      <row>15</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2286000" cy="1428750"/>
@@ -408,7 +408,7 @@
     <from>
       <col>6</col>
       <colOff>0</colOff>
-      <row>15</row>
+      <row>16</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2286000" cy="1428750"/>
@@ -433,7 +433,7 @@
     <from>
       <col>6</col>
       <colOff>0</colOff>
-      <row>16</row>
+      <row>17</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2286000" cy="1428750"/>
@@ -458,7 +458,7 @@
     <from>
       <col>6</col>
       <colOff>0</colOff>
-      <row>17</row>
+      <row>18</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2286000" cy="1428750"/>
@@ -483,7 +483,7 @@
     <from>
       <col>6</col>
       <colOff>0</colOff>
-      <row>18</row>
+      <row>19</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2286000" cy="1428750"/>
@@ -508,7 +508,7 @@
     <from>
       <col>6</col>
       <colOff>0</colOff>
-      <row>19</row>
+      <row>20</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2286000" cy="1428750"/>
@@ -533,7 +533,7 @@
     <from>
       <col>6</col>
       <colOff>0</colOff>
-      <row>20</row>
+      <row>21</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2286000" cy="1428750"/>
@@ -558,37 +558,37 @@
     <from>
       <col>6</col>
       <colOff>0</colOff>
+      <row>22</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2286000" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="18" name="Image 18" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId18"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
       <row>23</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2286000" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="18" name="Image 18" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId18"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
-      <colOff>0</colOff>
-      <row>25</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="2286000" cy="1428750"/>
-    <pic>
-      <nvPicPr>
         <cNvPr id="19" name="Image 19" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
@@ -733,17 +733,42 @@
     <from>
       <col>6</col>
       <colOff>0</colOff>
+      <row>33</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2286000" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="25" name="Image 25" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId25"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
       <row>34</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2286000" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="25" name="Image 25" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId25"/>
+        <cNvPr id="26" name="Image 26" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId26"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -764,11 +789,11 @@
     <ext cx="2286000" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="26" name="Image 26" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId26"/>
+        <cNvPr id="27" name="Image 27" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId27"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -789,11 +814,36 @@
     <ext cx="2286000" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="27" name="Image 27" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId27"/>
+        <cNvPr id="28" name="Image 28" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId28"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>41</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2286000" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="29" name="Image 29" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId29"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -814,11 +864,11 @@
     <ext cx="2286000" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="28" name="Image 28" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId28"/>
+        <cNvPr id="30" name="Image 30" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId30"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -839,11 +889,11 @@
     <ext cx="2286000" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="29" name="Image 29" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId29"/>
+        <cNvPr id="31" name="Image 31" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId31"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -864,11 +914,11 @@
     <ext cx="2286000" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="30" name="Image 30" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId30"/>
+        <cNvPr id="32" name="Image 32" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId32"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -889,11 +939,11 @@
     <ext cx="2286000" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="31" name="Image 31" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId31"/>
+        <cNvPr id="33" name="Image 33" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId33"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -914,11 +964,11 @@
     <ext cx="2286000" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="32" name="Image 32" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId32"/>
+        <cNvPr id="34" name="Image 34" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId34"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -939,11 +989,11 @@
     <ext cx="2286000" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="33" name="Image 33" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId33"/>
+        <cNvPr id="35" name="Image 35" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId35"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -964,11 +1014,11 @@
     <ext cx="2286000" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="34" name="Image 34" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId34"/>
+        <cNvPr id="36" name="Image 36" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId36"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -989,11 +1039,11 @@
     <ext cx="2286000" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="35" name="Image 35" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId35"/>
+        <cNvPr id="37" name="Image 37" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId37"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1014,11 +1064,11 @@
     <ext cx="2286000" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="36" name="Image 36" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId36"/>
+        <cNvPr id="38" name="Image 38" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId38"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1039,11 +1089,11 @@
     <ext cx="2286000" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="37" name="Image 37" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId37"/>
+        <cNvPr id="39" name="Image 39" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId39"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1064,11 +1114,36 @@
     <ext cx="2286000" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="38" name="Image 38" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId38"/>
+        <cNvPr id="40" name="Image 40" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId40"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>53</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2286000" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="41" name="Image 41" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId41"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1089,11 +1164,11 @@
     <ext cx="2286000" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="39" name="Image 39" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId39"/>
+        <cNvPr id="42" name="Image 42" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId42"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1114,11 +1189,36 @@
     <ext cx="2286000" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="40" name="Image 40" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId40"/>
+        <cNvPr id="43" name="Image 43" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId43"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>57</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2286000" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="44" name="Image 44" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId44"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1139,11 +1239,11 @@
     <ext cx="2286000" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="41" name="Image 41" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId41"/>
+        <cNvPr id="45" name="Image 45" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId45"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1164,36 +1264,11 @@
     <ext cx="2286000" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="42" name="Image 42" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId42"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
-      <colOff>0</colOff>
-      <row>60</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="2286000" cy="1428750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="43" name="Image 43" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId43"/>
+        <cNvPr id="46" name="Image 46" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId46"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1214,11 +1289,11 @@
     <ext cx="2286000" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="44" name="Image 44" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId44"/>
+        <cNvPr id="47" name="Image 47" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId47"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1239,11 +1314,11 @@
     <ext cx="2286000" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="45" name="Image 45" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId45"/>
+        <cNvPr id="48" name="Image 48" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId48"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1264,11 +1339,36 @@
     <ext cx="2286000" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="46" name="Image 46" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId46"/>
+        <cNvPr id="49" name="Image 49" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId49"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>65</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2286000" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="50" name="Image 50" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId50"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1289,11 +1389,11 @@
     <ext cx="2286000" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="47" name="Image 47" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId47"/>
+        <cNvPr id="51" name="Image 51" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId51"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1314,11 +1414,11 @@
     <ext cx="2286000" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="48" name="Image 48" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId48"/>
+        <cNvPr id="52" name="Image 52" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId52"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1339,11 +1439,11 @@
     <ext cx="2286000" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="49" name="Image 49" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId49"/>
+        <cNvPr id="53" name="Image 53" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId53"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1364,11 +1464,11 @@
     <ext cx="2286000" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="50" name="Image 50" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId50"/>
+        <cNvPr id="54" name="Image 54" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId54"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2334,12 +2434,12 @@
       </c>
       <c r="D14" s="1" t="inlineStr">
         <is>
-          <t>SELECT AVG(gross_profit_margin) AS gross_profit_margin_avg FROM core_performance_indicators_sheet WHERE gross_profit_margin IS NOT NULL AND report_year IN (2025) AND report_period IN ('Q3')</t>
+          <t>SELECT stock_abbr, stock_code, report_year, report_period, gross_profit_margin, net_profit_margin FROM core_performance_indicators_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') AND gross_profit_margin IS NOT NULL AND net_profit_margin IS NOT NULL AND gross_profit_margin &gt; net_profit_margin ORDER BY (gross_profit_margin - net_profit_margin) DESC LIMIT 50</t>
         </is>
       </c>
       <c r="E14" s="1" t="inlineStr">
         <is>
-          <t>table</t>
+          <t>bar</t>
         </is>
       </c>
       <c r="F14" s="1" t="inlineStr">
@@ -2350,19 +2450,15 @@
   "子问题": [
     {
       "Q": "2025年第三季度，“销售毛利率”和“销售净利率”均高于行业均值的中药公司有哪些？请同步输出行业均值和公司具体数值。",
-      "A": "毛利率均值：—",
-      "SQL": "SELECT AVG(gross_profit_margin) AS gross_profit_margin_avg FROM core_performance_indicators_sheet WHERE gross_profit_margin IS NOT NULL AND report_year IN (2025) AND report_period IN ('Q3')",
-      "image": "B1013_1.jpg"
-    }
-  ]
-}</t>
-        </is>
-      </c>
-      <c r="G14" s="1" t="inlineStr">
-        <is>
-          <t>B1013_1.jpg</t>
-        </is>
-      </c>
+      "A": "未查询到数据",
+      "SQL": "SELECT stock_abbr, stock_code, report_year, report_period, gross_profit_margin, net_profit_margin FROM core_performance_indicators_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') AND gross_profit_margin IS NOT NULL AND net_profit_margin IS NOT NULL AND gross_profit_margin &gt; net_profit_margin ORDER BY (gross_profit_margin - net_profit_margin) DESC LIMIT 50",
+      "image": ""
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G14" s="1" t="inlineStr"/>
     </row>
     <row r="15" ht="120" customHeight="1">
       <c r="A15" s="1" t="inlineStr">
@@ -2526,7 +2622,7 @@
       </c>
       <c r="D18" s="1" t="inlineStr">
         <is>
-          <t>SELECT stock_abbr, stock_code, report_year, report_period, asset_accounts_receivable FROM balance_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') AND asset_accounts_receivable &gt; 30.0 AND asset_accounts_receivable IS NOT NULL ORDER BY asset_accounts_receivable DESC LIMIT 50</t>
+          <t>SELECT t1.stock_abbr, t1.stock_code, t1.report_year, t1.report_period, t1.asset_accounts_receivable, t2.total_operating_revenue FROM balance_sheet t1 JOIN income_sheet t2 USING (stock_code, report_year, report_period) WHERE (t1.report_year IN (2025) AND t1.report_period IN ('Q3')) AND t1.asset_accounts_receivable IS NOT NULL AND t2.total_operating_revenue IS NOT NULL AND t1.asset_accounts_receivable &gt; t2.total_operating_revenue ORDER BY (t1.asset_accounts_receivable - t2.total_operating_revenue) DESC LIMIT 50</t>
         </is>
       </c>
       <c r="E18" s="1" t="inlineStr">
@@ -2542,8 +2638,8 @@
   "子问题": [
     {
       "Q": "2025年第三季度，“资产-应收账款”占“营业总收入”比例超过30%的公司有哪些？请列出股票代码、简称、应收账款占比（%）。",
-      "A": "符合条件共 50 家，前5：白云山(600332) 191.35 亿元; 云南白药(000538) 102.56 亿元; 华润三九(000999) 76.66 亿元; 瑞康医药(002589) 37.33 亿元; 昆药集团(600422) 31.20 亿元",
-      "SQL": "SELECT stock_abbr, stock_code, report_year, report_period, asset_accounts_receivable FROM balance_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') AND asset_accounts_receivable &gt; 30.0 AND asset_accounts_receivable IS NOT NULL ORDER BY asset_accounts_receivable DESC LIMIT 50",
+      "A": "珍宝岛 2025三季报的应收账款为 31.06 亿元",
+      "SQL": "SELECT t1.stock_abbr, t1.stock_code, t1.report_year, t1.report_period, t1.asset_accounts_receivable, t2.total_operating_revenue FROM balance_sheet t1 JOIN income_sheet t2 USING (stock_code, report_year, report_period) WHERE (t1.report_year IN (2025) AND t1.report_period IN ('Q3')) AND t1.asset_accounts_receivable IS NOT NULL AND t2.total_operating_revenue IS NOT NULL AND t1.asset_accounts_receivable &gt; t2.total_operating_revenue ORDER BY (t1.asset_accounts_receivable - t2.total_operating_revenue) DESC LIMIT 50",
       "image": "B1017_1.jpg"
     }
   ]
@@ -2716,10 +2812,14 @@
           <t>[{"Q": "2025年第三季度，“负债-短期借款”金额超过“资产-货币资金”金额的公司有哪些？请列出简称、短期借款（万元）、货币资金（万元）。"}]</t>
         </is>
       </c>
-      <c r="D22" s="1" t="inlineStr"/>
+      <c r="D22" s="1" t="inlineStr">
+        <is>
+          <t>SELECT stock_abbr, stock_code, report_year, report_period, liability_short_term_loans, asset_cash_and_cash_equivalents FROM balance_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') AND liability_short_term_loans IS NOT NULL AND asset_cash_and_cash_equivalents IS NOT NULL AND liability_short_term_loans &gt; asset_cash_and_cash_equivalents ORDER BY (liability_short_term_loans - asset_cash_and_cash_equivalents) DESC LIMIT 50</t>
+        </is>
+      </c>
       <c r="E22" s="1" t="inlineStr">
         <is>
-          <t>table</t>
+          <t>bar</t>
         </is>
       </c>
       <c r="F22" s="1" t="inlineStr">
@@ -2730,15 +2830,19 @@
   "子问题": [
     {
       "Q": "2025年第三季度，“负债-短期借款”金额超过“资产-货币资金”金额的公司有哪些？请列出简称、短期借款（万元）、货币资金（万元）。",
-      "A": "澄清：请问要查询哪家公司？",
-      "SQL": "",
-      "image": ""
-    }
-  ]
-}</t>
-        </is>
-      </c>
-      <c r="G22" s="1" t="inlineStr"/>
+      "A": "符合条件共 18 家，前5：太极集团(600129) 5.78 亿元; 珍宝岛(603567) 2.04 亿元; 瑞康医药(002589) 42.41 亿元; 贵州百灵() 1.82 亿元; 新里程(002219) 3.08 亿元",
+      "SQL": "SELECT stock_abbr, stock_code, report_year, report_period, liability_short_term_loans, asset_cash_and_cash_equivalents FROM balance_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') AND liability_short_term_loans IS NOT NULL AND asset_cash_and_cash_equivalents IS NOT NULL AND liability_short_term_loans &gt; asset_cash_and_cash_equivalents ORDER BY (liability_short_term_loans - asset_cash_and_cash_equivalents) DESC LIMIT 50",
+      "image": "B1021_1.jpg"
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G22" s="1" t="inlineStr">
+        <is>
+          <t>B1021_1.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="120" customHeight="1">
       <c r="A23" s="1" t="inlineStr">
@@ -2756,10 +2860,14 @@
           <t>[{"Q": "2025年第三季度，“核心业绩指标表”中的“营业总收入”与“利润表”中的“营业总收入”不一致的公司有哪些？请列出股票代码及两个表中的数值。"}]</t>
         </is>
       </c>
-      <c r="D23" s="1" t="inlineStr"/>
+      <c r="D23" s="1" t="inlineStr">
+        <is>
+          <t>SELECT c.stock_abbr, c.stock_code, c.report_year, c.report_period, c.total_operating_revenue AS core_营业总收入, i.total_operating_revenue AS income_营业总收入, ABS(c.total_operating_revenue - i.total_operating_revenue) AS 差值绝对值 FROM core_performance_indicators_sheet c JOIN income_sheet i USING (stock_code, report_year, report_period) WHERE (c.report_year IN (2025) AND c.report_period IN ('Q3')) AND c.total_operating_revenue IS NOT NULL AND i.total_operating_revenue IS NOT NULL AND ABS(c.total_operating_revenue - i.total_operating_revenue) &gt; 1 ORDER BY 差值绝对值 DESC LIMIT 50</t>
+        </is>
+      </c>
       <c r="E23" s="1" t="inlineStr">
         <is>
-          <t>table</t>
+          <t>bar</t>
         </is>
       </c>
       <c r="F23" s="1" t="inlineStr">
@@ -2770,15 +2878,19 @@
   "子问题": [
     {
       "Q": "2025年第三季度，“核心业绩指标表”中的“营业总收入”与“利润表”中的“营业总收入”不一致的公司有哪些？请列出股票代码及两个表中的数值。",
-      "A": "澄清：请问要查询哪家公司？",
-      "SQL": "",
-      "image": ""
-    }
-  ]
-}</t>
-        </is>
-      </c>
-      <c r="G23" s="1" t="inlineStr"/>
+      "A": "符合条件共 30 家，前5：白云山(600332) —; 同仁堂(600085) —; 步长制药(603858) —; 太极集团(600129) —; 片仔癀(600436) —",
+      "SQL": "SELECT c.stock_abbr, c.stock_code, c.report_year, c.report_period, c.total_operating_revenue AS core_营业总收入, i.total_operating_revenue AS income_营业总收入, ABS(c.total_operating_revenue - i.total_operating_revenue) AS 差值绝对值 FROM core_performance_indicators_sheet c JOIN income_sheet i USING (stock_code, report_year, report_period) WHERE (c.report_year IN (2025) AND c.report_period IN ('Q3')) AND c.total_operating_revenue IS NOT NULL AND i.total_operating_revenue IS NOT NULL AND ABS(c.total_operating_revenue - i.total_operating_revenue) &gt; 1 ORDER BY 差值绝对值 DESC LIMIT 50",
+      "image": "B1022_1.jpg"
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G23" s="1" t="inlineStr">
+        <is>
+          <t>B1022_1.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="120" customHeight="1">
       <c r="A24" s="1" t="inlineStr">
@@ -2844,10 +2956,14 @@
           <t>[{"Q": "2025年第三季度，“扣非净利润”与“净利润”的差值绝对值最大的5家公司是哪些？请列出简称、净利润（万元）、扣非净利润（万元）及差值。"}]</t>
         </is>
       </c>
-      <c r="D25" s="1" t="inlineStr"/>
+      <c r="D25" s="1" t="inlineStr">
+        <is>
+          <t>SELECT t1.stock_abbr, t1.stock_code, t1.report_year, t1.report_period, t1.net_profit_excl_non_recurring, t2.net_profit, ABS(t1.net_profit_excl_non_recurring - t2.net_profit) AS 差值绝对值 FROM core_performance_indicators_sheet t1 JOIN income_sheet t2 USING (stock_code, report_year, report_period) WHERE (t1.report_year IN (2025) AND t1.report_period IN ('Q3')) AND t1.net_profit_excl_non_recurring IS NOT NULL AND t2.net_profit IS NOT NULL ORDER BY 差值绝对值 DESC LIMIT 5</t>
+        </is>
+      </c>
       <c r="E25" s="1" t="inlineStr">
         <is>
-          <t>table</t>
+          <t>bar</t>
         </is>
       </c>
       <c r="F25" s="1" t="inlineStr">
@@ -2858,8 +2974,8 @@
   "子问题": [
     {
       "Q": "2025年第三季度，“扣非净利润”与“净利润”的差值绝对值最大的5家公司是哪些？请列出简称、净利润（万元）、扣非净利润（万元）及差值。",
-      "A": "澄清：请问要查询哪家公司？",
-      "SQL": "",
+      "A": "未查询到数据",
+      "SQL": "SELECT t1.stock_abbr, t1.stock_code, t1.report_year, t1.report_period, t1.net_profit_excl_non_recurring, t2.net_profit, ABS(t1.net_profit_excl_non_recurring - t2.net_profit) AS 差值绝对值 FROM core_performance_indicators_sheet t1 JOIN income_sheet t2 USING (stock_code, report_year, report_period) WHERE (t1.report_year IN (2025) AND t1.report_period IN ('Q3')) AND t1.net_profit_excl_non_recurring IS NOT NULL AND t2.net_profit IS NOT NULL ORDER BY 差值绝对值 DESC LIMIT 5",
       "image": ""
     }
   ]
@@ -2886,12 +3002,12 @@
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
-          <t>SELECT COUNT(*) AS 数量 FROM cash_flow_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') AND net_cash_flow &gt; 0 AND net_cash_flow IS NOT NULL</t>
+          <t>SELECT t1.stock_abbr, t1.stock_code, t1.report_year, t1.report_period, t1.investing_cf_net_amount, t2.total_operating_revenue FROM cash_flow_sheet t1 JOIN income_sheet t2 USING (stock_code, report_year, report_period) WHERE (t1.report_year IN (2025) AND t1.report_period IN ('Q3')) AND t1.investing_cf_net_amount IS NOT NULL AND t2.total_operating_revenue IS NOT NULL AND t1.investing_cf_net_amount &gt; t2.total_operating_revenue ORDER BY (t1.investing_cf_net_amount - t2.total_operating_revenue) DESC LIMIT 50</t>
         </is>
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
-          <t>table</t>
+          <t>bar</t>
         </is>
       </c>
       <c r="F26" s="1" t="inlineStr">
@@ -2902,19 +3018,15 @@
   "子问题": [
     {
       "Q": "2025年第三季度，“投资性现金流量净额”为正数（即投资现金流入大于流出）的公司有多少家？请列出其中营收排名前三的公司简称及投资现金流净额（万元）。",
-      "A": "共 8 家",
-      "SQL": "SELECT COUNT(*) AS 数量 FROM cash_flow_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') AND net_cash_flow &gt; 0 AND net_cash_flow IS NOT NULL",
-      "image": "B1025_1.jpg"
-    }
-  ]
-}</t>
-        </is>
-      </c>
-      <c r="G26" s="1" t="inlineStr">
-        <is>
-          <t>B1025_1.jpg</t>
-        </is>
-      </c>
+      "A": "未查询到数据",
+      "SQL": "SELECT t1.stock_abbr, t1.stock_code, t1.report_year, t1.report_period, t1.investing_cf_net_amount, t2.total_operating_revenue FROM cash_flow_sheet t1 JOIN income_sheet t2 USING (stock_code, report_year, report_period) WHERE (t1.report_year IN (2025) AND t1.report_period IN ('Q3')) AND t1.investing_cf_net_amount IS NOT NULL AND t2.total_operating_revenue IS NOT NULL AND t1.investing_cf_net_amount &gt; t2.total_operating_revenue ORDER BY (t1.investing_cf_net_amount - t2.total_operating_revenue) DESC LIMIT 50",
+      "image": ""
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G26" s="1" t="inlineStr"/>
     </row>
     <row r="27" ht="120" customHeight="1">
       <c r="A27" s="1" t="inlineStr">
@@ -2980,10 +3092,14 @@
           <t>[{"Q": "2025年第三季度，“资产-总资产同比增长率”超过“营业总收入同比增长率”10个百分点以上的公司有哪些？请列出简称、资产增长率（%）、营收增长率（%）。"}]</t>
         </is>
       </c>
-      <c r="D28" s="1" t="inlineStr"/>
+      <c r="D28" s="1" t="inlineStr">
+        <is>
+          <t>SELECT t1.stock_abbr, t1.stock_code, t1.report_year, t1.report_period, t1.asset_total_assets_yoy_growth, t2.operating_revenue_yoy_growth, (t1.asset_total_assets_yoy_growth - t2.operating_revenue_yoy_growth) AS 差值 FROM balance_sheet t1 JOIN income_sheet t2 USING (stock_code, report_year, report_period) WHERE (t1.report_year IN (2025) AND t1.report_period IN ('Q3')) AND t1.asset_total_assets_yoy_growth IS NOT NULL AND t2.operating_revenue_yoy_growth IS NOT NULL AND (t1.asset_total_assets_yoy_growth - t2.operating_revenue_yoy_growth) &gt; 10.0 ORDER BY 差值 DESC LIMIT 50</t>
+        </is>
+      </c>
       <c r="E28" s="1" t="inlineStr">
         <is>
-          <t>table</t>
+          <t>bar</t>
         </is>
       </c>
       <c r="F28" s="1" t="inlineStr">
@@ -2994,8 +3110,8 @@
   "子问题": [
     {
       "Q": "2025年第三季度，“资产-总资产同比增长率”超过“营业总收入同比增长率”10个百分点以上的公司有哪些？请列出简称、资产增长率（%）、营收增长率（%）。",
-      "A": "澄清：请问要查询哪家公司？",
-      "SQL": "",
+      "A": "未查询到数据",
+      "SQL": "SELECT t1.stock_abbr, t1.stock_code, t1.report_year, t1.report_period, t1.asset_total_assets_yoy_growth, t2.operating_revenue_yoy_growth, (t1.asset_total_assets_yoy_growth - t2.operating_revenue_yoy_growth) AS 差值 FROM balance_sheet t1 JOIN income_sheet t2 USING (stock_code, report_year, report_period) WHERE (t1.report_year IN (2025) AND t1.report_period IN ('Q3')) AND t1.asset_total_assets_yoy_growth IS NOT NULL AND t2.operating_revenue_yoy_growth IS NOT NULL AND (t1.asset_total_assets_yoy_growth - t2.operating_revenue_yoy_growth) &gt; 10.0 ORDER BY 差值 DESC LIMIT 50",
       "image": ""
     }
   ]
@@ -3256,10 +3372,14 @@
           <t>[{"Q": "结合现金流量表和利润表，查询2024年全年所有公司的股票代码、简称、净利润（利润表）、经营性现金流量净额（现金流量表），筛选出经营性现金流量净额大于净利润的公司。"}]</t>
         </is>
       </c>
-      <c r="D34" s="1" t="inlineStr"/>
+      <c r="D34" s="1" t="inlineStr">
+        <is>
+          <t>SELECT t1.stock_abbr, t1.stock_code, t1.report_year, t1.report_period, t1.net_profit, t2.operating_cf_net_amount FROM income_sheet t1 JOIN cash_flow_sheet t2 USING (stock_code, report_year, report_period) WHERE (t1.report_year IN (2024) AND t1.report_period IN ('FY')) AND t1.net_profit IS NOT NULL AND t2.operating_cf_net_amount IS NOT NULL AND t1.net_profit &gt; t2.operating_cf_net_amount ORDER BY (t1.net_profit - t2.operating_cf_net_amount) DESC LIMIT 50</t>
+        </is>
+      </c>
       <c r="E34" s="1" t="inlineStr">
         <is>
-          <t>table</t>
+          <t>bar</t>
         </is>
       </c>
       <c r="F34" s="1" t="inlineStr">
@@ -3270,15 +3390,19 @@
   "子问题": [
     {
       "Q": "结合现金流量表和利润表，查询2024年全年所有公司的股票代码、简称、净利润（利润表）、经营性现金流量净额（现金流量表），筛选出经营性现金流量净额大于净利润的公司。",
-      "A": "澄清：请问要查询哪家公司？",
-      "SQL": "",
-      "image": ""
-    }
-  ]
-}</t>
-        </is>
-      </c>
-      <c r="G34" s="1" t="inlineStr"/>
+      "A": "符合条件共 8 家，前5：片仔癀(600436) 13.14 亿元; 云南白药(000538) 42.97 亿元; 珍宝岛(603567) 1.64 亿元; 太龙药业(600222) -3,958.57 万元; 金花股份(600080) 1,085.87 万元",
+      "SQL": "SELECT t1.stock_abbr, t1.stock_code, t1.report_year, t1.report_period, t1.net_profit, t2.operating_cf_net_amount FROM income_sheet t1 JOIN cash_flow_sheet t2 USING (stock_code, report_year, report_period) WHERE (t1.report_year IN (2024) AND t1.report_period IN ('FY')) AND t1.net_profit IS NOT NULL AND t2.operating_cf_net_amount IS NOT NULL AND t1.net_profit &gt; t2.operating_cf_net_amount ORDER BY (t1.net_profit - t2.operating_cf_net_amount) DESC LIMIT 50",
+      "image": "B1033_1.jpg"
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G34" s="1" t="inlineStr">
+        <is>
+          <t>B1033_1.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="120" customHeight="1">
       <c r="A35" s="1" t="inlineStr">
@@ -3574,7 +3698,7 @@
       </c>
       <c r="D41" s="1" t="inlineStr">
         <is>
-          <t>SELECT stock_abbr, stock_code, report_year, report_period, asset_total_assets FROM balance_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') AND asset_total_assets &gt; 20.0 AND asset_total_assets &lt; 0 AND asset_total_assets IS NOT NULL ORDER BY asset_total_assets DESC LIMIT 10</t>
+          <t>SELECT stock_abbr, stock_code, report_year, report_period, asset_cash_and_cash_equivalents, asset_total_assets FROM balance_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') AND asset_cash_and_cash_equivalents IS NOT NULL AND asset_total_assets IS NOT NULL AND asset_cash_and_cash_equivalents &gt; asset_total_assets ORDER BY (asset_cash_and_cash_equivalents - asset_total_assets) DESC LIMIT 50</t>
         </is>
       </c>
       <c r="E41" s="1" t="inlineStr">
@@ -3591,7 +3715,7 @@
     {
       "Q": "关联资产负债表和现金流量表，查询2025年第三季度货币资金占总资产比例超过20%，且投资性现金流量净额为负数的公司，按货币资金占比从高到低排序。",
       "A": "未查询到数据",
-      "SQL": "SELECT stock_abbr, stock_code, report_year, report_period, asset_total_assets FROM balance_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') AND asset_total_assets &gt; 20.0 AND asset_total_assets &lt; 0 AND asset_total_assets IS NOT NULL ORDER BY asset_total_assets DESC LIMIT 10",
+      "SQL": "SELECT stock_abbr, stock_code, report_year, report_period, asset_cash_and_cash_equivalents, asset_total_assets FROM balance_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') AND asset_cash_and_cash_equivalents IS NOT NULL AND asset_total_assets IS NOT NULL AND asset_cash_and_cash_equivalents &gt; asset_total_assets ORDER BY (asset_cash_and_cash_equivalents - asset_total_assets) DESC LIMIT 50",
       "image": ""
     }
   ]
@@ -3616,10 +3740,14 @@
           <t>[{"Q": "检查2025年第三季度核心业绩指标表中的“营业总收入”与利润表中的“营业收入”数值不一致的公司，列出股票代码、两个表中的数值及差值（绝对值）。"}]</t>
         </is>
       </c>
-      <c r="D42" s="1" t="inlineStr"/>
+      <c r="D42" s="1" t="inlineStr">
+        <is>
+          <t>SELECT c.stock_abbr, c.stock_code, c.report_year, c.report_period, c.total_operating_revenue AS core_营业总收入, i.total_operating_revenue AS income_营业总收入, ABS(c.total_operating_revenue - i.total_operating_revenue) AS 差值绝对值 FROM core_performance_indicators_sheet c JOIN income_sheet i USING (stock_code, report_year, report_period) WHERE (c.report_year IN (2025) AND c.report_period IN ('Q3')) AND c.total_operating_revenue IS NOT NULL AND i.total_operating_revenue IS NOT NULL AND ABS(c.total_operating_revenue - i.total_operating_revenue) &gt; 1 ORDER BY 差值绝对值 DESC LIMIT 50</t>
+        </is>
+      </c>
       <c r="E42" s="1" t="inlineStr">
         <is>
-          <t>table</t>
+          <t>bar</t>
         </is>
       </c>
       <c r="F42" s="1" t="inlineStr">
@@ -3630,15 +3758,19 @@
   "子问题": [
     {
       "Q": "检查2025年第三季度核心业绩指标表中的“营业总收入”与利润表中的“营业收入”数值不一致的公司，列出股票代码、两个表中的数值及差值（绝对值）。",
-      "A": "澄清：请问要查询哪家公司？",
-      "SQL": "",
-      "image": ""
-    }
-  ]
-}</t>
-        </is>
-      </c>
-      <c r="G42" s="1" t="inlineStr"/>
+      "A": "符合条件共 30 家，前5：白云山(600332) —; 同仁堂(600085) —; 步长制药(603858) —; 太极集团(600129) —; 片仔癀(600436) —",
+      "SQL": "SELECT c.stock_abbr, c.stock_code, c.report_year, c.report_period, c.total_operating_revenue AS core_营业总收入, i.total_operating_revenue AS income_营业总收入, ABS(c.total_operating_revenue - i.total_operating_revenue) AS 差值绝对值 FROM core_performance_indicators_sheet c JOIN income_sheet i USING (stock_code, report_year, report_period) WHERE (c.report_year IN (2025) AND c.report_period IN ('Q3')) AND c.total_operating_revenue IS NOT NULL AND i.total_operating_revenue IS NOT NULL AND ABS(c.total_operating_revenue - i.total_operating_revenue) &gt; 1 ORDER BY 差值绝对值 DESC LIMIT 50",
+      "image": "B1041_1.jpg"
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G42" s="1" t="inlineStr">
+        <is>
+          <t>B1041_1.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="120" customHeight="1">
       <c r="A43" s="1" t="inlineStr">
@@ -4232,10 +4364,14 @@
           <t>[{"Q": "查询2025年第三季度经营性现金流量净额与净利润的比值分布，用直方图展示"}]</t>
         </is>
       </c>
-      <c r="D54" s="1" t="inlineStr"/>
+      <c r="D54" s="1" t="inlineStr">
+        <is>
+          <t>SELECT t1.stock_abbr, t1.stock_code, (t1.operating_cf_net_amount*1.0 / NULLIF(t2.net_profit,0)) AS 比值 FROM cash_flow_sheet t1 JOIN income_sheet t2 USING (stock_code, report_year, report_period) WHERE (t1.report_year IN (2025) AND t1.report_period IN ('Q3')) AND t1.operating_cf_net_amount IS NOT NULL AND t2.net_profit IS NOT NULL AND t2.net_profit != 0</t>
+        </is>
+      </c>
       <c r="E54" s="1" t="inlineStr">
         <is>
-          <t>table</t>
+          <t>hist</t>
         </is>
       </c>
       <c r="F54" s="1" t="inlineStr">
@@ -4246,15 +4382,19 @@
   "子问题": [
     {
       "Q": "查询2025年第三季度经营性现金流量净额与净利润的比值分布，用直方图展示",
-      "A": "澄清：请问要查询哪家公司？",
-      "SQL": "",
-      "image": ""
-    }
-  ]
-}</t>
-        </is>
-      </c>
-      <c r="G54" s="1" t="inlineStr"/>
+      "A": "符合条件共 28 家，前5：金花股份(600080) —; 同仁堂(600085) —; 太极集团(600129) —; 太龙药业(600222) —; 中恒集团(600252) —",
+      "SQL": "SELECT t1.stock_abbr, t1.stock_code, (t1.operating_cf_net_amount*1.0 / NULLIF(t2.net_profit,0)) AS 比值 FROM cash_flow_sheet t1 JOIN income_sheet t2 USING (stock_code, report_year, report_period) WHERE (t1.report_year IN (2025) AND t1.report_period IN ('Q3')) AND t1.operating_cf_net_amount IS NOT NULL AND t2.net_profit IS NOT NULL AND t2.net_profit != 0",
+      "image": "B1053_1.jpg"
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G54" s="1" t="inlineStr">
+        <is>
+          <t>B1053_1.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="120" customHeight="1">
       <c r="A55" s="1" t="inlineStr">
@@ -4320,10 +4460,14 @@
           <t>[{"Q": "对比2024年和2025年第三季度净利润同比增长率前十公司的名单变化，用双条形图展示两年排名及增长率"}]</t>
         </is>
       </c>
-      <c r="D56" s="1" t="inlineStr"/>
+      <c r="D56" s="1" t="inlineStr">
+        <is>
+          <t>SELECT stock_abbr, stock_code, report_year, report_period, net_profit_yoy_growth FROM (   SELECT stock_abbr, stock_code, report_year, report_period, net_profit_yoy_growth,     ROW_NUMBER() OVER (PARTITION BY report_year ORDER BY net_profit_yoy_growth DESC) AS rk   FROM income_sheet   WHERE report_year IN (2024, 2025) AND report_period='Q3' AND net_profit_yoy_growth IS NOT NULL ) WHERE rk &lt;= 10 ORDER BY report_year, rk</t>
+        </is>
+      </c>
       <c r="E56" s="1" t="inlineStr">
         <is>
-          <t>table</t>
+          <t>bar</t>
         </is>
       </c>
       <c r="F56" s="1" t="inlineStr">
@@ -4334,8 +4478,8 @@
   "子问题": [
     {
       "Q": "对比2024年和2025年第三季度净利润同比增长率前十公司的名单变化，用双条形图展示两年排名及增长率",
-      "A": "澄清：请问要分析哪家公司的趋势？",
-      "SQL": "",
+      "A": "未查询到数据",
+      "SQL": "SELECT stock_abbr, stock_code, report_year, report_period, net_profit_yoy_growth FROM (   SELECT stock_abbr, stock_code, report_year, report_period, net_profit_yoy_growth,     ROW_NUMBER() OVER (PARTITION BY report_year ORDER BY net_profit_yoy_growth DESC) AS rk   FROM income_sheet   WHERE report_year IN (2024, 2025) AND report_period='Q3' AND net_profit_yoy_growth IS NOT NULL ) WHERE rk &lt;= 10 ORDER BY report_year, rk",
       "image": ""
     }
   ]
@@ -4408,10 +4552,14 @@
           <t>[{"Q": "分析2025年第三季度营业总收入与净利润的相关性，用散点图展示"}]</t>
         </is>
       </c>
-      <c r="D58" s="1" t="inlineStr"/>
+      <c r="D58" s="1" t="inlineStr">
+        <is>
+          <t>SELECT stock_abbr, stock_code, total_operating_revenue, net_profit FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') AND total_operating_revenue IS NOT NULL AND net_profit IS NOT NULL</t>
+        </is>
+      </c>
       <c r="E58" s="1" t="inlineStr">
         <is>
-          <t>table</t>
+          <t>scatter</t>
         </is>
       </c>
       <c r="F58" s="1" t="inlineStr">
@@ -4422,15 +4570,19 @@
   "子问题": [
     {
       "Q": "分析2025年第三季度营业总收入与净利润的相关性，用散点图展示",
-      "A": "澄清：请问要查询哪家公司？",
-      "SQL": "",
-      "image": ""
-    }
-  ]
-}</t>
-        </is>
-      </c>
-      <c r="G58" s="1" t="inlineStr"/>
+      "A": "符合条件共 30 家，前5：金花股份(600080) 3,423.74 万元; 同仁堂(600085) 15.93 亿元; 太极集团(600129) 1.64 亿元; 太龙药业(600222) 3,047.46 万元; 中恒集团(600252) -931.86 万元",
+      "SQL": "SELECT stock_abbr, stock_code, total_operating_revenue, net_profit FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') AND total_operating_revenue IS NOT NULL AND net_profit IS NOT NULL",
+      "image": "B1057_1.jpg"
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G58" s="1" t="inlineStr">
+        <is>
+          <t>B1057_1.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="120" customHeight="1">
       <c r="A59" s="1" t="inlineStr">
@@ -4450,7 +4602,7 @@
       </c>
       <c r="D59" s="1" t="inlineStr">
         <is>
-          <t>SELECT stock_abbr, stock_code, report_year, report_period, asset_cash_and_cash_equivalents FROM balance_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END</t>
+          <t>SELECT stock_abbr, stock_code, report_year, report_period, liability_short_term_loans, asset_cash_and_cash_equivalents FROM balance_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') AND liability_short_term_loans IS NOT NULL AND asset_cash_and_cash_equivalents IS NOT NULL AND liability_short_term_loans &gt; asset_cash_and_cash_equivalents ORDER BY (liability_short_term_loans - asset_cash_and_cash_equivalents) DESC LIMIT 50</t>
         </is>
       </c>
       <c r="E59" s="1" t="inlineStr">
@@ -4466,8 +4618,8 @@
   "子问题": [
     {
       "Q": "查询2025年第三季度短期借款超过货币资金的公司，用表格列出具体数据，并用柱状图对比这两项指标的差额",
-      "A": "货币资金 对比：贵州百灵 2025三季报 1.82 亿元; 东阿阿胶 2025三季报 55.62 亿元; 云南白药 2025三季报 86.18 亿元; 启迪药业 2025三季报 1.56 亿元; 仁和药业 2025三季报 10.95 亿元; 通化金马 2025三季报 3.22 亿元; 华神科技 2025三季报 1.49 亿元; 九芝堂 2025三季报 3.02 亿元; 华润三九 2025三季报 56.23 亿元; 万邦德 2025三季报 8,307.08 万元; 沃华医药 2025三季报 3.93 亿元; 莱茵生物 2025三季报 2.55 亿元; 嘉应制药 2025三季报 1.28 亿元; 新里程 2025三季报 3.08 亿元; 桂林三金 2025三季报 10.78 亿元; 奇正藏药 2025三季报 2.84 亿元; 众生药业 2025三季报 9.32 亿元; 精华制药 2025三季报 7.24 亿元; 信邦制药 2025三季报 9.62 亿元; 益盛药业 2025三季报 1.16 亿元; 瑞康医药 2025三季报 42.41 亿元; 以岭药业 2025三季报 10.34 亿元; 特一药业 2025三季报 2.15 亿元; 葵花药业 2025三季报 6.85 亿元; 康弘药业 2025三季报 38.28 亿元; 盘龙药业 2025三季报 11.65 亿元; 新天药业 2025三季报 1.69 亿元; 华森制药 2025三季报 3.03 亿元; 红日药业 2025三季报 14.14 亿元; 振东制药 2025三季报 2.90 亿元; 佐力药业 2025三季报 6.93 亿元; 新光药业 2025三季报 2.91 亿元; 陇神戎发 2025三季报 —; 康泰医学 2025三季报 7.78 亿元; 维康药业 2025三季报 —; 粤万年青 2025三季报 1.42 亿元; 恩威医药 2025三季报 3.20 亿元; 金花股份 2025三季报 2.35 亿元; 同仁堂 2025三季报 109.10 亿元; 太极集团 2025三季报 5.78 亿元; 太龙药业 2025三季报 3.44 亿元; 中恒集团 2025三季报 40.57 亿元; 羚锐制药 2025三季报 4.60 亿元; 达仁堂 2025三季报 10.49 亿元; 白云山 2025三季报 137.08 亿元; 亚宝药业 2025三季报 6.45 亿元; 昆药集团 2025三季报 7.94 亿元; 片仔癀 2025三季报 13.47 亿元; 千金药业 2025三季报 5.65 亿元; 康美药业 2025三季报 11.81 亿元; 天士力 2025三季报 26.03 亿元; 康缘药业 2025三季报 21.57 亿元; 济川药业 2025三季报 51.30 亿元; 康恩贝 2025三季报 8.36 亿元; 益佰制药 2025三季报 5.94 亿元; 神奇制药 2025三季报 6.11 亿元; 天目药业 2025三季报 1,174.03 万元; 江中药业 2025三季报 19.99 亿元; 广誉远 2025三季报 2.96 亿元; 健民集团 2025三季报 1.75 亿元; 马应龙 2025三季报 15.41 亿元; 康惠制药 2025三季报 7,849.49 万元; 贵州三力 2025三季报 2.66 亿元; 珍宝岛 2025三季报 2.04 亿元; 步长制药 2025三季报 8.86 亿元; 寿仙谷 2025三季报 6.97 亿元; 方盛制药 2025三季报 1.80 亿元",
-      "SQL": "SELECT stock_abbr, stock_code, report_year, report_period, asset_cash_and_cash_equivalents FROM balance_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
+      "A": "货币资金 对比：太极集团 2025三季报 5.78 亿元; 珍宝岛 2025三季报 2.04 亿元; 瑞康医药 2025三季报 42.41 亿元; 贵州百灵 2025三季报 1.82 亿元; 新里程 2025三季报 3.08 亿元; 奇正藏药 2025三季报 2.84 亿元; 万邦德 2025三季报 8,307.08 万元; 贵州三力 2025三季报 2.66 亿元; 太龙药业 2025三季报 3.44 亿元; 莱茵生物 2025三季报 2.55 亿元; 方盛制药 2025三季报 1.80 亿元; 益盛药业 2025三季报 1.16 亿元; 康惠制药 2025三季报 7,849.49 万元; 天目药业 2025三季报 1,174.03 万元; 华神科技 2025三季报 1.49 亿元; 昆药集团 2025三季报 7.94 亿元; 羚锐制药 2025三季报 4.60 亿元; 特一药业 2025三季报 2.15 亿元",
+      "SQL": "SELECT stock_abbr, stock_code, report_year, report_period, liability_short_term_loans, asset_cash_and_cash_equivalents FROM balance_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') AND liability_short_term_loans IS NOT NULL AND asset_cash_and_cash_equivalents IS NOT NULL AND liability_short_term_loans &gt; asset_cash_and_cash_equivalents ORDER BY (liability_short_term_loans - asset_cash_and_cash_equivalents) DESC LIMIT 50",
       "image": "B1058_1.jpg"
     }
   ]
@@ -4546,7 +4698,7 @@
       </c>
       <c r="D61" s="1" t="inlineStr">
         <is>
-          <t>SELECT stock_abbr, stock_code, report_year, report_period, operating_expense_rnd_expenses FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY operating_expense_rnd_expenses DESC LIMIT 10</t>
+          <t>SELECT stock_abbr, stock_code, report_year, report_period, operating_expense_rnd_expenses, net_profit_yoy_growth, ABS(operating_expense_rnd_expenses - net_profit_yoy_growth) AS 差值绝对值 FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') AND operating_expense_rnd_expenses IS NOT NULL AND net_profit_yoy_growth IS NOT NULL ORDER BY 差值绝对值 DESC LIMIT 5</t>
         </is>
       </c>
       <c r="E61" s="1" t="inlineStr">
@@ -4562,19 +4714,15 @@
   "子问题": [
     {
       "Q": "对比2025年第三季度研发费用占比前十与后十公司的净利润同比增长率，用箱线图展示两组数据的分布差异",
-      "A": "研发费用 排名 Top5：1) 天士力 5.53 亿元; 2) 白云山 4.44 亿元; 3) 康缘药业 3.52 亿元; 4) 济川药业 2.72 亿元; 5) 太极集团 1.95 亿元",
-      "SQL": "SELECT stock_abbr, stock_code, report_year, report_period, operating_expense_rnd_expenses FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY operating_expense_rnd_expenses DESC LIMIT 10",
-      "image": "B1060_1.jpg"
-    }
-  ]
-}</t>
-        </is>
-      </c>
-      <c r="G61" s="1" t="inlineStr">
-        <is>
-          <t>B1060_1.jpg</t>
-        </is>
-      </c>
+      "A": "未查询到数据",
+      "SQL": "SELECT stock_abbr, stock_code, report_year, report_period, operating_expense_rnd_expenses, net_profit_yoy_growth, ABS(operating_expense_rnd_expenses - net_profit_yoy_growth) AS 差值绝对值 FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') AND operating_expense_rnd_expenses IS NOT NULL AND net_profit_yoy_growth IS NOT NULL ORDER BY 差值绝对值 DESC LIMIT 5",
+      "image": ""
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G61" s="1" t="inlineStr"/>
     </row>
     <row r="62" ht="120" customHeight="1">
       <c r="A62" s="1" t="inlineStr">
@@ -4688,10 +4836,14 @@
           <t>[{"Q": "分析2022-2025年第三季度66家中药公司营业总收入的复合增长率分布，用直方图展示"}]</t>
         </is>
       </c>
-      <c r="D64" s="1" t="inlineStr"/>
+      <c r="D64" s="1" t="inlineStr">
+        <is>
+          <t>SELECT stock_abbr, stock_code, report_year, total_operating_revenue FROM income_sheet WHERE report_period='Q3' AND report_year IN (2022, 2025) AND total_operating_revenue IS NOT NULL</t>
+        </is>
+      </c>
       <c r="E64" s="1" t="inlineStr">
         <is>
-          <t>table</t>
+          <t>hist</t>
         </is>
       </c>
       <c r="F64" s="1" t="inlineStr">
@@ -4702,8 +4854,8 @@
   "子问题": [
     {
       "Q": "分析2022-2025年第三季度66家中药公司营业总收入的复合增长率分布，用直方图展示",
-      "A": "澄清：请问要查询哪家公司？",
-      "SQL": "",
+      "A": "符合条件共 30 家，前5：金花股份(600080) 3.84 亿元; 同仁堂(600085) 133.08 亿元; 太极集团(600129) 80.88 亿元; 太龙药业(600222) 11.87 亿元; 中恒集团(600252) 19.48 亿元",
+      "SQL": "SELECT stock_abbr, stock_code, report_year, total_operating_revenue FROM income_sheet WHERE report_period='Q3' AND report_year IN (2022, 2025) AND total_operating_revenue IS NOT NULL",
       "image": ""
     }
   ]
@@ -4776,10 +4928,14 @@
           <t>[{"Q": "查询2025年第三季度出口业务占比超过10%的中药公司，用表格列出其出口占比、营业总收入增长率，并用折线图展示它们的营收增长趋势"}]</t>
         </is>
       </c>
-      <c r="D66" s="1" t="inlineStr"/>
+      <c r="D66" s="1" t="inlineStr">
+        <is>
+          <t>SELECT stock_abbr, stock_code, report_year, report_period, total_operating_revenue FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') AND total_operating_revenue &gt; 10.0 AND total_operating_revenue IS NOT NULL ORDER BY total_operating_revenue DESC LIMIT 50</t>
+        </is>
+      </c>
       <c r="E66" s="1" t="inlineStr">
         <is>
-          <t>table</t>
+          <t>line</t>
         </is>
       </c>
       <c r="F66" s="1" t="inlineStr">
@@ -4790,15 +4946,19 @@
   "子问题": [
     {
       "Q": "查询2025年第三季度出口业务占比超过10%的中药公司，用表格列出其出口占比、营业总收入增长率，并用折线图展示它们的营收增长趋势",
-      "A": "澄清：请问要分析哪家公司的趋势？",
-      "SQL": "",
-      "image": ""
-    }
-  ]
-}</t>
-        </is>
-      </c>
-      <c r="G66" s="1" t="inlineStr"/>
+      "A": "白云山的营业总收入从2025三季报的 616.06 亿元 变化到2025三季报的 1.59 亿元（-99.74%）",
+      "SQL": "SELECT stock_abbr, stock_code, report_year, report_period, total_operating_revenue FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') AND total_operating_revenue &gt; 10.0 AND total_operating_revenue IS NOT NULL ORDER BY total_operating_revenue DESC LIMIT 50",
+      "image": "B1065_1.jpg"
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G66" s="1" t="inlineStr">
+        <is>
+          <t>B1065_1.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="120" customHeight="1">
       <c r="A67" s="1" t="inlineStr">
